--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1114"/>
+  <dimension ref="A1:F1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27181,12 +27181,12 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hyner, Jan Mrógala, Krystof Krmaschek, Jan Hula </t>
+          <t xml:space="preserve">Petr Hyner, Jan Mrógala, Jan Hula </t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learning to Search with Subgoals. </t>
+          <t xml:space="preserve"> Ability Transfer Through Language Mixing. </t>
         </is>
       </c>
       <c r="C893" t="n">
@@ -27199,28 +27199,28 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-02725-2_24 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2025.ijcnlp-long.76/ </t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Computational Intelligence - 18th International Work-Conference on Artificial Neural Networks, IWANN 2025, A Coruña, Spain, June 16-18, 2025, Proceedings, Part I: 310-321 (2025).</t>
+          <t xml:space="preserve"> Proceedings of the 14th International Joint Conference on Natural Language Processing and the 4th Conference of the Asia-Pacific Chapter of the Association for Computational Linguistics, IJCNLP-AACL 2025, Mumbai, India, December 20-24, 2025: 1374-1381 (2025).</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hula, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
+          <t xml:space="preserve">Petr Hyner, Jan Mrógala, Krystof Krmaschek, Jan Hula </t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards an Understanding of Stepwise Inference in Transformers: A Synthetic Graph Navigation Model. </t>
+          <t xml:space="preserve"> Learning to Search with Subgoals. </t>
         </is>
       </c>
       <c r="C894" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -27229,24 +27229,24 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=8VEGkphQaK </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-02725-2_24 </t>
         </is>
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 23758-23780 (2024).</t>
+          <t xml:space="preserve"> Advances in Computational Intelligence - 18th International Work-Conference on Artificial Neural Networks, IWANN 2025, A Coruña, Spain, June 16-18, 2025, Proceedings, Part I: 310-321 (2025).</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Mojzísek, Jan Hula </t>
+          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hula, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient Solver Scheduling and Selection for Satisfiability Modulo Theories (SMT) Problems. </t>
+          <t xml:space="preserve"> Towards an Understanding of Stepwise Inference in Transformers: A Synthetic Graph Navigation Model. </t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -27259,24 +27259,24 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0012393600003654 </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=8VEGkphQaK </t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 13th International Conference on Pattern Recognition Applications and Methods, ICPRAM 2024, Rome, Italy, February 24-26, 2024.: 360-369 (2024).</t>
+          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 23758-23780 (2024).</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Adamczyk, Jan Hula </t>
+          <t xml:space="preserve">David Mojzísek, Jan Hula </t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient Use of Large Language Models for Analysis of Text Corpora. </t>
+          <t xml:space="preserve"> Efficient Solver Scheduling and Selection for Satisfiability Modulo Theories (SMT) Problems. </t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -27289,24 +27289,24 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0012349800003654 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0012393600003654 </t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 13th International Conference on Pattern Recognition Applications and Methods, ICPRAM 2024, Rome, Italy, February 24-26, 2024.: 695-705 (2024).</t>
+          <t xml:space="preserve"> Proceedings of the 13th International Conference on Pattern Recognition Applications and Methods, ICPRAM 2024, Rome, Italy, February 24-26, 2024.: 360-369 (2024).</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hyner, Petr Marek, David Adamczyk, Jan Hula, Jan Sedivý </t>
+          <t xml:space="preserve">David Adamczyk, Jan Hula </t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stealing Brains: From English to Czech Language Model. </t>
+          <t xml:space="preserve"> Efficient Use of Large Language Models for Analysis of Text Corpora. </t>
         </is>
       </c>
       <c r="C897" t="n">
@@ -27319,24 +27319,24 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0013064500003837 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0012349800003654 </t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 16th International Joint Conference on Computational Intelligence, IJCCI 2024, Porto, Portugal, November 20-22, 2024.: 606-612 (2024).</t>
+          <t xml:space="preserve"> Proceedings of the 13th International Conference on Pattern Recognition Applications and Methods, ICPRAM 2024, Rome, Italy, February 24-26, 2024.: 695-705 (2024).</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hula, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
+          <t xml:space="preserve">Petr Hyner, Petr Marek, David Adamczyk, Jan Hula, Jan Sedivý </t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards an Understanding of Stepwise Inference in Transformers: A Synthetic Graph Navigation Model. </t>
+          <t xml:space="preserve"> Stealing Brains: From English to Czech Language Model. </t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -27349,24 +27349,24 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.07757 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0013064500003837 </t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2402.07757 (2024).</t>
+          <t xml:space="preserve"> Proceedings of the 16th International Joint Conference on Computational Intelligence, IJCCI 2024, Porto, Portugal, November 20-22, 2024.: 606-612 (2024).</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Fajcik, Martin Docekal, Jan Dolezal, Karel Ondrej, Karel Benes, Jan Kapsa, Pavel Smrz, Alexander Polok, Michal Hradis, Zuzana Neverilová, Ales Horák, Radoslav Sabol, Michal Stefánik, Adam Jirkovsky, David Adamczyk, Petr Hyner, Jan Hula, Hynek Kydlícek </t>
+          <t xml:space="preserve">Mikail Khona, Maya Okawa, Jan Hula, Rahul Ramesh, Kento Nishi, Robert P. Dick, Ekdeep Singh Lubana, Hidenori Tanaka </t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BenCzechMark : A Czech-centric Multitask and Multimetric Benchmark for Large Language Models with Duel Scoring Mechanism. </t>
+          <t xml:space="preserve"> Towards an Understanding of Stepwise Inference in Transformers: A Synthetic Graph Navigation Model. </t>
         </is>
       </c>
       <c r="C899" t="n">
@@ -27379,28 +27379,28 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.17933 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.07757 </t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.17933 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2402.07757 (2024).</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula, Marek Vajgl, Pavel Vlasánek, Tomas Nejezchleba </t>
+          <t xml:space="preserve">Martin Fajcik, Martin Docekal, Jan Dolezal, Karel Ondrej, Karel Benes, Jan Kapsa, Pavel Smrz, Alexander Polok, Michal Hradis, Zuzana Neverilová, Ales Horák, Radoslav Sabol, Michal Stefánik, Adam Jirkovsky, David Adamczyk, Petr Hyner, Jan Hula, Hynek Kydlícek </t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Poly-YOLO: higher speed, more precise detection and instance segmentation for YOLOv3. </t>
+          <t xml:space="preserve"> BenCzechMark : A Czech-centric Multitask and Multimetric Benchmark for Large Language Models with Duel Scoring Mechanism. </t>
         </is>
       </c>
       <c r="C900" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -27409,24 +27409,24 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s00521-021-05978-9 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.17933 </t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Neural Comput. Appl. 34: 8275-8290 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.17933 (2024).</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Stefania Tomasiello, Jan Hula, David Hynar </t>
+          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula, Marek Vajgl, Pavel Vlasánek, Tomas Nejezchleba </t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Binary cross-entropy with dynamical clipping. </t>
+          <t xml:space="preserve"> Poly-YOLO: higher speed, more precise detection and instance segmentation for YOLOv3. </t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -27439,24 +27439,24 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s00521-022-07091-x </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s00521-021-05978-9 </t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Neural Comput. Appl. 34: 12029-12041 (2022).</t>
+          <t xml:space="preserve"> Neural Comput. Appl. 34: 8275-8290 (2022).</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, David Adamczyk </t>
+          <t xml:space="preserve">Petr Hurtík, Stefania Tomasiello, Jan Hula, David Hynar </t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3D Shapes Classification Using Intermediate Parts Representation. </t>
+          <t xml:space="preserve"> Binary cross-entropy with dynamical clipping. </t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -27469,24 +27469,24 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-08974-9_34 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s00521-022-07091-x </t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Processing and Management of Uncertainty in Knowledge-Based Systems - 19th International Conference, IPMU 2022, Milan, Italy, July 11-15, 2022, Proceedings, Part II: 431-442 (2022).</t>
+          <t xml:space="preserve"> Neural Comput. Appl. 34: 12029-12041 (2022).</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Mojzísek, Jan Hula </t>
+          <t xml:space="preserve">Jan Hula, David Mojzísek, David Adamczyk </t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Image Classifier with Dynamic Set of Known Classes. </t>
+          <t xml:space="preserve"> 3D Shapes Classification Using Intermediate Parts Representation. </t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -27499,24 +27499,24 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://ceur-ws.org/Vol-3226/paper8.pdf </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-08974-9_34 </t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 22nd Conference Information Technologies - Applications and Theory (ITAT 2022), Zuberec, Slovakia, September 23-27, 2022.: 68-74 (2022).</t>
+          <t xml:space="preserve"> Information Processing and Management of Uncertainty in Knowledge-Based Systems - 19th International Conference, IPMU 2022, Milan, Italy, July 11-15, 2022, Proceedings, Part II: 431-442 (2022).</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xinying Chen, Jan Hula, Antonín Dvorák </t>
+          <t xml:space="preserve">David Mojzísek, Jan Hula </t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analysis of the Semantic Vector Space Induced by a Neural Language Model and a Corpus. </t>
+          <t xml:space="preserve"> Image Classifier with Dynamic Set of Known Classes. </t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -27529,28 +27529,28 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://ceur-ws.org/Vol-3226/paper12.pdf </t>
+          <t xml:space="preserve"> https://ceur-ws.org/Vol-3226/paper8.pdf </t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 22nd Conference Information Technologies - Applications and Theory (ITAT 2022), Zuberec, Slovakia, September 23-27, 2022.: 103-110 (2022).</t>
+          <t xml:space="preserve"> Proceedings of the 22nd Conference Information Technologies - Applications and Theory (ITAT 2022), Zuberec, Slovakia, September 23-27, 2022.: 68-74 (2022).</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Adamczyk, David Mojzísek, Vojtech Molek </t>
+          <t xml:space="preserve">Xinying Chen, Jan Hula, Antonín Dvorák </t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Segmenting out Generic Objects in Monocular Videos. </t>
+          <t xml:space="preserve"> Analysis of the Semantic Vector Space Induced by a Neural Language Model and a Corpus. </t>
         </is>
       </c>
       <c r="C905" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -27559,28 +27559,28 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://ceur-ws.org/Vol-2962/paper49.pdf </t>
+          <t xml:space="preserve"> https://ceur-ws.org/Vol-3226/paper12.pdf </t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st Conference Information Technologies - Applications and Theory (ITAT 2021), Hotel Heľpa, Nízke Tatry and Muránska planina, Slovakia, September 24-28, 2021.: 123-129 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 22nd Conference Information Technologies - Applications and Theory (ITAT 2022), Zuberec, Slovakia, September 23-27, 2022.: 103-110 (2022).</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula </t>
+          <t xml:space="preserve">Jan Hula, David Adamczyk, David Mojzísek, Vojtech Molek </t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Data Preprocessing Technique for Neural Networks Based on Image Represented by a Fuzzy Function. </t>
+          <t xml:space="preserve"> Segmenting out Generic Objects in Monocular Videos. </t>
         </is>
       </c>
       <c r="C906" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -27589,24 +27589,24 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TFUZZ.2019.2911494 </t>
+          <t xml:space="preserve"> https://ceur-ws.org/Vol-2962/paper49.pdf </t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Fuzzy Syst. 28: 1195-1204 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 21st Conference Information Technologies - Applications and Theory (ITAT 2021), Hotel Heľpa, Nízke Tatry and Muránska planina, Slovakia, September 24-28, 2021.: 123-129 (2021).</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, David Mojzísek, David Adamczyk, Radek Cech </t>
+          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula </t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Acquiring Custom OCR System with Minimal Manual Annotation. </t>
+          <t xml:space="preserve"> Data Preprocessing Technique for Neural Networks Based on Image Represented by a Fuzzy Function. </t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -27619,24 +27619,24 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/DSMP47368.2020.9204229 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TFUZZ.2019.2911494 </t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Third International Conference on Data Stream Mining, Processing, DSMP 2020, Lviv, Ukraine, August 21-25, 2020: 231-236 (2020).</t>
+          <t xml:space="preserve"> IEEE Trans. Fuzzy Syst. 28: 1195-1204 (2020).</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula </t>
+          <t xml:space="preserve">Jan Hula, David Mojzísek, David Adamczyk, Radek Cech </t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unsupervised Object-aware Learning from Videos. </t>
+          <t xml:space="preserve"> Acquiring Custom OCR System with Minimal Manual Annotation. </t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -27649,24 +27649,24 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/DSMP47368.2020.9204219 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/DSMP47368.2020.9204229 </t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Third International Conference on Data Stream Mining, Processing, DSMP 2020, Lviv, Ukraine, August 21-25, 2020: 237-242 (2020).</t>
+          <t xml:space="preserve"> IEEE Third International Conference on Data Stream Mining, Processing, DSMP 2020, Lviv, Ukraine, August 21-25, 2020: 231-236 (2020).</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Adamczyk, Jan Hula </t>
+          <t xml:space="preserve">Jan Hula </t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Keypoints Selection Using Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> Unsupervised Object-aware Learning from Videos. </t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -27679,24 +27679,24 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://ceur-ws.org/Vol-2718/paper30.pdf </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/DSMP47368.2020.9204219 </t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 20th Conference Information Technologies - Applications and Theory (ITAT 2020), Hotel Tyrapol, Oravská Lesná, Slovakia, September 18-22, 2020.: 186-191 (2020).</t>
+          <t xml:space="preserve"> IEEE Third International Conference on Data Stream Mining, Processing, DSMP 2020, Lviv, Ukraine, August 21-25, 2020: 237-242 (2020).</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula, Marek Vajgl, Pavel Vlasánek, Tomas Nejezchleba </t>
+          <t xml:space="preserve">David Adamczyk, Jan Hula </t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Poly-YOLO: higher speed, more precise detection and instance segmentation for YOLOv3. </t>
+          <t xml:space="preserve"> Keypoints Selection Using Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -27709,28 +27709,28 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.13243 </t>
+          <t xml:space="preserve"> https://ceur-ws.org/Vol-2718/paper30.pdf </t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.13243 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 20th Conference Information Technologies - Applications and Theory (ITAT 2020), Hotel Tyrapol, Oravská Lesná, Slovakia, September 18-22, 2020.: 186-191 (2020).</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, Miroslav Kubát, Radek Cech, Xinying Chen, David Cíz, Katerina Pelegrinová, Jirí Milicka </t>
+          <t xml:space="preserve">Petr Hurtík, Vojtech Molek, Jan Hula, Marek Vajgl, Pavel Vlasánek, Tomas Nejezchleba </t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context Specificity of Lemma. Diachronic Analysis. </t>
+          <t xml:space="preserve"> Poly-YOLO: higher speed, more precise detection and instance segmentation for YOLOv3. </t>
         </is>
       </c>
       <c r="C911" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -27739,24 +27739,24 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.ram-verlag.eu/wp-content/uploads/2019/04/g45zeit-1.pdf </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.13243 </t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Glottometrics 45: 7-23 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.13243 (2020).</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radek Cech, Jan Hula, Miroslav Kubát, Xinying Chen, Jirí Milicka </t>
+          <t xml:space="preserve">Jan Hula, Miroslav Kubát, Radek Cech, Xinying Chen, David Cíz, Katerina Pelegrinová, Jirí Milicka </t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Development of Context Specificity of Lemma. A Word Embeddings Approach. </t>
+          <t xml:space="preserve"> Context Specificity of Lemma. Diachronic Analysis. </t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -27769,24 +27769,24 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q125022853 </t>
+          <t xml:space="preserve"> https://www.ram-verlag.eu/wp-content/uploads/2019/04/g45zeit-1.pdf </t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Quant. Linguistics 26: 187-204 (2019).</t>
+          <t xml:space="preserve"> Glottometrics 45: 7-23 (2019).</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alex Wang, Jan Hula, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen, Benjamin Van Durme, Edouard Grave, Ellie Pavlick, Samuel R. Bowman </t>
+          <t xml:space="preserve">Radek Cech, Jan Hula, Miroslav Kubát, Xinying Chen, Jirí Milicka </t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can You Tell Me How to Get Past Sesame Street? Sentence-Level Pretraining Beyond Language Modeling. </t>
+          <t xml:space="preserve"> The Development of Context Specificity of Lemma. A Word Embeddings Approach. </t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -27799,24 +27799,24 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/P19-1439/ </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q125022853 </t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 57th Conference of the Association for Computational Linguistics, ACL 2019, Florence, Italy, July 28- August 2, 2019, Volume 1: Long Papers: 4465-4476 (2019).</t>
+          <t xml:space="preserve"> J. Quant. Linguistics 26: 187-204 (2019).</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waren Long, Vadim Markovtsev, Hugo Mougard, Egor Bulychev, Jan Hula </t>
+          <t xml:space="preserve">Alex Wang, Jan Hula, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen, Benjamin Van Durme, Edouard Grave, Ellie Pavlick, Samuel R. Bowman </t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Identifying collaborators in large codebases. </t>
+          <t xml:space="preserve"> Can You Tell Me How to Get Past Sesame Street? Sentence-Level Pretraining Beyond Language Modeling. </t>
         </is>
       </c>
       <c r="C914" t="n">
@@ -27829,28 +27829,28 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1905.06782 </t>
+          <t xml:space="preserve"> https://aclanthology.org/P19-1439/ </t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1905.06782 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 57th Conference of the Association for Computational Linguistics, ACL 2019, Florence, Italy, July 28- August 2, 2019, Volume 1: Long Papers: 4465-4476 (2019).</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samuel R. Bowman, Ellie Pavlick, Edouard Grave, Benjamin Van Durme, Alex Wang, Jan Hula, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen </t>
+          <t xml:space="preserve">Waren Long, Vadim Markovtsev, Hugo Mougard, Egor Bulychev, Jan Hula </t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Looking for ELMo's friends: Sentence-Level Pretraining Beyond Language Modeling. </t>
+          <t xml:space="preserve"> Identifying collaborators in large codebases. </t>
         </is>
       </c>
       <c r="C915" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -27859,28 +27859,28 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1812.10860 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1905.06782 </t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1812.10860 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1905.06782 (2019).</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Hula, Irina Perfilieva, Ali Ahsan Muhummad Muzaheed </t>
+          <t xml:space="preserve">Samuel R. Bowman, Ellie Pavlick, Edouard Grave, Benjamin Van Durme, Alex Wang, Jan Hula, Patrick Xia, Raghavendra Pappagari, R. Thomas McCoy, Roma Patel, Najoung Kim, Ian Tenney, Yinghui Huang, Katherin Yu, Shuning Jin, Berlin Chen </t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Visual Training Set Generation Framework. </t>
+          <t xml:space="preserve"> Looking for ELMo's friends: Sentence-Level Pretraining Beyond Language Modeling. </t>
         </is>
       </c>
       <c r="C916" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -27889,58 +27889,58 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-59147-6_63 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1812.10860 </t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Computational Intelligence - 14th International Work-Conference on Artificial Neural Networks, IWANN 2017, Cadiz, Spain, June 14-16, 2017, Proceedings, Part II: 747-758 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1812.10860 (2018).</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Jan Hula, Irina Perfilieva, Ali Ahsan Muhummad Muzaheed </t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Wos Challenge Met. </t>
+          <t xml:space="preserve"> Towards Visual Training Set Generation Framework. </t>
         </is>
       </c>
       <c r="C917" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114264018 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-59147-6_63 </t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 66: 565-574 (2022).</t>
+          <t xml:space="preserve"> Advances in Computational Intelligence - 14th International Work-Conference on Artificial Neural Networks, IWANN 2017, Cadiz, Spain, June 14-16, 2017, Proceedings, Part II: 747-758 (2017).</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stepan Holub, Robert Veroff </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Formalizing a Fragment of Combinatorics on Words. </t>
+          <t xml:space="preserve"> A Wos Challenge Met. </t>
         </is>
       </c>
       <c r="C918" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -27949,28 +27949,28 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-58741-7_3 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114264018 </t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unveiling Dynamics and Complexity - 13th Conference on Computability in Europe, CiE 2017, Turku, Finland, June 12-16, 2017, Proceedings: 24-31 (2017).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 66: 565-574 (2022).</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Spinks, Robert J. Bignall, Robert Veroff </t>
+          <t xml:space="preserve">Stepan Holub, Robert Veroff </t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discriminator logics (Research announcement). </t>
+          <t xml:space="preserve"> Formalizing a Fragment of Combinatorics on Words. </t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -27979,28 +27979,28 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.26686/ajl.v11i2.2020 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-58741-7_3 </t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Australas. J. Log. 11: (2014).</t>
+          <t xml:space="preserve"> Unveiling Dynamics and Complexity - 13th Conference on Computability in Europe, CiE 2017, Turku, Finland, June 12-16, 2017, Proceedings: 24-31 (2017).</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranganathan Padmanabhan, Robert Veroff </t>
+          <t xml:space="preserve">Matthew Spinks, Robert J. Bignall, Robert Veroff </t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Geometric Procedure with Prover9. </t>
+          <t xml:space="preserve"> Discriminator logics (Research announcement). </t>
         </is>
       </c>
       <c r="C920" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -28009,24 +28009,24 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_7 </t>
+          <t xml:space="preserve"> https://doi.org/10.26686/ajl.v11i2.2020 </t>
         </is>
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 139-150 (2013).</t>
+          <t xml:space="preserve"> Australas. J. Log. 11: (2014).</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael K. Kinyon, Robert Veroff, Petr Vojtechovský </t>
+          <t xml:space="preserve">Ranganathan Padmanabhan, Robert Veroff </t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Loops with Abelian Inner Mapping Groups: An Application of Automated Deduction. </t>
+          <t xml:space="preserve"> A Geometric Procedure with Prover9. </t>
         </is>
       </c>
       <c r="C921" t="n">
@@ -28039,28 +28039,28 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_7 </t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 151-164 (2013).</t>
+          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 139-150 (2013).</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francesco Paoli, Matthew Spinks, Robert Veroff </t>
+          <t xml:space="preserve">Michael K. Kinyon, Robert Veroff, Petr Vojtechovský </t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abelian Logic and the Logics of Pointed Lattice-Ordered Varieties. </t>
+          <t xml:space="preserve"> Loops with Abelian Inner Mapping Groups: An Application of Automated Deduction. </t>
         </is>
       </c>
       <c r="C922" t="n">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -28069,24 +28069,24 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11787-008-0034-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_8 </t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logica Universalis 2: 209-233 (2008).</t>
+          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 151-164 (2013).</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
+          <t xml:space="preserve">Francesco Paoli, Matthew Spinks, Robert Veroff </t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. I. </t>
+          <t xml:space="preserve"> Abelian Logic and the Logics of Pointed Lattice-Ordered Varieties. </t>
         </is>
       </c>
       <c r="C923" t="n">
@@ -28099,12 +28099,12 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9113-x </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11787-008-0034-2 </t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 88: 325-348 (2008).</t>
+          <t xml:space="preserve"> Logica Universalis 2: 209-233 (2008).</t>
         </is>
       </c>
     </row>
@@ -28116,7 +28116,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. II. </t>
+          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. I. </t>
         </is>
       </c>
       <c r="C924" t="n">
@@ -28129,28 +28129,28 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9138-1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9113-x </t>
         </is>
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 89: 401-425 (2008).</t>
+          <t xml:space="preserve"> Stud Logica 88: 325-348 (2008).</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Gilfeather, Vikas Hamine, Paul Helman, Julie Hutt, Terry Loring, C. Rick Lyons, Robert Veroff </t>
+          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learning and modeling biosignatures from tissue images. </t>
+          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. II. </t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -28159,28 +28159,28 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33282059 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9138-1 </t>
         </is>
       </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Biol. Medicine 37: 1539-1552 (2007).</t>
+          <t xml:space="preserve"> Stud Logica 89: 401-425 (2008).</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff, Matthew Spinks </t>
+          <t xml:space="preserve">Frank Gilfeather, Vikas Hamine, Paul Helman, Julie Hutt, Terry Loring, C. Rick Lyons, Robert Veroff </t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Axiomatizing the Skew Boolean Propositional Calculus. </t>
+          <t xml:space="preserve"> Learning and modeling biosignatures from tissue images. </t>
         </is>
       </c>
       <c r="C926" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -28189,28 +28189,28 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-006-9029-y </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33282059 </t>
         </is>
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 37: 3-20 (2006).</t>
+          <t xml:space="preserve"> Comput. Biol. Medicine 37: 1539-1552 (2007).</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
+          <t xml:space="preserve">Robert Veroff, Matthew Spinks </t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics. </t>
+          <t xml:space="preserve"> Axiomatizing the Skew Boolean Propositional Calculus. </t>
         </is>
       </c>
       <c r="C927" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -28219,28 +28219,28 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262834 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-006-9029-y </t>
         </is>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 80: 195-234 (2005).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 37: 3-20 (2006).</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff, Susan R. Atlas, Cheryl Willman </t>
+          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Bayesian Network Classification Methodology for Gene Expression Data. </t>
+          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics. </t>
         </is>
       </c>
       <c r="C928" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -28249,28 +28249,28 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33209551 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262834 </t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Comput. Biol. 11: 581-615 (2004).</t>
+          <t xml:space="preserve"> Stud Logica 80: 195-234 (2005).</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff, Susan R. Atlas, Cheryl Willman </t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Shortest 2-Basis for Boolean Algebra in Terms of the Sheffer Stroke. </t>
+          <t xml:space="preserve"> A Bayesian Network Classification Methodology for Gene Expression Data. </t>
         </is>
       </c>
       <c r="C929" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -28279,24 +28279,24 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1027322305654 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33209551 </t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 31: 1-9 (2003).</t>
+          <t xml:space="preserve"> J. Comput. Biol. 11: 581-615 (2004).</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics </t>
+          <t xml:space="preserve"> A Shortest 2-Basis for Boolean Algebra in Terms of the Sheffer Stroke. </t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -28309,28 +28309,28 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/cs/0301026 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1027322305654 </t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR cs.LO/0301026 (2003).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 31: 1-9 (2003).</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t xml:space="preserve">William McCune, Robert Veroff, Branden Fitelson, Kenneth Harris, Andrew Feist, Larry Wos </t>
+          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Single Axioms for Boolean Algebra. </t>
+          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics </t>
         </is>
       </c>
       <c r="C931" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -28339,28 +28339,28 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q60061107 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/cs/0301026 </t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 29: 1-16 (2002).</t>
+          <t xml:space="preserve"> arXiv CoRR cs.LO/0301026 (2003).</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
+          <t xml:space="preserve">William McCune, Robert Veroff, Branden Fitelson, Kenneth Harris, Andrew Feist, Larry Wos </t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The application of automated reasoning to formal models of combinatorial optimization. </t>
+          <t xml:space="preserve"> Short Single Axioms for Boolean Algebra. </t>
         </is>
       </c>
       <c r="C932" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -28369,24 +28369,24 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q127517130 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q60061107 </t>
         </is>
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Math. Comput. 120: 175-194 (2001).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 29: 1-16 (2002).</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Finding Shortest Proofs: An Application of Linked Inference Rules. </t>
+          <t xml:space="preserve"> The application of automated reasoning to formal models of combinatorial optimization. </t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -28399,12 +28399,12 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1010635625063 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q127517130 </t>
         </is>
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 27: 123-139 (2001).</t>
+          <t xml:space="preserve"> Appl. Math. Comput. 120: 175-194 (2001).</t>
         </is>
       </c>
     </row>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving Open Questions and Other Challenge Problems Using Proof Sketches. </t>
+          <t xml:space="preserve"> Finding Shortest Proofs: An Application of Linked Inference Rules. </t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -28429,28 +28429,28 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1010639725972 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1010635625063 </t>
         </is>
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 27: 157-174 (2001).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 27: 123-139 (2001).</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gregory H. Chisholm, Steven T. Eckmann, Christopher M. Lain, Robert Veroff </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Integrated Circuits. </t>
+          <t xml:space="preserve"> Solving Open Questions and Other Challenge Problems Using Proof Sketches. </t>
         </is>
       </c>
       <c r="C935" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -28459,28 +28459,28 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://doi.ieeecomputersociety.org/10.1109/54.765201 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1010639725972 </t>
         </is>
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Des. Test Comput. 16: 26-37 (1999).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 27: 157-174 (2001).</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Gregory H. Chisholm, Steven T. Eckmann, Christopher M. Lain, Robert Veroff </t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Using Hints to Increase the Effectiveness of an Automated Reasoning Program: Case Studies. </t>
+          <t xml:space="preserve"> Understanding Integrated Circuits. </t>
         </is>
       </c>
       <c r="C936" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -28489,28 +28489,28 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/BF00252178 </t>
+          <t xml:space="preserve"> http://doi.ieeecomputersociety.org/10.1109/54.765201 </t>
         </is>
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 16: 223-239 (1996).</t>
+          <t xml:space="preserve"> IEEE Des. Test Comput. 16: 26-37 (1999).</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Robert Veroff </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logical basis for the automation of reasoning: Case studies. </t>
+          <t xml:space="preserve"> Using Hints to Increase the Effectiveness of an Automated Reasoning Program: Case Studies. </t>
         </is>
       </c>
       <c r="C937" t="n">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -28519,28 +28519,28 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/BF00252178 </t>
         </is>
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Handbook of Logic in Artificial Intelligence and Logic Programming, Volume2, Deduction Methodologies: 1-40 (1994).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 16: 223-239 (1996).</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Larry Wos, Robert Veroff </t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Linked Inference Principle, I: The Formal Treatment. </t>
+          <t xml:space="preserve"> Logical basis for the automation of reasoning: Case studies. </t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -28549,28 +28549,28 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114267080 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 8: 213-274 (1992).</t>
+          <t xml:space="preserve"> Handbook of Logic in Artificial Intelligence and Logic Programming, Volume2, Deduction Methodologies: 1-40 (1994).</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff, Frank R. Carrano </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intermediate problem solving and data structures - walls and mirrors (2. ed.). </t>
+          <t xml:space="preserve"> The Linked Inference Principle, I: The Formal Treatment. </t>
         </is>
       </c>
       <c r="C939" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -28579,28 +28579,28 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114267080 </t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Benjamin/Cummings series in computer science, Benjamin/Cummings (1991).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 8: 213-274 (1992).</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff, Frank R. Carrano </t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Designing Deductive Databases. </t>
+          <t xml:space="preserve"> Intermediate problem solving and data structures - walls and mirrors (2. ed.). </t>
         </is>
       </c>
       <c r="C940" t="n">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -28609,28 +28609,28 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/BF00244512 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 4: 29-68 (1988).</t>
+          <t xml:space="preserve"> Benjamin/Cummings series in computer science, Benjamin/Cummings (1991).</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Steve Winker, Barry Smith, Robert Veroff, Lawrence J. Henschen </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A New Use of an Automated Reasoning Assistant: Open Questions in Equivalential Calculus and the Study of Infinite Domains. </t>
+          <t xml:space="preserve"> Designing Deductive Databases. </t>
         </is>
       </c>
       <c r="C941" t="n">
-        <v>1984</v>
+        <v>1988</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -28639,24 +28639,24 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262293 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/BF00244512 </t>
         </is>
       </c>
       <c r="F941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. 22: 303-356 (1984).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 4: 29-68 (1988).</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Robert Veroff, Barry Smith, William McCune </t>
+          <t xml:space="preserve">Larry Wos, Steve Winker, Barry Smith, Robert Veroff, Lawrence J. Henschen </t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Linked Inference Principle, II: The User's Viewpoint. </t>
+          <t xml:space="preserve"> A New Use of an Automated Reasoning Assistant: Open Questions in Equivalential Calculus and the Study of Infinite Domains. </t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -28669,28 +28669,28 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-0-387-34768-4_19 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262293 </t>
         </is>
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7th International Conference on Automated Deduction, Napa, California, USA, May 14-16, 1984, Proceedings: 316-332 (1984).</t>
+          <t xml:space="preserve"> Artif. Intell. 22: 303-356 (1984).</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Henschen, Barry Smith, Robert Veroff, Steve Winker, Larry Wos </t>
+          <t xml:space="preserve">Larry Wos, Robert Veroff, Barry Smith, William McCune </t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Questions concerning possible shortest single axioms for the equivalential calculus: an application of automated theorem proving to infinite domains. </t>
+          <t xml:space="preserve"> The Linked Inference Principle, II: The User's Viewpoint. </t>
         </is>
       </c>
       <c r="C943" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -28699,28 +28699,28 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114254310 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-0-387-34768-4_19 </t>
         </is>
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Notre Dame J. Formal Log. 24: 205-223 (1983).</t>
+          <t xml:space="preserve"> 7th International Conference on Automated Deduction, Napa, California, USA, May 14-16, 1984, Proceedings: 316-332 (1984).</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff, Lawrence J. Henschen </t>
+          <t xml:space="preserve">Larry Henschen, Barry Smith, Robert Veroff, Steve Winker, Larry Wos </t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Automatic Transformations to Program Verification. </t>
+          <t xml:space="preserve"> Questions concerning possible shortest single axioms for the equivalential calculus: an application of automated theorem proving to infinite domains. </t>
         </is>
       </c>
       <c r="C944" t="n">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -28729,28 +28729,28 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://ijcai.org/Proceedings/81-1/Papers/087.pdf </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114254310 </t>
         </is>
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 7th International Joint Conference on Artificial Intelligence, IJCAI '81, Vancouver, BC, Canada, August 24-28, 1981: 472-479 (1981).</t>
+          <t xml:space="preserve"> Notre Dame J. Formal Log. 24: 205-223 (1983).</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Robert Veroff, Lawrence J. Henschen </t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
+          <t xml:space="preserve"> Application of Automatic Transformations to Program Verification. </t>
         </is>
       </c>
       <c r="C945" t="n">
-        <v>2024</v>
+        <v>1981</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -28759,24 +28759,24 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
+          <t xml:space="preserve"> http://ijcai.org/Proceedings/81-1/Papers/087.pdf </t>
         </is>
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
+          <t xml:space="preserve"> Proceedings of the 7th International Joint Conference on Artificial Intelligence, IJCAI '81, Vancouver, BC, Canada, August 24-28, 1981: 472-479 (1981).</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -28784,29 +28784,29 @@
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
         </is>
       </c>
       <c r="F946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
+          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
+          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -28814,29 +28814,29 @@
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
         </is>
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
+          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -28844,29 +28844,29 @@
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
         </is>
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek </t>
+          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
+          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
         </is>
       </c>
       <c r="C949" t="n">
@@ -28874,29 +28874,29 @@
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
         </is>
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
+          <t xml:space="preserve">Lasse Blaauwbroek </t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beneficial AGI: Care and Collaboration Are All You Need. </t>
+          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -28909,28 +28909,28 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-65572-2_9 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
         </is>
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial General Intelligence - 17th International Conference, AGI 2024, Seattle, WA, USA, August 13-16, 2024, Proceedings: 84-88 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sergey Rodionov, Zarathustra Amadeus Goertzel, Ben Goertzel </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Evaluation of GPT-4 on the ETHICS Dataset. </t>
+          <t xml:space="preserve"> Beneficial AGI: Care and Collaboration Are All You Need. </t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -28939,24 +28939,24 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2309.10492 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-65572-2_9 </t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2309.10492 (2023).</t>
+          <t xml:space="preserve"> Artificial General Intelligence - 17th International Conference, AGI 2024, Seattle, WA, USA, August 13-16, 2024, Proceedings: 84-88 (2024).</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ben Goertzel, Vitaly Bogdanov, Michael Duncan, Deborah Duong, Zarathustra Amadeus Goertzel, Jan Horlings, Matthew Iklé, Lucius Gregory Meredith, Alexey Potapov, Andre Luiz de Senna, Hedra Seid, Andres Suarez, Adam Vandervorst, Robert Werko </t>
+          <t xml:space="preserve">Sergey Rodionov, Zarathustra Amadeus Goertzel, Ben Goertzel </t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OpenCog Hyperon: A Framework for AGI at the Human Level and Beyond. </t>
+          <t xml:space="preserve"> An Evaluation of GPT-4 on the ETHICS Dataset. </t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -28969,28 +28969,28 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2310.18318 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2309.10492 </t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2310.18318 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2309.10492 (2023).</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
+          <t xml:space="preserve">Ben Goertzel, Vitaly Bogdanov, Michael Duncan, Deborah Duong, Zarathustra Amadeus Goertzel, Jan Horlings, Matthew Iklé, Lucius Gregory Meredith, Alexey Potapov, Andre Luiz de Senna, Hedra Seid, Andres Suarez, Adam Vandervorst, Robert Werko </t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Make E Smart Again (Short Paper). </t>
+          <t xml:space="preserve"> OpenCog Hyperon: A Framework for AGI at the Human Level and Beyond. </t>
         </is>
       </c>
       <c r="C953" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -28999,12 +28999,12 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51054-1_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2310.18318 </t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part II: 408-415 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2310.18318 (2023).</t>
         </is>
       </c>
     </row>
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Make E Smart Again. </t>
+          <t xml:space="preserve"> Make E Smart Again (Short Paper). </t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -29029,28 +29029,28 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.08858 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51054-1_26 </t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2004.08858 (2020).</t>
+          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part II: 408-415 (2020).</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Make E Smart Again. </t>
         </is>
       </c>
       <c r="C955" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -29059,12 +29059,12 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2004.08858 </t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2004.08858 (2020).</t>
         </is>
       </c>
     </row>
@@ -29076,11 +29076,11 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
+          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C956" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -29089,12 +29089,12 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
         </is>
       </c>
     </row>
@@ -29106,7 +29106,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -29119,12 +29119,12 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
+          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
         </is>
       </c>
     </row>
@@ -29136,7 +29136,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C958" t="n">
@@ -29149,12 +29149,12 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
         </is>
       </c>
     </row>
@@ -29166,7 +29166,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -29179,12 +29179,12 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
         </is>
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
         </is>
       </c>
     </row>
@@ -29196,7 +29196,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -29209,12 +29209,12 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
         </is>
       </c>
     </row>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
+          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -29239,12 +29239,12 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
         </is>
       </c>
     </row>
@@ -29256,7 +29256,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -29269,12 +29269,12 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
         </is>
       </c>
     </row>
@@ -29286,11 +29286,11 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C963" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -29299,12 +29299,12 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -29329,12 +29329,12 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
+          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
         </is>
       </c>
     </row>
@@ -29346,7 +29346,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -29359,12 +29359,12 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
         </is>
       </c>
     </row>
@@ -29376,7 +29376,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -29389,12 +29389,12 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Designing Game of Theorems. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C967" t="n">
@@ -29419,12 +29419,12 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
         </is>
       </c>
     </row>
@@ -29436,7 +29436,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
+          <t xml:space="preserve"> Designing Game of Theorems. </t>
         </is>
       </c>
       <c r="C968" t="n">
@@ -29449,28 +29449,28 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
         </is>
       </c>
       <c r="C969" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -29479,24 +29479,24 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
+          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -29509,12 +29509,12 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
+          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
         </is>
       </c>
     </row>
@@ -29539,24 +29539,24 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -29569,24 +29569,24 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
         </is>
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
+          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -29599,28 +29599,28 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -29629,24 +29629,24 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -29659,12 +29659,12 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
         </is>
       </c>
     </row>
@@ -29676,11 +29676,11 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Strategy Language. </t>
+          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -29689,24 +29689,24 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
+          <t xml:space="preserve"> Proof Strategy Language. </t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -29719,24 +29719,24 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
+          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
+          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -29749,24 +29749,24 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
+          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
+          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -29779,24 +29779,24 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
+          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
+          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -29809,24 +29809,24 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
+          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
+          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -29839,24 +29839,24 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
         </is>
       </c>
       <c r="C982" t="n">
@@ -29869,54 +29869,54 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
+          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
+          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
         </is>
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
+          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -29929,19 +29929,19 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -29959,28 +29959,28 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
         </is>
       </c>
       <c r="C986" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -29989,24 +29989,24 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -30019,24 +30019,24 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
+          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
         </is>
       </c>
       <c r="C988" t="n">
@@ -30049,28 +30049,28 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C989" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -30079,28 +30079,28 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
+          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
+          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -30109,24 +30109,24 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
+          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
+          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
+          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -30139,28 +30139,28 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
+          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
+          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C992" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -30169,24 +30169,24 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
+          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C993" t="n">
@@ -30199,24 +30199,24 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
+          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -30229,12 +30229,12 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
         </is>
       </c>
     </row>
@@ -30246,7 +30246,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -30259,24 +30259,24 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
+          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -30289,28 +30289,28 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
+          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -30319,24 +30319,24 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -30349,19 +30349,19 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
+          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -30379,24 +30379,24 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2025/08)</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1000" t="n">
@@ -30409,24 +30409,24 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
+          <t xml:space="preserve"> Zenodo (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C1001" t="n">
@@ -30439,24 +30439,24 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -30464,29 +30464,29 @@
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FAI </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
+          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
+          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
         </is>
       </c>
       <c r="C1003" t="n">
@@ -30499,28 +30499,28 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
+          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
+          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -30529,24 +30529,24 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
+          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
+          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -30559,12 +30559,12 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
+          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
+          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
         </is>
       </c>
     </row>
@@ -30576,11 +30576,11 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
+          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -30589,54 +30589,54 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
+          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
+          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
+          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ML </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
+          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
+          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -30649,28 +30649,28 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
+          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
+          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -30679,28 +30679,28 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
         </is>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
+          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
+          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -30709,24 +30709,24 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
+          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -30739,28 +30739,28 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
+          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -30769,24 +30769,24 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
         </is>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
+          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
         </is>
       </c>
       <c r="C1013" t="n">
@@ -30799,7 +30799,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
@@ -30811,16 +30811,16 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
+          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -30829,28 +30829,28 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
         </is>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
+          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
+          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
         </is>
       </c>
     </row>
@@ -30880,7 +30880,7 @@
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -30889,24 +30889,24 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sensors 19: (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
+          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
         </is>
       </c>
       <c r="C1017" t="n">
@@ -30919,28 +30919,28 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
+          <t xml:space="preserve"> Sensors 19: (2019).</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
+          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -30949,28 +30949,28 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
+          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
+          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
+          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -30979,24 +30979,24 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
+          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
+          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
         </is>
       </c>
       <c r="C1020" t="n">
@@ -31009,28 +31009,28 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
+          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
+          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -31039,24 +31039,24 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
+          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
+          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
         </is>
       </c>
       <c r="C1022" t="n">
@@ -31069,24 +31069,24 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
+          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
+          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -31099,28 +31099,28 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
         </is>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
+          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -31129,24 +31129,24 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
+          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
+          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -31159,24 +31159,24 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
         </is>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
+          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
+          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
+          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -31189,24 +31189,24 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
         </is>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
+          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
+          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -31219,28 +31219,28 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
         </is>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
+          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -31249,24 +31249,24 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1029" t="n">
@@ -31279,24 +31279,24 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
         </is>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
+          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
+          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
         </is>
       </c>
       <c r="C1030" t="n">
@@ -31309,24 +31309,24 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
+          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
+          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -31339,28 +31339,28 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
+          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
+          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1032" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -31369,24 +31369,24 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
         </is>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
+          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
+          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
         </is>
       </c>
       <c r="C1033" t="n">
@@ -31399,24 +31399,24 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
         </is>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
+          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -31429,24 +31429,24 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -31459,24 +31459,24 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -31489,24 +31489,24 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
         </is>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
+          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -31519,24 +31519,24 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -31549,28 +31549,28 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
         </is>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -31579,12 +31579,12 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
         </is>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
         </is>
       </c>
     </row>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
+          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -31609,12 +31609,12 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
         </is>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
         </is>
       </c>
     </row>
@@ -31626,7 +31626,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -31639,24 +31639,24 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
         </is>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
+          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -31669,28 +31669,28 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
         </is>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
+          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
         </is>
       </c>
       <c r="C1043" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -31699,28 +31699,28 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
         </is>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
+          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -31729,28 +31729,28 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
         </is>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -31759,24 +31759,24 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
         </is>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
+          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1046" t="n">
@@ -31789,24 +31789,24 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
         </is>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
+          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
+          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -31819,28 +31819,28 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
+          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
+          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
         </is>
       </c>
       <c r="C1048" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -31849,24 +31849,24 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
         </is>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
+          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
+          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -31879,28 +31879,28 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
         </is>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
+          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
+          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
+          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
         </is>
       </c>
       <c r="C1050" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -31909,24 +31909,24 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
         </is>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
+          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
         </is>
       </c>
       <c r="C1051" t="n">
@@ -31939,24 +31939,24 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
         </is>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
+          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
+          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
+          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -31969,28 +31969,28 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
         </is>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
+          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
         </is>
       </c>
       <c r="C1053" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -31999,28 +31999,28 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
+          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -32029,24 +32029,24 @@
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
         </is>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
+          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
+          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -32059,24 +32059,24 @@
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
         </is>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
+          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
+          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -32094,23 +32094,23 @@
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
+          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
         </is>
       </c>
       <c r="C1057" t="n">
-        <v>2025</v>
+        <v>2002</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -32119,28 +32119,28 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -32149,12 +32149,12 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
@@ -32179,28 +32179,28 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -32209,28 +32209,28 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -32239,24 +32239,24 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -32269,24 +32269,24 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -32299,28 +32299,28 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -32329,24 +32329,24 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -32359,24 +32359,24 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -32389,24 +32389,24 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -32419,24 +32419,24 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -32449,24 +32449,24 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -32479,24 +32479,24 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -32509,28 +32509,28 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -32539,24 +32539,24 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1072" t="n">
@@ -32569,24 +32569,24 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -32599,24 +32599,24 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1074" t="n">
@@ -32629,24 +32629,24 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -32659,24 +32659,24 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -32689,28 +32689,28 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -32719,24 +32719,24 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1078" t="n">
@@ -32749,24 +32749,24 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -32779,28 +32779,28 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -32809,28 +32809,28 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -32839,28 +32839,28 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -32869,24 +32869,24 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1083" t="n">
@@ -32899,24 +32899,24 @@
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1084" t="n">
@@ -32929,28 +32929,28 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -32959,12 +32959,12 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
@@ -32976,7 +32976,7 @@
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1086" t="n">
@@ -32989,28 +32989,28 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -33019,12 +33019,12 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
@@ -33036,7 +33036,7 @@
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -33049,24 +33049,24 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -33079,24 +33079,24 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -33109,28 +33109,28 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -33139,28 +33139,28 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -33169,12 +33169,12 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
@@ -33186,11 +33186,11 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -33199,24 +33199,24 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -33229,28 +33229,28 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -33259,24 +33259,24 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -33289,28 +33289,28 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -33319,28 +33319,28 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -33349,28 +33349,28 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -33379,24 +33379,24 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1100" t="n">
@@ -33409,24 +33409,24 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -33439,24 +33439,24 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -33469,28 +33469,28 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -33499,24 +33499,24 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -33529,7 +33529,7 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
@@ -33541,12 +33541,12 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -33559,24 +33559,24 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -33589,24 +33589,24 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -33619,24 +33619,24 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -33649,28 +33649,28 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
@@ -33679,12 +33679,12 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -33709,28 +33709,28 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
@@ -33739,24 +33739,24 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -33769,28 +33769,28 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
@@ -33799,40 +33799,70 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1114" t="inlineStr">
+      <c r="B1115" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1114" t="n">
+      <c r="C1115" t="n">
         <v>2021</v>
       </c>
-      <c r="D1114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1114" t="inlineStr">
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1114" t="inlineStr">
+      <c r="F1115" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1115"/>
+  <dimension ref="A1:F1117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32131,16 +32131,16 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -32149,28 +32149,28 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -32179,28 +32179,28 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -32209,28 +32209,28 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -32239,28 +32239,28 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1062" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -32269,28 +32269,28 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1063" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -32299,24 +32299,24 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1064" t="n">
@@ -32329,28 +32329,28 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1065" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -32359,28 +32359,28 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1066" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -32389,24 +32389,24 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -32419,24 +32419,24 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -32449,24 +32449,24 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -32479,24 +32479,24 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -32509,24 +32509,24 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1071" t="n">
@@ -32539,28 +32539,28 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -32569,28 +32569,28 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1073" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -32599,24 +32599,24 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1074" t="n">
@@ -32629,24 +32629,24 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -32659,24 +32659,24 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -32689,24 +32689,24 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -32719,28 +32719,28 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -32749,28 +32749,28 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -32779,24 +32779,24 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1080" t="n">
@@ -32809,28 +32809,28 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1081" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -32839,28 +32839,28 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -32869,28 +32869,28 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -32899,28 +32899,28 @@
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -32929,24 +32929,24 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1085" t="n">
@@ -32959,28 +32959,28 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -32989,28 +32989,28 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -33019,28 +33019,28 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -33049,28 +33049,28 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -33079,24 +33079,24 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -33109,24 +33109,24 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1091" t="n">
@@ -33139,28 +33139,28 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -33169,28 +33169,28 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -33199,28 +33199,28 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -33229,28 +33229,28 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -33259,28 +33259,28 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -33289,28 +33289,28 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -33319,28 +33319,28 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -33349,28 +33349,28 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -33379,28 +33379,28 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -33409,28 +33409,28 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -33439,24 +33439,24 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -33469,24 +33469,24 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1103" t="n">
@@ -33499,28 +33499,28 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -33529,28 +33529,28 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -33559,12 +33559,12 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
@@ -33589,24 +33589,24 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -33619,24 +33619,24 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -33649,24 +33649,24 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -33679,28 +33679,28 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
@@ -33709,28 +33709,28 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
@@ -33739,28 +33739,28 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1112" t="inlineStr">
         <is>
@@ -33769,28 +33769,28 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
@@ -33799,28 +33799,28 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
@@ -33829,24 +33829,24 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eduard Alibekov </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1115" t="n">
@@ -33859,10 +33859,70 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eduard Alibekov </t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1115" t="inlineStr">
+      <c r="F1117" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1117"/>
+  <dimension ref="A1:F1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30481,16 +30481,16 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
+          <t xml:space="preserve">Barbora Hudcová, Frantisek Dusek, Marco Tuccio, Clément Hongler </t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
+          <t xml:space="preserve"> Visualizing the Structure of Lenia Parameter Space. </t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -30499,24 +30499,24 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2601.01932 </t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2601.01932 (2026/01).</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
+          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
+          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -30529,28 +30529,28 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
+          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
+          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -30559,24 +30559,24 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
+          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
+          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -30589,12 +30589,12 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
+          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
+          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
         </is>
       </c>
     </row>
@@ -30606,11 +30606,11 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
+          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -30619,54 +30619,54 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
+          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
+          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
+          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ML </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
+          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
+          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -30679,28 +30679,28 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
         </is>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
+          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
+          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -30709,28 +30709,28 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
+          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
+          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -30739,24 +30739,24 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
+          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
         </is>
       </c>
       <c r="C1012" t="n">
@@ -30769,28 +30769,28 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
         </is>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
+          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -30799,24 +30799,24 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
+          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -30829,7 +30829,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
         </is>
       </c>
       <c r="F1014" t="inlineStr">
@@ -30841,16 +30841,16 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
+          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -30859,28 +30859,28 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
+          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
+          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -30889,12 +30889,12 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
         </is>
       </c>
     </row>
@@ -30910,7 +30910,7 @@
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -30919,24 +30919,24 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sensors 19: (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
+          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -30949,28 +30949,28 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
+          <t xml:space="preserve"> Sensors 19: (2019).</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
+          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -30979,28 +30979,28 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
+          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
+          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
+          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -31009,24 +31009,24 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
+          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
+          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
         </is>
       </c>
       <c r="C1021" t="n">
@@ -31039,28 +31039,28 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
+          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
+          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -31069,24 +31069,24 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
+          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
+          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -31099,24 +31099,24 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
         </is>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
+          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
+          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -31129,28 +31129,28 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
+          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
         </is>
       </c>
       <c r="C1025" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -31159,24 +31159,24 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
         </is>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
+          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
+          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -31189,24 +31189,24 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
         </is>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
+          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
+          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
+          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -31219,24 +31219,24 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
         </is>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
+          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
+          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -31249,28 +31249,28 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
+          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -31279,24 +31279,24 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
         </is>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1030" t="n">
@@ -31309,24 +31309,24 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
+          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
+          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -31339,24 +31339,24 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
+          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
+          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
         </is>
       </c>
       <c r="C1032" t="n">
@@ -31369,28 +31369,28 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
         </is>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
+          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
+          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1033" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -31399,24 +31399,24 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
         </is>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
+          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
+          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -31429,24 +31429,24 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
+          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -31459,24 +31459,24 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -31489,24 +31489,24 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
         </is>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -31519,24 +31519,24 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
+          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -31549,24 +31549,24 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
         </is>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -31579,28 +31579,28 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
         </is>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -31609,12 +31609,12 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
         </is>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
         </is>
       </c>
     </row>
@@ -31626,7 +31626,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
+          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -31639,12 +31639,12 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
         </is>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31656,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -31669,24 +31669,24 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
         </is>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
+          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1043" t="n">
@@ -31699,28 +31699,28 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
         </is>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
+          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -31729,28 +31729,28 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
         </is>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
+          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -31759,28 +31759,28 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
         </is>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1046" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -31789,24 +31789,24 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
         </is>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
+          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -31819,24 +31819,24 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
+          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
+          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -31849,28 +31849,28 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
         </is>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
+          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
+          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
         </is>
       </c>
       <c r="C1049" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -31879,24 +31879,24 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
         </is>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
+          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
+          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
         </is>
       </c>
       <c r="C1050" t="n">
@@ -31909,28 +31909,28 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
         </is>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
+          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
+          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
+          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
         </is>
       </c>
       <c r="C1051" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -31939,24 +31939,24 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
         </is>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
+          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -31969,24 +31969,24 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
         </is>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
+          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
+          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
+          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -31999,28 +31999,28 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
+          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
         </is>
       </c>
       <c r="C1054" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -32029,28 +32029,28 @@
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
         </is>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
+          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
         </is>
       </c>
       <c r="C1055" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -32059,24 +32059,24 @@
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
         </is>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
+          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
+          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -32089,24 +32089,24 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
         </is>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
+          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
+          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -32124,23 +32124,23 @@
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
+          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
+          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
+          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>2026</v>
+        <v>2002</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -32149,12 +32149,12 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
+          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
         </is>
       </c>
     </row>
@@ -32166,7 +32166,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
         </is>
       </c>
       <c r="C1059" t="n">
@@ -32179,28 +32179,28 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
         </is>
       </c>
       <c r="C1060" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -32209,28 +32209,28 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -32239,12 +32239,12 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
@@ -32269,28 +32269,28 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1063" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -32299,28 +32299,28 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -32329,24 +32329,24 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -32359,24 +32359,24 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -32389,28 +32389,28 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1067" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -32419,24 +32419,24 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -32449,24 +32449,24 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -32479,24 +32479,24 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -32509,24 +32509,24 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1071" t="n">
@@ -32539,24 +32539,24 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1072" t="n">
@@ -32569,24 +32569,24 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -32599,28 +32599,28 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -32629,24 +32629,24 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -32659,24 +32659,24 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -32689,24 +32689,24 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -32719,24 +32719,24 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1078" t="n">
@@ -32749,24 +32749,24 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -32779,28 +32779,28 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -32809,24 +32809,24 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -32839,24 +32839,24 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1082" t="n">
@@ -32869,28 +32869,28 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -32899,28 +32899,28 @@
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1084" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -32929,28 +32929,28 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -32959,24 +32959,24 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1086" t="n">
@@ -32989,24 +32989,24 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1087" t="n">
@@ -33019,28 +33019,28 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -33049,12 +33049,12 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
@@ -33066,7 +33066,7 @@
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -33079,28 +33079,28 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -33109,12 +33109,12 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
@@ -33126,7 +33126,7 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1091" t="n">
@@ -33139,24 +33139,24 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1092" t="n">
@@ -33169,24 +33169,24 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1093" t="n">
@@ -33199,28 +33199,28 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -33229,28 +33229,28 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -33259,12 +33259,12 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
@@ -33276,11 +33276,11 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -33289,24 +33289,24 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1097" t="n">
@@ -33319,28 +33319,28 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -33349,24 +33349,24 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -33379,28 +33379,28 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -33409,28 +33409,28 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -33439,28 +33439,28 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1102" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -33469,24 +33469,24 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1103" t="n">
@@ -33499,24 +33499,24 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -33529,24 +33529,24 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -33559,28 +33559,28 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -33589,24 +33589,24 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
@@ -33631,12 +33631,12 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -33649,24 +33649,24 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -33679,24 +33679,24 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1110" t="n">
@@ -33709,24 +33709,24 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -33739,28 +33739,28 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1112" t="inlineStr">
         <is>
@@ -33769,12 +33769,12 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -33799,28 +33799,28 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
@@ -33829,24 +33829,24 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1115" t="n">
@@ -33859,28 +33859,28 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
@@ -33889,40 +33889,70 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1117" t="inlineStr">
+      <c r="B1118" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1117" t="n">
+      <c r="C1118" t="n">
         <v>2021</v>
       </c>
-      <c r="D1117" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1117" t="inlineStr">
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1117" t="inlineStr">
+      <c r="F1118" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FAI, FM </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E541" t="inlineStr">

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -25471,196 +25471,196 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Niederhauser, Chad E. Brown, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Karel Chvalovský </t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableaux for Automated Reasoning in Dependently-Typed Higher-Order Logic. </t>
+          <t xml:space="preserve"> Top-Down Neural Model For Formulae. </t>
         </is>
       </c>
       <c r="C836" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-63498-7_6 </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=Byg5QhR5FQ </t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 12th International Joint Conference, IJCAR 2024, Nancy, France, July 3-6, 2024, Proceedings, Part I: 86-104 (2024).</t>
+          <t xml:space="preserve"> 7th International Conference on Learning Representations, ICLR 2019, New Orleans, LA, USA, May 6-9, 2019: (2019).</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown </t>
+          <t xml:space="preserve">Karel Chvalovský, Rostislav Horcík </t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Formal Proof of R(4, 5)=25. </t>
+          <t xml:space="preserve"> Full Lambek Calculus with Contraction is Undecidable. </t>
         </is>
       </c>
       <c r="C837" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ITP.2024.16 </t>
+          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2015.18 </t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15th International Conference on Interactive Theorem Proving, ITP 2024, Tbilisi, Georgia, September 9-14, 2024: 16:1-16:18 (2024).</t>
+          <t xml:space="preserve"> J. Symb. Log. 81: 524-540 (2016).</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Ranalter, Chad E. Brown, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Karel Chvalovský </t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experiments with Choice in Dependently-Typed Higher-Order Logic. </t>
+          <t xml:space="preserve"> Undecidability of Consequence Relation in Full non-Associative Lambek Calculus. </t>
         </is>
       </c>
       <c r="C838" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/2v8h </t>
+          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2014.39 </t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LPAR 2024: Proceedings of 25th Conference on Logic for Programming, Artificial Intelligence and Reasoning, Port Louis, Mauritius, May 26-31, 2024: 311-320 (2024).</t>
+          <t xml:space="preserve"> J. Symb. Log. 80: 567-586 (2015).</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown </t>
+          <t xml:space="preserve">Karel Chvalovský </t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Formal Proof of R(4, 5)=25. </t>
+          <t xml:space="preserve"> On the independence of axioms in BL and MTL. </t>
         </is>
       </c>
       <c r="C839" t="n">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2404.01761 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.fss.2011.10.018 </t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2404.01761 (2024).</t>
+          <t xml:space="preserve"> Fuzzy Sets Syst. 197: 123-129 (2012).</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Ranalter, Chad E. Brown, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Karel Chvalovský, Petr Cintula </t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experiments with Choice in Dependently-Typed Higher-Order Logic. </t>
+          <t xml:space="preserve"> Note on Deduction Theorems in contraction-free logics. </t>
         </is>
       </c>
       <c r="C840" t="n">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2410.08874 </t>
+          <t xml:space="preserve"> https://doi.org/10.1002/malq.201110065 </t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2410.08874 (2024).</t>
+          <t xml:space="preserve"> Math. Log. Q. 58: 236-243 (2012).</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johannes Niederhauser, Chad E. Brown, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Karel Chvalovský, Petr Cintula </t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableaux for Automated Reasoning in Dependently-Typed Higher-Order Logic (Extended Version). </t>
+          <t xml:space="preserve"> Note on Deduction Theorems in Contraction-Free Logics. </t>
         </is>
       </c>
       <c r="C841" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2410.14232 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/c66c </t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2410.14232 (2024).</t>
+          <t xml:space="preserve"> Short papers for 17th International Conference on Logic for Programming, Artificial intelligence, and Reasoning, LPAR-17-short, Yogyakarta, Indonesia, October 10-15, 2010: 26-29 (2010).</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Johannes Niederhauser, Chad E. Brown, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lash 1.0 (System Description). </t>
+          <t xml:space="preserve"> Tableaux for Automated Reasoning in Dependently-Typed Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C842" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -25669,58 +25669,58 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-10769-6_21 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-63498-7_6 </t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 11th International Joint Conference, IJCAR 2022, Haifa, Israel, August 8-10, 2022, Proceedings: 350-358 (2022).</t>
+          <t xml:space="preserve"> Automated Reasoning - 12th International Joint Conference, IJCAR 2024, Nancy, France, July 3-6, 2024, Proceedings, Part I: 86-104 (2024).</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown </t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lash 1.0 (System Description). </t>
+          <t xml:space="preserve"> A Formal Proof of R(4, 5)=25. </t>
         </is>
       </c>
       <c r="C843" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2205.06640 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ITP.2024.16 </t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2205.06640 (2022).</t>
+          <t xml:space="preserve"> 15th International Conference on Interactive Theorem Proving, ITP 2024, Tbilisi, Georgia, September 9-14, 2024: 16:1-16:18 (2024).</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Karol Pak </t>
+          <t xml:space="preserve">Daniel Ranalter, Chad E. Brown, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AIM Loops and the AIM Conjecture. </t>
+          <t xml:space="preserve"> Experiments with Choice in Dependently-Typed Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C844" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -25729,58 +25729,58 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q123021496 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/2v8h </t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Formaliz. Math. 27: 321-335 (2019).</t>
+          <t xml:space="preserve"> LPAR 2024: Proceedings of 25th Conference on Logic for Programming, Artificial Intelligence and Reasoning, Port Louis, Mauritius, May 26-31, 2024: 311-320 (2024).</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Cezary Kaliszyk, Karol Pak </t>
+          <t xml:space="preserve">Thibault Gauthier, Chad E. Brown </t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Higher-Order Tarski Grothendieck as a Foundation for Formal Proof. </t>
+          <t xml:space="preserve"> A Formal Proof of R(4, 5)=25. </t>
         </is>
       </c>
       <c r="C845" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ITP.2019.9 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2404.01761 </t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10th International Conference on Interactive Theorem Proving, ITP 2019, Portland, OR, USA, September 9-12, 2019: 9:1-9:16 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2404.01761 (2024).</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Karol Pak </t>
+          <t xml:space="preserve">Daniel Ranalter, Chad E. Brown, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Tale of Two Set Theories. </t>
+          <t xml:space="preserve"> Experiments with Choice in Dependently-Typed Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C846" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -25789,28 +25789,28 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-23250-4_4 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2410.08874 </t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 12th International Conference, CICM 2019, Prague, Czech Republic, July 8-12, 2019, Proceedings: 44-60 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2410.08874 (2024).</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cécilia Pradic, Chad E. Brown </t>
+          <t xml:space="preserve">Johannes Niederhauser, Chad E. Brown, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cantor-Bernstein implies Excluded Middle. </t>
+          <t xml:space="preserve"> Tableaux for Automated Reasoning in Dependently-Typed Higher-Order Logic (Extended Version). </t>
         </is>
       </c>
       <c r="C847" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -25819,28 +25819,28 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.09193 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2410.14232 </t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.09193 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2410.14232 (2024).</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Karol Pak </t>
+          <t xml:space="preserve">Chad E. Brown, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Tale of Two Set Theories. </t>
+          <t xml:space="preserve"> Lash 1.0 (System Description). </t>
         </is>
       </c>
       <c r="C848" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -25849,58 +25849,58 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1907.08368 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-10769-6_21 </t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1907.08368 (2019).</t>
+          <t xml:space="preserve"> Automated Reasoning - 11th International Joint Conference, IJCAR 2022, Haifa, Israel, August 8-10, 2022, Proceedings: 350-358 (2022).</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Thibault Gauthier </t>
+          <t xml:space="preserve">Chad E. Brown, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Self-Learned Formula Synthesis in Set Theory. </t>
+          <t xml:space="preserve"> Lash 1.0 (System Description). </t>
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1912.01525 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2205.06640 </t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1912.01525 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2205.06640 (2022).</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Färber, Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown, Karol Pak </t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Internal Guidance for Satallax. </t>
+          <t xml:space="preserve"> AIM Loops and the AIM Conjecture. </t>
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -25909,28 +25909,28 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-40229-1_24 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q123021496 </t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 8th International Joint Conference, IJCAR 2016, Coimbra, Portugal, June 27 - July 2, 2016, Proceedings: 349-361 (2016).</t>
+          <t xml:space="preserve"> Formaliz. Math. 27: 321-335 (2019).</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Färber, Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown, Cezary Kaliszyk, Karol Pak </t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Internal Guidance for Satallax. </t>
+          <t xml:space="preserve"> Higher-Order Tarski Grothendieck as a Foundation for Formal Proof. </t>
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -25939,28 +25939,28 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1605.09293 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ITP.2019.9 </t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1605.09293 (2016).</t>
+          <t xml:space="preserve"> 10th International Conference on Interactive Theorem Proving, ITP 2019, Portland, OR, USA, September 9-12, 2019: 9:1-9:16 (2019).</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown, Karol Pak </t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reconsidering Pairs and Functions as Sets. </t>
+          <t xml:space="preserve"> A Tale of Two Set Theories. </t>
         </is>
       </c>
       <c r="C852" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -25969,28 +25969,28 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-015-9340-6 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-23250-4_4 </t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 55: 199-210 (2015).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 12th International Conference, CICM 2019, Prague, Czech Republic, July 8-12, 2019, Proceedings: 44-60 (2019).</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Christine Rizkallah </t>
+          <t xml:space="preserve">Cécilia Pradic, Chad E. Brown </t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Glivenko and Kuroda for Simple Type Theory. </t>
+          <t xml:space="preserve"> Cantor-Bernstein implies Excluded Middle. </t>
         </is>
       </c>
       <c r="C853" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -25999,28 +25999,28 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2013.10 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.09193 </t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Log. 79: 485-495 (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.09193 (2019).</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown, Karol Pak </t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reducing Higher-Order Theorem Proving to a Sequence of SAT Problems. </t>
+          <t xml:space="preserve"> A Tale of Two Set Theories. </t>
         </is>
       </c>
       <c r="C854" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -26029,58 +26029,58 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-013-9283-8 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1907.08368 </t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 51: 57-77 (2013).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1907.08368 (2019).</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Christine Rizkallah </t>
+          <t xml:space="preserve">Chad E. Brown, Thibault Gauthier </t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t xml:space="preserve"> From Classical Extensional Higher-Order Tableau to Intuitionistic Intentional Natural Deduction. </t>
+          <t xml:space="preserve"> Self-Learned Formula Synthesis in Set Theory. </t>
         </is>
       </c>
       <c r="C855" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/8p9q </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1912.01525 </t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Third International Workshop on Proof Exchange for Theorem Proving, PxTP 2013, Lake Placid, NY, USA, June 9-10, 2013: 27-42 (2013).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1912.01525 (2019).</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown </t>
+          <t xml:space="preserve">Michael Färber, Chad E. Brown </t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Satallax: An Automatic Higher-Order Prover. </t>
+          <t xml:space="preserve"> Internal Guidance for Satallax. </t>
         </is>
       </c>
       <c r="C856" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -26089,28 +26089,28 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-31365-3_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-40229-1_24 </t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 6th International Joint Conference, IJCAR 2012, Manchester, UK, June 26-29, 2012. Proceedings: 111-117 (2012).</t>
+          <t xml:space="preserve"> Automated Reasoning - 8th International Joint Conference, IJCAR 2016, Coimbra, Portugal, June 27 - July 2, 2016, Proceedings: 349-361 (2016).</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julian Backes, Chad E. Brown </t>
+          <t xml:space="preserve">Michael Färber, Chad E. Brown </t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Tableaux for Higher-Order Logic with Choice. </t>
+          <t xml:space="preserve"> Internal Guidance for Satallax. </t>
         </is>
       </c>
       <c r="C857" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -26119,12 +26119,12 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-011-9233-2 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1605.09293 </t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 47: 451-479 (2011).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1605.09293 (2016).</t>
         </is>
       </c>
     </row>
@@ -26136,11 +26136,11 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reducing Higher-Order Theorem Proving to a Sequence of SAT Problems. </t>
+          <t xml:space="preserve"> Reconsidering Pairs and Functions as Sets. </t>
         </is>
       </c>
       <c r="C858" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -26149,28 +26149,28 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-22438-6_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-015-9340-6 </t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE-23 - 23rd International Conference on Automated Deduction, Wroclaw, Poland, July 31 - August 5, 2011. Proceedings: 147-161 (2011).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 55: 199-210 (2015).</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Gert Smolka </t>
+          <t xml:space="preserve">Chad E. Brown, Christine Rizkallah </t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Tableaux for Simple Type Theory and its First-Order Fragment </t>
+          <t xml:space="preserve"> Glivenko and Kuroda for Simple Type Theory. </t>
         </is>
       </c>
       <c r="C859" t="n">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -26179,28 +26179,28 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1004.1947 </t>
+          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2013.10 </t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 6: (2010).</t>
+          <t xml:space="preserve"> J. Symb. Log. 79: 485-495 (2014).</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julian Backes, Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown </t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Tableaux for Higher-Order Logic with Choice. </t>
+          <t xml:space="preserve"> Reducing Higher-Order Theorem Proving to a Sequence of SAT Problems. </t>
         </is>
       </c>
       <c r="C860" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -26209,28 +26209,28 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-14203-1_7 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-013-9283-8 </t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning, 5th International Joint Conference, IJCAR 2010, Edinburgh, UK, July 16-19, 2010. Proceedings: 76-90 (2010).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 51: 57-77 (2013).</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christoph Benzmüller, Chad E. Brown, Michael Kohlhase </t>
+          <t xml:space="preserve">Chad E. Brown, Christine Rizkallah </t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cut-Simulation and Impredicativity </t>
+          <t xml:space="preserve"> From Classical Extensional Higher-Order Tableau to Intuitionistic Intentional Natural Deduction. </t>
         </is>
       </c>
       <c r="C861" t="n">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -26239,28 +26239,28 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/0902.0043 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/8p9q </t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 5: (2009).</t>
+          <t xml:space="preserve"> Third International Workshop on Proof Exchange for Theorem Proving, PxTP 2013, Lake Placid, NY, USA, June 9-10, 2013: 27-42 (2013).</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geoff Sutcliffe, Christoph Benzmüller, Chad E. Brown, Frank Theiss </t>
+          <t xml:space="preserve">Chad E. Brown </t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Progress in the Development of Automated Theorem Proving for Higher-Order Logic. </t>
+          <t xml:space="preserve"> Satallax: An Automatic Higher-Order Prover. </t>
         </is>
       </c>
       <c r="C862" t="n">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -26269,28 +26269,28 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-02959-2_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-31365-3_11 </t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE-22, 22nd International Conference on Automated Deduction, Montreal, Canada, August 2-7, 2009. Proceedings: 116-130 (2009).</t>
+          <t xml:space="preserve"> Automated Reasoning - 6th International Joint Conference, IJCAR 2012, Manchester, UK, June 26-29, 2012. Proceedings: 111-117 (2012).</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Gert Smolka </t>
+          <t xml:space="preserve">Julian Backes, Chad E. Brown </t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Terminating Tableaux for the Basic Fragment of Simple Type Theory. </t>
+          <t xml:space="preserve"> Analytic Tableaux for Higher-Order Logic with Choice. </t>
         </is>
       </c>
       <c r="C863" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -26299,28 +26299,28 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-02716-1_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-011-9233-2 </t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods, 18th International Conference, TABLEAUX 2009, Oslo, Norway, July 6-10, 2009. Proceedings: 138-151 (2009).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 47: 451-479 (2011).</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown, Gert Smolka </t>
+          <t xml:space="preserve">Chad E. Brown </t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Extended First-Order Logic. </t>
+          <t xml:space="preserve"> Reducing Higher-Order Theorem Proving to a Sequence of SAT Problems. </t>
         </is>
       </c>
       <c r="C864" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -26329,28 +26329,28 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-03359-9_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-22438-6_13 </t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theorem Proving in Higher Order Logics, 22nd International Conference, TPHOLs 2009, Munich, Germany, August 17-20, 2009. Proceedings: 164-179 (2009).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE-23 - 23rd International Conference on Automated Deduction, Wroclaw, Poland, July 31 - August 5, 2011. Proceedings: 147-161 (2011).</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feryal Fulya Horozal, Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown, Gert Smolka </t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Formal Representation of Mathematics in a Dependently Typed Set Theory. </t>
+          <t xml:space="preserve"> Analytic Tableaux for Simple Type Theory and its First-Order Fragment </t>
         </is>
       </c>
       <c r="C865" t="n">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -26359,28 +26359,28 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-73086-6_22 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1004.1947 </t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Mechanized Mathematical Assistants, 14th Symposium, Calculemus 2007, 6th International Conference, MKM 2007, Hagenberg, Austria, June 27-30, 2007, Proceedings: 265-279 (2007).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 6: (2010).</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter B. Andrews, Chad E. Brown </t>
+          <t xml:space="preserve">Julian Backes, Chad E. Brown </t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TPS: A hybrid automatic-interactive system for developing proofs. </t>
+          <t xml:space="preserve"> Analytic Tableaux for Higher-Order Logic with Choice. </t>
         </is>
       </c>
       <c r="C866" t="n">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -26389,28 +26389,28 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.jal.2005.10.002 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-14203-1_7 </t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Appl. Log. 4: 367-395 (2006).</t>
+          <t xml:space="preserve"> Automated Reasoning, 5th International Joint Conference, IJCAR 2010, Edinburgh, UK, July 16-19, 2010. Proceedings: 76-90 (2010).</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown </t>
+          <t xml:space="preserve">Christoph Benzmüller, Chad E. Brown, Michael Kohlhase </t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Combining Type Theory and Untyped Set Theory. </t>
+          <t xml:space="preserve"> Cut-Simulation and Impredicativity </t>
         </is>
       </c>
       <c r="C867" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -26419,28 +26419,28 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11814771_19 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/0902.0043 </t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning, Third International Joint Conference, IJCAR 2006, Seattle, WA, USA, August 17-20, 2006, Proceedings: 205-219 (2006).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 5: (2009).</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christoph Benzmüller, Chad E. Brown, Michael Kohlhase </t>
+          <t xml:space="preserve">Geoff Sutcliffe, Christoph Benzmüller, Chad E. Brown, Frank Theiss </t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cut-Simulation in Impredicative Logics. </t>
+          <t xml:space="preserve"> Progress in the Development of Automated Theorem Proving for Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C868" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -26449,28 +26449,28 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11814771_20 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-02959-2_8 </t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning, Third International Joint Conference, IJCAR 2006, Seattle, WA, USA, August 17-20, 2006, Proceedings: 220-234 (2006).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE-22, 22nd International Conference on Automated Deduction, Montreal, Canada, August 2-7, 2009. Proceedings: 116-130 (2009).</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown, Gert Smolka </t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Verifying and Invalidating Textbook Proofs Using Scunak. </t>
+          <t xml:space="preserve"> Terminating Tableaux for the Basic Fragment of Simple Type Theory. </t>
         </is>
       </c>
       <c r="C869" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -26479,28 +26479,28 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11812289_10 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-02716-1_11 </t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mathematical Knowledge Management, 5th International Conference, MKM 2006, Wokingham, UK, August 11-12, 2006, Proceedings: 110-123 (2006).</t>
+          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods, 18th International Conference, TABLEAUX 2009, Oslo, Norway, July 6-10, 2009. Proceedings: 138-151 (2009).</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown, Gert Smolka </t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Encoding Functional Relations in Scunak. </t>
+          <t xml:space="preserve"> Extended First-Order Logic. </t>
         </is>
       </c>
       <c r="C870" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -26509,28 +26509,28 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.entcs.2007.01.022 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-03359-9_13 </t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the First International Workshop on Logical Frameworks and Meta-Languages: Theory and Practice, LFMTP@FLoC 2006, Seattle, WA, USA, August 16, 2006: 127-139 (2006).</t>
+          <t xml:space="preserve"> Theorem Proving in Higher Order Logics, 22nd International Conference, TPHOLs 2009, Munich, Germany, August 17-20, 2009. Proceedings: 164-179 (2009).</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chad E. Brown </t>
+          <t xml:space="preserve">Feryal Fulya Horozal, Chad E. Brown </t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reasoning in Extensional Type Theory with Equality. </t>
+          <t xml:space="preserve"> Formal Representation of Mathematics in a Dependently Typed Set Theory. </t>
         </is>
       </c>
       <c r="C871" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -26539,28 +26539,28 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11532231_3 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-73086-6_22 </t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE-20, 20th International Conference on Automated Deduction, Tallinn, Estonia, July 22-27, 2005, Proceedings: 23-37 (2005).</t>
+          <t xml:space="preserve"> Towards Mechanized Mathematical Assistants, 14th Symposium, Calculemus 2007, 6th International Conference, MKM 2007, Hagenberg, Austria, June 27-30, 2007, Proceedings: 265-279 (2007).</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christoph Benzmüller, Chad E. Brown </t>
+          <t xml:space="preserve">Peter B. Andrews, Chad E. Brown </t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Structured Set of Higher-Order Problems. </t>
+          <t xml:space="preserve"> TPS: A hybrid automatic-interactive system for developing proofs. </t>
         </is>
       </c>
       <c r="C872" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -26569,28 +26569,28 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11541868_5 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.jal.2005.10.002 </t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theorem Proving in Higher Order Logics, 18th International Conference, TPHOLs 2005, Oxford, UK, August 22-25, 2005, Proceedings: 66-81 (2005).</t>
+          <t xml:space="preserve"> J. Appl. Log. 4: 367-395 (2006).</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter B. Andrews, Chad E. Brown, Frank Pfenning, Matthew Bishop, Sunil Issar, Hongwei Xi </t>
+          <t xml:space="preserve">Chad E. Brown </t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ETPS: A System to Help Students Write Formal Proofs. </t>
+          <t xml:space="preserve"> Combining Type Theory and Untyped Set Theory. </t>
         </is>
       </c>
       <c r="C873" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -26599,12 +26599,12 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/B:JARS.0000021871.18776.94 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11814771_19 </t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 32: 75-92 (2004).</t>
+          <t xml:space="preserve"> Automated Reasoning, Third International Joint Conference, IJCAR 2006, Seattle, WA, USA, August 17-20, 2006, Proceedings: 205-219 (2006).</t>
         </is>
       </c>
     </row>
@@ -26616,11 +26616,11 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Higher-order semantics and extensionality. </t>
+          <t xml:space="preserve"> Cut-Simulation in Impredicative Logics. </t>
         </is>
       </c>
       <c r="C874" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -26629,12 +26629,12 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389428 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11814771_20 </t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Log. 69: 1027-1088 (2004).</t>
+          <t xml:space="preserve"> Automated Reasoning, Third International Joint Conference, IJCAR 2006, Seattle, WA, USA, August 17-20, 2006, Proceedings: 220-234 (2006).</t>
         </is>
       </c>
     </row>
@@ -26646,11 +26646,11 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving for Set Variables in Higher-Order Theorem Proving. </t>
+          <t xml:space="preserve"> Verifying and Invalidating Textbook Proofs Using Scunak. </t>
         </is>
       </c>
       <c r="C875" t="n">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -26659,28 +26659,28 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/3-540-45620-1_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11812289_10 </t>
         </is>
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE-18, 18th International Conference on Automated Deduction, Copenhagen, Denmark, July 27-30, 2002, Proceedings: 408-422 (2002).</t>
+          <t xml:space="preserve"> Mathematical Knowledge Management, 5th International Conference, MKM 2006, Wokingham, UK, August 11-12, 2006, Proceedings: 110-123 (2006).</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter B. Andrews, Matthew Bishop, Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown </t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t xml:space="preserve"> System Description: TPS: A Theorem Proving System for Type Theory. </t>
+          <t xml:space="preserve"> Encoding Functional Relations in Scunak. </t>
         </is>
       </c>
       <c r="C876" t="n">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -26689,28 +26689,28 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/10721959_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.entcs.2007.01.022 </t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE-17, 17th International Conference on Automated Deduction, Pittsburgh, PA, USA, June 17-20, 2000, Proceedings: 164-169 (2000).</t>
+          <t xml:space="preserve"> Proceedings of the First International Workshop on Logical Frameworks and Meta-Languages: Theory and Practice, LFMTP@FLoC 2006, Seattle, WA, USA, August 16, 2006: 127-139 (2006).</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter B. Andrews, Chad E. Brown </t>
+          <t xml:space="preserve">Chad E. Brown </t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tutorial: Using TPS for Higher-Order Theorem Proving and ETPS for Teaching Logic. </t>
+          <t xml:space="preserve"> Reasoning in Extensional Type Theory with Equality. </t>
         </is>
       </c>
       <c r="C877" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -26719,28 +26719,28 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/10721959_44 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11532231_3 </t>
         </is>
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE-17, 17th International Conference on Automated Deduction, Pittsburgh, PA, USA, June 17-20, 2000, Proceedings: 511-512 (2000).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE-20, 20th International Conference on Automated Deduction, Tallinn, Estonia, July 22-27, 2005, Proceedings: 23-37 (2005).</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Christoph Benzmüller, Chad E. Brown </t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Strategy Invention for Confluence of Term Rewrite Systems. </t>
+          <t xml:space="preserve"> A Structured Set of Higher-Order Problems. </t>
         </is>
       </c>
       <c r="C878" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -26749,28 +26749,28 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2025/526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11541868_5 </t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Thirty-Fourth International Joint Conference on Artificial Intelligence, IJCAI 2025, Montreal, Canada, August 16-22, 2025: 4724-4732 (2025).</t>
+          <t xml:space="preserve"> Theorem Proving in Higher Order Logics, 18th International Conference, TPHOLs 2005, Oxford, UK, August 22-25, 2005, Proceedings: 66-81 (2005).</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kristina Aleksandrova, Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Peter B. Andrews, Chad E. Brown, Frank Pfenning, Matthew Bishop, Sunil Issar, Hongwei Xi </t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Prover9 Unleashed: Automated Configuration for Enhanced Proof Discovery. </t>
+          <t xml:space="preserve"> ETPS: A System to Help Students Write Formal Proofs. </t>
         </is>
       </c>
       <c r="C879" t="n">
-        <v>2024</v>
+        <v>2004</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -26779,28 +26779,28 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/sd6t </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/B:JARS.0000021871.18776.94 </t>
         </is>
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LPAR 2024: Proceedings of 25th Conference on Logic for Programming, Artificial Intelligence and Reasoning, Port Louis, Mauritius, May 26-31, 2024: 360-369 (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 32: 75-92 (2004).</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Christoph Benzmüller, Chad E. Brown, Michael Kohlhase </t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Strategy Invention for Confluence of Term Rewrite Systems. </t>
+          <t xml:space="preserve"> Higher-order semantics and extensionality. </t>
         </is>
       </c>
       <c r="C880" t="n">
-        <v>2024</v>
+        <v>2004</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -26809,28 +26809,28 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2411.06409 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389428 </t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2411.06409 (2024).</t>
+          <t xml:space="preserve"> J. Symb. Log. 69: 1027-1088 (2004).</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Chad E. Brown </t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VizAR: Visualization of Automated Reasoning Proofs (System Description). </t>
+          <t xml:space="preserve"> Solving for Set Variables in Higher-Order Theorem Proving. </t>
         </is>
       </c>
       <c r="C881" t="n">
-        <v>2023</v>
+        <v>2002</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -26839,28 +26839,28 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-42753-4_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/3-540-45620-1_33 </t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 16th International Conference, CICM 2023, Cambridge, UK, September 5-8, 2023, Proceedings: 303-308 (2023).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE-18, 18th International Conference on Automated Deduction, Copenhagen, Denmark, July 27-30, 2002, Proceedings: 408-422 (2002).</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Peter B. Andrews, Matthew Bishop, Chad E. Brown </t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relaxed Weighted Path Order in Theorem Proving. </t>
+          <t xml:space="preserve"> System Description: TPS: A Theorem Proving System for Type Theory. </t>
         </is>
       </c>
       <c r="C882" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -26869,28 +26869,28 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482108 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/10721959_11 </t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Math. Comput. Sci. 14: 657-670 (2020).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE-17, 17th International Conference on Automated Deduction, Pittsburgh, PA, USA, June 17-20, 2000, Proceedings: 164-169 (2000).</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
+          <t xml:space="preserve">Peter B. Andrews, Chad E. Brown </t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Recursive Reductions of Action Dependencies for Coordination-Based Multiagent Planning. </t>
+          <t xml:space="preserve"> Tutorial: Using TPS for Higher-Order Theorem Proving and ETPS for Teaching Logic. </t>
         </is>
       </c>
       <c r="C883" t="n">
-        <v>2018</v>
+        <v>2000</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -26899,28 +26899,28 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/10721959_44 </t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trans. Comput. Collect. Intell. 28: 66-92 (2018).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE-17, 17th International Conference on Automated Deduction, Pittsburgh, PA, USA, June 17-20, 2000, Proceedings: 511-512 (2000).</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubuv, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards a Unified Ordering for Superposition-Based Automated Reasoning. </t>
+          <t xml:space="preserve"> Automated Strategy Invention for Confluence of Term Rewrite Systems. </t>
         </is>
       </c>
       <c r="C884" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -26929,28 +26929,28 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482122 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2025/526 </t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mathematical Software - ICMS 2018 - 6th International Conference, South Bend, IN, USA, July 24-27, 2018, Proceedings: 245-254 (2018).</t>
+          <t xml:space="preserve"> Proceedings of the Thirty-Fourth International Joint Conference on Artificial Intelligence, IJCAI 2025, Montreal, Canada, August 16-22, 2025: 4724-4732 (2025).</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda, Michal Pechoucek </t>
+          <t xml:space="preserve">Kristina Aleksandrova, Jan Jakubuv, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Privacy-concerned multiagent planning. </t>
+          <t xml:space="preserve"> Prover9 Unleashed: Automated Configuration for Enhanced Proof Discovery. </t>
         </is>
       </c>
       <c r="C885" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -26959,28 +26959,28 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044875 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/sd6t </t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowl. Inf. Syst. 48: 581-618 (2016).</t>
+          <t xml:space="preserve"> LPAR 2024: Proceedings of 25th Conference on Logic for Programming, Artificial Intelligence and Reasoning, Port Louis, Mauritius, May 26-31, 2024: 360-369 (2024).</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Martin Svatos, Antonín Komenda </t>
+          <t xml:space="preserve">Liao Zhang, Fabian Mitterwallner, Jan Jakubuv, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Recursive Polynomial Reductions for Classical Planning. </t>
+          <t xml:space="preserve"> Automated Strategy Invention for Confluence of Term Rewrite Systems. </t>
         </is>
       </c>
       <c r="C886" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -26989,28 +26989,28 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://www.aaai.org/ocs/index.php/ICAPS/ICAPS16/paper/view/13088 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2411.06409 </t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Twenty-Sixth International Conference on Automated Planning and Scheduling, ICAPS 2016, London, UK, June 12-17, 2016.: 317-325 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2411.06409 (2024).</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Recursive Reductions of Internal Dependencies in Multiagent Planning. </t>
+          <t xml:space="preserve"> VizAR: Visualization of Automated Reasoning Proofs (System Description). </t>
         </is>
       </c>
       <c r="C887" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -27019,28 +27019,28 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0005754901810191 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-42753-4_22 </t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 8th International Conference on Agents and Artificial Intelligence (ICAART 2016), Volume 2, Rome, Italy, February 24-26, 2016.: 181-191 (2016).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 16th International Conference, CICM 2023, Cambridge, UK, September 5-8, 2023, Proceedings: 303-308 (2023).</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Karel Durkota, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Extensibility Based Multiagent Planner with Plan Diversity Metrics. </t>
+          <t xml:space="preserve"> Relaxed Weighted Path Order in Theorem Proving. </t>
         </is>
       </c>
       <c r="C888" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -27049,12 +27049,12 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044876 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482108 </t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trans. Comput. Collect. Intell. 20: 117-139 (2015).</t>
+          <t xml:space="preserve"> Math. Comput. Sci. 14: 657-670 (2020).</t>
         </is>
       </c>
     </row>
@@ -27066,11 +27066,11 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t xml:space="preserve"> From Public Plans to Global Solutions in Multiagent Planning. </t>
+          <t xml:space="preserve"> Recursive Reductions of Action Dependencies for Coordination-Based Multiagent Planning. </t>
         </is>
       </c>
       <c r="C889" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -27079,28 +27079,28 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044872 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044865 </t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multi-Agent Systems and Agreement Technologies - 13th European Conference, EUMAS 2015, and Third International Conference, AT 2015, Athens, Greece, December 17-18, 2015, Revised Selected Papers: 21-33 (2015).</t>
+          <t xml:space="preserve"> Trans. Comput. Collect. Intell. 28: 66-92 (2018).</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Jan Tozicka, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Jakubuv, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiagent Planning by Plan Set Intersection and Plan Verification. </t>
+          <t xml:space="preserve"> Towards a Unified Ordering for Superposition-Based Automated Reasoning. </t>
         </is>
       </c>
       <c r="C890" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -27109,28 +27109,28 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482122 </t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICAART 2015 - Proceedings of the International Conference on Agents and Artificial Intelligence, Volume 2, Lisbon, Portugal, 10-12 January, 2015.: 173-182 (2015).</t>
+          <t xml:space="preserve"> Mathematical Software - ICMS 2018 - 6th International Conference, South Bend, IN, USA, July 24-27, 2018, Proceedings: 245-254 (2018).</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, Jan Tozicka, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Using Process Calculi for Plan Verification in Multiagent Planning. </t>
+          <t xml:space="preserve"> Privacy-concerned multiagent planning. </t>
         </is>
       </c>
       <c r="C891" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -27139,28 +27139,28 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044878 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044875 </t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Agents and Artificial Intelligence - 7th International Conference, ICAART 2015, Lisbon, Portugal, January 10-12, 2015, Revised Selected Papers: 245-261 (2015).</t>
+          <t xml:space="preserve"> Knowl. Inf. Syst. 48: 581-618 (2016).</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Martin Svatos, Antonín Komenda </t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generating Multi-Agent Plans by Distributed Intersection of Finite State Machines. </t>
+          <t xml:space="preserve"> Recursive Polynomial Reductions for Classical Planning. </t>
         </is>
       </c>
       <c r="C892" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -27169,28 +27169,28 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-419-0-1111 </t>
+          <t xml:space="preserve"> http://www.aaai.org/ocs/index.php/ICAPS/ICAPS16/paper/view/13088 </t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ECAI 2014 - 21st European Conference on Artificial Intelligence, 18-22 August 2014, Prague, Czech Republic - Including Prestigious Applications of Intelligent Systems (PAIS 2014): 1111-1112 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the Twenty-Sixth International Conference on Automated Planning and Scheduling, ICAPS 2016, London, UK, June 12-17, 2016.: 317-325 (2016).</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Karel Durkota, Antonín Komenda, Michal Pechoucek </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiagent Planning Supported by Plan Diversity Metrics and Landmark Actions. </t>
+          <t xml:space="preserve"> Recursive Reductions of Internal Dependencies in Multiagent Planning. </t>
         </is>
       </c>
       <c r="C893" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -27199,28 +27199,28 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004918701780189 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0005754901810191 </t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICAART 2014 - Proceedings of the 6th International Conference on Agents and Artificial Intelligence, Volume 1, ESEO, Angers, Loire Valley, France, 6-8 March, 2014: 178-189 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 8th International Conference on Agents and Artificial Intelligence (ICAART 2016), Volume 2, Rome, Italy, February 24-26, 2016.: 181-191 (2016).</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Karel Durkota, Antonín Komenda </t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generic process shape types and the Poly* system </t>
+          <t xml:space="preserve"> Extensibility Based Multiagent Planner with Plan Diversity Metrics. </t>
         </is>
       </c>
       <c r="C894" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -27229,28 +27229,28 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://ethos.bl.uk/OrderDetails.do?uin=uk.bl.ethos.547706 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044876 </t>
         </is>
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2010).</t>
+          <t xml:space="preserve"> Trans. Comput. Collect. Intell. 20: 117-139 (2015).</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, J. B. Wells </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Expressiveness of Generic Process Shape Types. </t>
+          <t xml:space="preserve"> From Public Plans to Global Solutions in Multiagent Planning. </t>
         </is>
       </c>
       <c r="C895" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -27259,28 +27259,28 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044883 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044872 </t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trustworthly Global Computing - 5th International Symposium, TGC 2010, Munich, Germany, February 24-26, 2010, Revised Selected Papers: 103-119 (2010).</t>
+          <t xml:space="preserve"> Multi-Agent Systems and Agreement Technologies - 13th European Conference, EUMAS 2015, and Third International Conference, AT 2015, Athens, Greece, December 17-18, 2015, Revised Selected Papers: 21-33 (2015).</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Jakubuv, J. B. Wells </t>
+          <t xml:space="preserve">Jan Jakubuv, Jan Tozicka, Antonín Komenda </t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Expressiveness of Generic Process Shape Types </t>
+          <t xml:space="preserve"> Multiagent Planning by Plan Set Intersection and Plan Verification. </t>
         </is>
       </c>
       <c r="C896" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -27289,118 +27289,118 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1003.6096 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1003.6096 (2010).</t>
+          <t xml:space="preserve"> ICAART 2015 - Proceedings of the International Conference on Agents and Artificial Intelligence, Volume 2, Lisbon, Portugal, 10-12 January, 2015.: 173-182 (2015).</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Gary K. L. Tam </t>
+          <t xml:space="preserve">Jan Jakubuv, Jan Tozicka, Antonín Komenda </t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust point cloud completion under corruption. </t>
+          <t xml:space="preserve"> Using Process Calculi for Plan Verification in Multiagent Planning. </t>
         </is>
       </c>
       <c r="C897" t="n">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cag.2025.104401 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044878 </t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Graph. 132: (2025).</t>
+          <t xml:space="preserve"> Agents and Artificial Intelligence - 7th International Conference, ICAART 2015, Lisbon, Portugal, January 10-12, 2015, Revised Selected Papers: 245-261 (2015).</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Gary K. L. Tam </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Antonín Komenda </t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust Point Cloud Completion Under Corruption. </t>
+          <t xml:space="preserve"> Generating Multi-Agent Plans by Distributed Intersection of Finite State Machines. </t>
         </is>
       </c>
       <c r="C898" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.16743 </t>
+          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-419-0-1111 </t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.16743 (2025/07).</t>
+          <t xml:space="preserve"> ECAI 2014 - 21st European Conference on Artificial Intelligence, 18-22 August 2014, Prague, Czech Republic - Including Prestigious Applications of Intelligent Systems (PAIS 2014): 1111-1112 (2014).</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Muneeb Imtiaz Ahmad, Gary K. L. Tam </t>
+          <t xml:space="preserve">Jan Tozicka, Jan Jakubuv, Karel Durkota, Antonín Komenda, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Point Cloud Completion: A Survey. </t>
+          <t xml:space="preserve"> Multiagent Planning Supported by Plan Diversity Metrics and Landmark Actions. </t>
         </is>
       </c>
       <c r="C899" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TVCG.2023.3344935 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004918701780189 </t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 30: 6880-6899 (2024/10).</t>
+          <t xml:space="preserve"> ICAART 2014 - Proceedings of the 6th International Conference on Agents and Artificial Intelligence, Volume 1, ESEO, Angers, Loire Valley, France, 6-8 March, 2014: 178-189 (2014).</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
+          <t xml:space="preserve">Jan Jakubuv </t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Gold-medalist Performance in Solving Olympiad Geometry with AlphaGeometry2. </t>
+          <t xml:space="preserve"> Generic process shape types and the Poly* system </t>
         </is>
       </c>
       <c r="C900" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -27409,58 +27409,58 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2502.03544 </t>
+          <t xml:space="preserve"> https://ethos.bl.uk/OrderDetails.do?uin=uk.bl.ethos.547706 </t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2502.03544 (2025/02).</t>
+          <t xml:space="preserve"> Thesis (2010).</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Jan Jakubuv, J. B. Wells </t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
+          <t xml:space="preserve"> Expressiveness of Generic Process Shape Types. </t>
         </is>
       </c>
       <c r="C901" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q62044883 </t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
+          <t xml:space="preserve"> Trustworthly Global Computing - 5th International Symposium, TGC 2010, Munich, Germany, February 24-26, 2010, Revised Selected Papers: 103-119 (2010).</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simon Frieder, Mirek Olsák, Julius Berner, Thomas Lukasiewicz </t>
+          <t xml:space="preserve">Jan Jakubuv, J. B. Wells </t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The IMO Small Challenge: Not-Too-Hard Olympiad Math Datasets for LLMs. </t>
+          <t xml:space="preserve"> Expressiveness of Generic Process Shape Types </t>
         </is>
       </c>
       <c r="C902" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -27469,24 +27469,24 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=HYuKXhgzjm </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1003.6096 </t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Second Tiny Papers Track at ICLR 2024, Tiny Papers @ ICLR 2024, Vienna, Austria, May 11, 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1003.6096 (2010).</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
+          <t xml:space="preserve"> Beneficial AGI: Care and Collaboration Are All You Need. </t>
         </is>
       </c>
       <c r="C903" t="n">
@@ -27494,1083 +27494,1083 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-65572-2_9 </t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
+          <t xml:space="preserve"> Artificial General Intelligence - 17th International Conference, AGI 2024, Seattle, WA, USA, August 13-16, 2024, Proceedings: 84-88 (2024).</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Sergey Rodionov, Zarathustra Amadeus Goertzel, Ben Goertzel </t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
+          <t xml:space="preserve"> An Evaluation of GPT-4 on the ETHICS Dataset. </t>
         </is>
       </c>
       <c r="C904" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2309.10492 </t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2309.10492 (2023).</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Ben Goertzel, Vitaly Bogdanov, Michael Duncan, Deborah Duong, Zarathustra Amadeus Goertzel, Jan Horlings, Matthew Iklé, Lucius Gregory Meredith, Alexey Potapov, Andre Luiz de Senna, Hedra Seid, Andres Suarez, Adam Vandervorst, Robert Werko </t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
+          <t xml:space="preserve"> OpenCog Hyperon: A Framework for AGI at the Human Level and Beyond. </t>
         </is>
       </c>
       <c r="C905" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2310.18318 </t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2310.18318 (2023).</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Erratum: Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
+          <t xml:space="preserve"> Make E Smart Again (Short Paper). </t>
         </is>
       </c>
       <c r="C906" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1142/S021906132192001X </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51054-1_26 </t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Math. Log. 21: (2021).</t>
+          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part II: 408-415 (2020).</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Maltsev conditions for General Congruence Meet-semidistributive Algebras. </t>
+          <t xml:space="preserve"> Make E Smart Again. </t>
         </is>
       </c>
       <c r="C907" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2021.14 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2004.08858 </t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Log. 86: 1432-1451 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2004.08858 (2020).</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Miroslav Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Gary K. L. Tam </t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
+          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust point cloud completion under corruption. </t>
         </is>
       </c>
       <c r="C908" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://proceedings.neurips.cc/paper/2021/hash/cf708fc1decf0337aded484f8f4519ae-Abstract.html </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cag.2025.104401 </t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 34: Annual Conference on Neural Information Processing Systems 2021, NeurIPS 2021, December 6-14, 2021, virtual.: 24707-24718 (2021).</t>
+          <t xml:space="preserve"> Comput. Graph. 132: (2025).</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Mirek Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Gary K. L. Tam </t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
+          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust Point Cloud Completion Under Corruption. </t>
         </is>
       </c>
       <c r="C909" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2110.06149 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.16743 </t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2110.06149 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.16743 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Muneeb Imtiaz Ahmad, Gary K. L. Tam </t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Loop conditions for strongly connected digraphs. </t>
+          <t xml:space="preserve"> Point Cloud Completion: A Survey. </t>
         </is>
       </c>
       <c r="C910" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114614801 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TVCG.2023.3344935 </t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Int. J. Algebra Comput. 30: 467-499 (2020).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 30: 6880-6899 (2024/10).</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GeoLogic - Graphical Interactive Theorem Prover for Euclidean Geometry. </t>
+          <t xml:space="preserve"> A Wos Challenge Met. </t>
         </is>
       </c>
       <c r="C911" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-52200-1_26 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114264018 </t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mathematical Software - ICMS 2020 - 7th International Conference, Braunschweig, Germany, July 13-16, 2020, Proceedings: 263-271 (2020).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 66: 565-574 (2022).</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Stepan Holub, Robert Veroff </t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GeoLogic - Graphical interactive theorem prover for Euclidean geometry. </t>
+          <t xml:space="preserve"> Formalizing a Fragment of Combinatorics on Words. </t>
         </is>
       </c>
       <c r="C912" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.03586 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-58741-7_3 </t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.03586 (2020).</t>
+          <t xml:space="preserve"> Unveiling Dynamics and Complexity - 13th Conference on Computability in Europe, CiE 2017, Turku, Finland, June 12-16, 2017, Proceedings: 24-31 (2017).</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Matthew Spinks, Robert J. Bignall, Robert Veroff </t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ω-categorical structures avoiding height 1 identities. </t>
+          <t xml:space="preserve"> Discriminator logics (Research announcement). </t>
         </is>
       </c>
       <c r="C913" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2006.12254 </t>
+          <t xml:space="preserve"> https://doi.org/10.26686/ajl.v11i2.2020 </t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2006.12254 (2020).</t>
+          <t xml:space="preserve"> Australas. J. Log. 11: (2014).</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Van Trung Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Ranganathan Padmanabhan, Robert Veroff </t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
+          <t xml:space="preserve"> A Geometric Procedure with Prover9. </t>
         </is>
       </c>
       <c r="C914" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1142/S0219061319500107 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_7 </t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Math. Log. 19: 1950010:1-1950010:31 (2019).</t>
+          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 139-150 (2013).</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Michael K. Kinyon, Robert Veroff, Petr Vojtechovský </t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dichotomy for Symmetric Boolean PCSPs. </t>
+          <t xml:space="preserve"> Loops with Abelian Inner Mapping Groups: An Application of Automated Deduction. </t>
         </is>
       </c>
       <c r="C915" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ICALP.2019.57 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_8 </t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 46th International Colloquium on Automata, Languages, and Programming, ICALP 2019, Patras, Greece, July 9-12, 2019: 57:1-57:12 (2019).</t>
+          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 151-164 (2013).</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Francesco Paoli, Matthew Spinks, Robert Veroff </t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Topology is relevant (in a dichotomy conjecture for infinite-domain constraint satisfaction problems). </t>
+          <t xml:space="preserve"> Abelian Logic and the Logics of Pointed Lattice-Ordered Varieties. </t>
         </is>
       </c>
       <c r="C916" t="n">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/LICS.2019.8785883 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11787-008-0034-2 </t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 34th Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2019, Vancouver, BC, Canada, June 24-27, 2019: 1-12 (2019).</t>
+          <t xml:space="preserve"> Logica Universalis 2: 209-233 (2008).</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Topology is relevant (in the infinite-domain dichotomy conjecture for constraint satisfaction problems). </t>
+          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. I. </t>
         </is>
       </c>
       <c r="C917" t="n">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1901.04237 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9113-x </t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1901.04237 (2019).</t>
+          <t xml:space="preserve"> Stud Logica 88: 325-348 (2008).</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dichotomy for symmetric Boolean PCSPs. </t>
+          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. II. </t>
         </is>
       </c>
       <c r="C918" t="n">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.12424 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9138-1 </t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.12424 (2019).</t>
+          <t xml:space="preserve"> Stud Logica 89: 401-425 (2008).</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Frank Gilfeather, Vikas Hamine, Paul Helman, Julie Hutt, Terry Loring, C. Rick Lyons, Robert Veroff </t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The equivalence of two dichotomy conjectures for infinite domain constraint satisfaction problems. </t>
+          <t xml:space="preserve"> Learning and modeling biosignatures from tissue images. </t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/LICS.2017.8005128 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33282059 </t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 32nd Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2017, Reykjavik, Iceland, June 20-23, 2017: 1-12 (2017).</t>
+          <t xml:space="preserve"> Comput. Biol. Medicine 37: 1539-1552 (2007).</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Michael Pinsker, Van Trung Pham </t>
+          <t xml:space="preserve">Robert Veroff, Matthew Spinks </t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Equations in oligomorphic clones and the Constraint Satisfaction Problem for $ω$-categorical structures. </t>
+          <t xml:space="preserve"> Axiomatizing the Skew Boolean Propositional Calculus. </t>
         </is>
       </c>
       <c r="C920" t="n">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1612.07551 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-006-9029-y </t>
         </is>
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1612.07551 (2016).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 37: 3-20 (2006).</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics. </t>
         </is>
       </c>
       <c r="C921" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262834 </t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 11176-11184 (2025).</t>
+          <t xml:space="preserve"> Stud Logica 80: 195-234 (2005).</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff, Susan R. Atlas, Cheryl Willman </t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> A Bayesian Network Classification Methodology for Gene Expression Data. </t>
         </is>
       </c>
       <c r="C922" t="n">
-        <v>2025</v>
+        <v>2004</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33209551 </t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
+          <t xml:space="preserve"> J. Comput. Biol. 11: 581-615 (2004).</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> A Shortest 2-Basis for Boolean Algebra in Terms of the Sheffer Stroke. </t>
         </is>
       </c>
       <c r="C923" t="n">
-        <v>2025</v>
+        <v>2003</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1027322305654 </t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 31: 1-9 (2003).</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
+          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics </t>
         </is>
       </c>
       <c r="C924" t="n">
-        <v>2025</v>
+        <v>2003</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/cs/0301026 </t>
         </is>
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
+          <t xml:space="preserve"> arXiv CoRR cs.LO/0301026 (2003).</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">William McCune, Robert Veroff, Branden Fitelson, Kenneth Harris, Andrew Feist, Larry Wos </t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> Short Single Axioms for Boolean Algebra. </t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>2025</v>
+        <v>2002</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q60061107 </t>
         </is>
       </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 29: 1-16 (2002).</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> The application of automated reasoning to formal models of combinatorial optimization. </t>
         </is>
       </c>
       <c r="C926" t="n">
-        <v>2025</v>
+        <v>2001</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q127517130 </t>
         </is>
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
+          <t xml:space="preserve"> Appl. Math. Comput. 120: 175-194 (2001).</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
+          <t xml:space="preserve"> Finding Shortest Proofs: An Application of Linked Inference Rules. </t>
         </is>
       </c>
       <c r="C927" t="n">
-        <v>2025</v>
+        <v>2001</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1010635625063 </t>
         </is>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 27: 123-139 (2001).</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Solving Open Questions and Other Challenge Problems Using Proof Sketches. </t>
         </is>
       </c>
       <c r="C928" t="n">
-        <v>2024</v>
+        <v>2001</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1010639725972 </t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 27: 157-174 (2001).</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Gregory H. Chisholm, Steven T. Eckmann, Christopher M. Lain, Robert Veroff </t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> Understanding Integrated Circuits. </t>
         </is>
       </c>
       <c r="C929" t="n">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
+          <t xml:space="preserve"> http://doi.ieeecomputersociety.org/10.1109/54.765201 </t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
+          <t xml:space="preserve"> IEEE Des. Test Comput. 16: 26-37 (1999).</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Using Hints to Increase the Effectiveness of an Automated Reasoning Program: Case Studies. </t>
         </is>
       </c>
       <c r="C930" t="n">
-        <v>2024</v>
+        <v>1996</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/BF00252178 </t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 16: 223-239 (1996).</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
+          <t xml:space="preserve">Larry Wos, Robert Veroff </t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
+          <t xml:space="preserve"> Logical basis for the automation of reasoning: Case studies. </t>
         </is>
       </c>
       <c r="C931" t="n">
-        <v>2024</v>
+        <v>1994</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
+          <t xml:space="preserve"> Handbook of Logic in Artificial Intelligence and Logic Programming, Volume2, Deduction Methodologies: 1-40 (1994).</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> The Linked Inference Principle, I: The Formal Treatment. </t>
         </is>
       </c>
       <c r="C932" t="n">
-        <v>2024</v>
+        <v>1992</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114267080 </t>
         </is>
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 8: 213-274 (1992).</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff, Frank R. Carrano </t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Intermediate problem solving and data structures - walls and mirrors (2. ed.). </t>
         </is>
       </c>
       <c r="C933" t="n">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
+          <t xml:space="preserve"> Benjamin/Cummings series in computer science, Benjamin/Cummings (1991).</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
+          <t xml:space="preserve"> Designing Deductive Databases. </t>
         </is>
       </c>
       <c r="C934" t="n">
-        <v>2023</v>
+        <v>1988</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/BF00244512 </t>
         </is>
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2023/12)</t>
+          <t xml:space="preserve"> J. Autom. Reason. 4: 29-68 (1988).</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
+          <t xml:space="preserve">Larry Wos, Steve Winker, Barry Smith, Robert Veroff, Lawrence J. Henschen </t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
+          <t xml:space="preserve"> A New Use of an Automated Reasoning Assistant: Open Questions in Equivalential Calculus and the Study of Infinite Domains. </t>
         </is>
       </c>
       <c r="C935" t="n">
-        <v>2023</v>
+        <v>1984</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262293 </t>
         </is>
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
+          <t xml:space="preserve"> Artif. Intell. 22: 303-356 (1984).</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Larry Wos, Robert Veroff, Barry Smith, William McCune </t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> The Linked Inference Principle, II: The User's Viewpoint. </t>
         </is>
       </c>
       <c r="C936" t="n">
-        <v>2023</v>
+        <v>1984</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-0-387-34768-4_19 </t>
         </is>
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
+          <t xml:space="preserve"> 7th International Conference on Automated Deduction, Napa, California, USA, May 14-16, 1984, Proceedings: 316-332 (1984).</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Larry Henschen, Barry Smith, Robert Veroff, Steve Winker, Larry Wos </t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
+          <t xml:space="preserve"> Questions concerning possible shortest single axioms for the equivalential calculus: an application of automated theorem proving to infinite domains. </t>
         </is>
       </c>
       <c r="C937" t="n">
-        <v>2022</v>
+        <v>1983</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114254310 </t>
         </is>
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
+          <t xml:space="preserve"> Notre Dame J. Formal Log. 24: 205-223 (1983).</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Robert Veroff, Lawrence J. Henschen </t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Application of Automatic Transformations to Program Verification. </t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>2022</v>
+        <v>1981</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
+          <t xml:space="preserve"> http://ijcai.org/Proceedings/81-1/Papers/087.pdf </t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
+          <t xml:space="preserve"> Proceedings of the 7th International Joint Conference on Artificial Intelligence, IJCAI '81, Vancouver, BC, Canada, August 24-28, 1981: 472-479 (1981).</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Gold-medalist Performance in Solving Olympiad Geometry with AlphaGeometry2. </t>
         </is>
       </c>
       <c r="C939" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -28579,58 +28579,58 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2502.03544 </t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2502.03544 (2025/02).</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
         </is>
       </c>
       <c r="C940" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
         </is>
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
+          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Simon Frieder, Mirek Olsák, Julius Berner, Thomas Lukasiewicz </t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> The IMO Small Challenge: Not-Too-Hard Olympiad Math Datasets for LLMs. </t>
         </is>
       </c>
       <c r="C941" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -28639,118 +28639,118 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=HYuKXhgzjm </t>
         </is>
       </c>
       <c r="F941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
+          <t xml:space="preserve"> The Second Tiny Papers Track at ICLR 2024, Tiny Papers @ ICLR 2024, Vienna, Austria, May 11, 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
         </is>
       </c>
       <c r="C942" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
         </is>
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
+          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
         </is>
       </c>
       <c r="C943" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
         </is>
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
         </is>
       </c>
       <c r="C944" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
         </is>
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
+          <t xml:space="preserve"> Erratum: Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
         </is>
       </c>
       <c r="C945" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -28759,28 +28759,28 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1142/S021906132192001X </t>
         </is>
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
+          <t xml:space="preserve"> J. Math. Log. 21: (2021).</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> Maltsev conditions for General Congruence Meet-semidistributive Algebras. </t>
         </is>
       </c>
       <c r="C946" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -28789,28 +28789,28 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
+          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2021.14 </t>
         </is>
       </c>
       <c r="F946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
+          <t xml:space="preserve"> J. Symb. Log. 86: 1432-1451 (2021).</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Marco Bagatella, Miroslav Olsák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
+          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
         </is>
       </c>
       <c r="C947" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -28819,28 +28819,28 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
+          <t xml:space="preserve"> https://proceedings.neurips.cc/paper/2021/hash/cf708fc1decf0337aded484f8f4519ae-Abstract.html </t>
         </is>
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 34: Annual Conference on Neural Information Processing Systems 2021, NeurIPS 2021, December 6-14, 2021, virtual.: 24707-24718 (2021).</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Marco Bagatella, Mirek Olsák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
         </is>
       </c>
       <c r="C948" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -28849,28 +28849,28 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2110.06149 </t>
         </is>
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2110.06149 (2021).</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> Loop conditions for strongly connected digraphs. </t>
         </is>
       </c>
       <c r="C949" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -28879,28 +28879,28 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114614801 </t>
         </is>
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
+          <t xml:space="preserve"> Int. J. Algebra Comput. 30: 467-499 (2020).</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
+          <t xml:space="preserve"> GeoLogic - Graphical Interactive Theorem Prover for Euclidean Geometry. </t>
         </is>
       </c>
       <c r="C950" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -28909,28 +28909,28 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-52200-1_26 </t>
         </is>
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
+          <t xml:space="preserve"> Mathematical Software - ICMS 2020 - 7th International Conference, Braunschweig, Germany, July 13-16, 2020, Proceedings: 263-271 (2020).</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
+          <t xml:space="preserve"> GeoLogic - Graphical interactive theorem prover for Euclidean geometry. </t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -28939,28 +28939,28 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.03586 </t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.03586 (2020).</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> ω-categorical structures avoiding height 1 identities. </t>
         </is>
       </c>
       <c r="C952" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -28969,28 +28969,28 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2006.12254 </t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2006.12254 (2020).</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Van Trung Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
+          <t xml:space="preserve"> Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
         </is>
       </c>
       <c r="C953" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -28999,28 +28999,28 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
+          <t xml:space="preserve"> https://doi.org/10.1142/S0219061319500107 </t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
+          <t xml:space="preserve"> J. Math. Log. 19: 1950010:1-1950010:31 (2019).</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
+          <t xml:space="preserve"> Dichotomy for Symmetric Boolean PCSPs. </t>
         </is>
       </c>
       <c r="C954" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -29029,28 +29029,28 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ICALP.2019.57 </t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
+          <t xml:space="preserve"> 46th International Colloquium on Automata, Languages, and Programming, ICALP 2019, Patras, Greece, July 9-12, 2019: 57:1-57:12 (2019).</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> Topology is relevant (in a dichotomy conjecture for infinite-domain constraint satisfaction problems). </t>
         </is>
       </c>
       <c r="C955" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -29059,28 +29059,28 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/LICS.2019.8785883 </t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
+          <t xml:space="preserve"> 34th Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2019, Vancouver, BC, Canada, June 24-27, 2019: 1-12 (2019).</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Topology is relevant (in the infinite-domain dichotomy conjecture for constraint satisfaction problems). </t>
         </is>
       </c>
       <c r="C956" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -29089,28 +29089,28 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1901.04237 </t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1901.04237 (2019).</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Nicholas Chew </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> QBF proof complexity. </t>
+          <t xml:space="preserve"> Dichotomy for symmetric Boolean PCSPs. </t>
         </is>
       </c>
       <c r="C957" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -29119,24 +29119,24 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.12424 </t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.12424 (2019).</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> The equivalence of two dichotomy conjectures for infinite domain constraint satisfaction problems. </t>
         </is>
       </c>
       <c r="C958" t="n">
@@ -29149,28 +29149,28 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/LICS.2017.8005128 </t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
+          <t xml:space="preserve"> 32nd Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2017, Reykjavik, Iceland, June 20-23, 2017: 1-12 (2017).</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Michael Pinsker, Van Trung Pham </t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
+          <t xml:space="preserve"> Equations in oligomorphic clones and the Constraint Satisfaction Problem for $ω$-categorical structures. </t>
         </is>
       </c>
       <c r="C959" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -29179,28 +29179,28 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1612.07551 </t>
         </is>
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1612.07551 (2016).</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C960" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -29209,28 +29209,28 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
+          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 11176-11184 (2025).</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C961" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -29239,28 +29239,28 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
+          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C962" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -29269,28 +29269,28 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
+          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
         </is>
       </c>
       <c r="C963" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -29299,28 +29299,28 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
+          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C964" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -29329,28 +29329,28 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C965" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -29359,28 +29359,28 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
+          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
         </is>
       </c>
       <c r="C966" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -29389,28 +29389,28 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C967" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -29419,28 +29419,28 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
+          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C968" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -29449,28 +29449,28 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
+          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C969" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -29479,28 +29479,28 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
+          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
         </is>
       </c>
       <c r="C970" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -29509,28 +29509,28 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C971" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -29539,28 +29539,28 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C972" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -29569,28 +29569,28 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
         </is>
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
         </is>
       </c>
       <c r="C973" t="n">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -29599,474 +29599,474 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
+          <t xml:space="preserve"> Zenodo (2023/12)</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
+          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C975" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
+          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
+          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C977" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
+          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C978" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C979" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C980" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C981" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
         </is>
       </c>
       <c r="C982" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
+          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
         </is>
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
+          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
+          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
         </is>
       </c>
       <c r="C984" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C985" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
+          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
         </is>
       </c>
       <c r="C986" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C987" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
+          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C988" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Top-Down Neural Model For Formulae. </t>
+          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -30074,209 +30074,209 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=Byg5QhR5FQ </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7th International Conference on Learning Representations, ICLR 2019, New Orleans, LA, USA, May 6-9, 2019: (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský, Rostislav Horcík </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Full Lambek Calculus with Contraction is Undecidable. </t>
+          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2015.18 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Log. 81: 524-540 (2016).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Undecidability of Consequence Relation in Full non-Associative Lambek Calculus. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C991" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2014.39 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Log. 80: 567-586 (2015).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> On the independence of axioms in BL and MTL. </t>
+          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
         </is>
       </c>
       <c r="C992" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.fss.2011.10.018 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fuzzy Sets Syst. 197: 123-129 (2012).</t>
+          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský, Petr Cintula </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Note on Deduction Theorems in contraction-free logics. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1002/malq.201110065 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Math. Log. Q. 58: 236-243 (2012).</t>
+          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karel Chvalovský, Petr Cintula </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Note on Deduction Theorems in Contraction-Free Logics. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C994" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/c66c </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short papers for 17th International Conference on Logic for Programming, Artificial intelligence, and Reasoning, LPAR-17-short, Yogyakarta, Indonesia, October 10-15, 2010: 26-29 (2010).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Wos Challenge Met. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C995" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114264018 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 66: 565-574 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stepan Holub, Robert Veroff </t>
+          <t xml:space="preserve">Leroy Nicholas Chew </t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Formalizing a Fragment of Combinatorics on Words. </t>
+          <t xml:space="preserve"> QBF proof complexity. </t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -30284,513 +30284,513 @@
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-58741-7_3 </t>
+          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unveiling Dynamics and Complexity - 13th Conference on Computability in Europe, CiE 2017, Turku, Finland, June 12-16, 2017, Proceedings: 24-31 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Spinks, Robert J. Bignall, Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discriminator logics (Research announcement). </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.26686/ajl.v11i2.2020 </t>
+          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Australas. J. Log. 11: (2014).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranganathan Padmanabhan, Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Geometric Procedure with Prover9. </t>
+          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
         </is>
       </c>
       <c r="C998" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_7 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 139-150 (2013).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael K. Kinyon, Robert Veroff, Petr Vojtechovský </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Loops with Abelian Inner Mapping Groups: An Application of Automated Deduction. </t>
+          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
         </is>
       </c>
       <c r="C999" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 151-164 (2013).</t>
+          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francesco Paoli, Matthew Spinks, Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abelian Logic and the Logics of Pointed Lattice-Ordered Varieties. </t>
+          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11787-008-0034-2 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logica Universalis 2: 209-233 (2008).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. I. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9113-x </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 88: 325-348 (2008).</t>
+          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. II. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1002" t="n">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9138-1 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 89: 401-425 (2008).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Gilfeather, Vikas Hamine, Paul Helman, Julie Hutt, Terry Loring, C. Rick Lyons, Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learning and modeling biosignatures from tissue images. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33282059 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Biol. Medicine 37: 1539-1552 (2007).</t>
+          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff, Matthew Spinks </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Axiomatizing the Skew Boolean Propositional Calculus. </t>
+          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-006-9029-y </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 37: 3-20 (2006).</t>
+          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics. </t>
+          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
         </is>
       </c>
       <c r="C1005" t="n">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262834 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 80: 195-234 (2005).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff, Susan R. Atlas, Cheryl Willman </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Bayesian Network Classification Methodology for Gene Expression Data. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>2004</v>
+        <v>2015</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33209551 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Comput. Biol. 11: 581-615 (2004).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Shortest 2-Basis for Boolean Algebra in Terms of the Sheffer Stroke. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1007" t="n">
-        <v>2003</v>
+        <v>2015</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1027322305654 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 31: 1-9 (2003).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/cs/0301026 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR cs.LO/0301026 (2003).</t>
+          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">William McCune, Robert Veroff, Branden Fitelson, Kenneth Harris, Andrew Feist, Larry Wos </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Single Axioms for Boolean Algebra. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q60061107 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
         </is>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 29: 1-16 (2002).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The application of automated reasoning to formal models of combinatorial optimization. </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>2001</v>
+        <v>2014</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q127517130 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Math. Comput. 120: 175-194 (2001).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Finding Shortest Proofs: An Application of Linked Inference Rules. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1011" t="n">
-        <v>2001</v>
+        <v>2014</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1010635625063 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 27: 123-139 (2001).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving Open Questions and Other Challenge Problems Using Proof Sketches. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>2001</v>
+        <v>2014</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1010639725972 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
         </is>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 27: 157-174 (2001).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gregory H. Chisholm, Steven T. Eckmann, Christopher M. Lain, Robert Veroff </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Integrated Circuits. </t>
+          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>1999</v>
+        <v>2022</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -30799,28 +30799,28 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://doi.ieeecomputersociety.org/10.1109/54.765201 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Des. Test Comput. 16: 26-37 (1999).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Using Hints to Increase the Effectiveness of an Automated Reasoning Program: Case Studies. </t>
+          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>1996</v>
+        <v>2021</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -30829,28 +30829,28 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/BF00252178 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
         </is>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 16: 223-239 (1996).</t>
+          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Robert Veroff </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logical basis for the automation of reasoning: Case studies. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>1994</v>
+        <v>2020</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -30859,28 +30859,28 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Handbook of Logic in Artificial Intelligence and Logic Programming, Volume2, Deduction Methodologies: 1-40 (1994).</t>
+          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Linked Inference Principle, I: The Formal Treatment. </t>
+          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>1992</v>
+        <v>2020</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -30889,28 +30889,28 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114267080 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 8: 213-274 (1992).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff, Frank R. Carrano </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intermediate problem solving and data structures - walls and mirrors (2. ed.). </t>
+          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>1991</v>
+        <v>2020</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -30919,28 +30919,28 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Benjamin/Cummings series in computer science, Benjamin/Cummings (1991).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Designing Deductive Databases. </t>
+          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
         </is>
       </c>
       <c r="C1018" t="n">
-        <v>1988</v>
+        <v>2019</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -30949,28 +30949,28 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/BF00244512 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 4: 29-68 (1988).</t>
+          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Steve Winker, Barry Smith, Robert Veroff, Lawrence J. Henschen </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A New Use of an Automated Reasoning Assistant: Open Questions in Equivalential Calculus and the Study of Infinite Domains. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>1984</v>
+        <v>2019</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -30979,28 +30979,28 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262293 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. 22: 303-356 (1984).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Robert Veroff, Barry Smith, William McCune </t>
+          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Linked Inference Principle, II: The User's Viewpoint. </t>
+          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>1984</v>
+        <v>2017</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -31009,28 +31009,28 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-0-387-34768-4_19 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7th International Conference on Automated Deduction, Napa, California, USA, May 14-16, 1984, Proceedings: 316-332 (1984).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Henschen, Barry Smith, Robert Veroff, Steve Winker, Larry Wos </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Questions concerning possible shortest single axioms for the equivalential calculus: an application of automated theorem proving to infinite domains. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>1983</v>
+        <v>2015</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -31039,28 +31039,28 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114254310 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Notre Dame J. Formal Log. 24: 205-223 (1983).</t>
+          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff, Lawrence J. Henschen </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Automatic Transformations to Program Verification. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>1981</v>
+        <v>2015</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -31069,28 +31069,28 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://ijcai.org/Proceedings/81-1/Papers/087.pdf </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 7th International Joint Conference on Artificial Intelligence, IJCAI '81, Vancouver, BC, Canada, August 24-28, 1981: 472-479 (1981).</t>
+          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -31099,28 +31099,28 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
         </is>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beneficial AGI: Care and Collaboration Are All You Need. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -31129,28 +31129,28 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-65572-2_9 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial General Intelligence - 17th International Conference, AGI 2024, Seattle, WA, USA, August 13-16, 2024, Proceedings: 84-88 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sergey Rodionov, Zarathustra Amadeus Goertzel, Ben Goertzel </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Evaluation of GPT-4 on the ETHICS Dataset. </t>
+          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
         </is>
       </c>
       <c r="C1025" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -31159,28 +31159,28 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2309.10492 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
         </is>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2309.10492 (2023).</t>
+          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ben Goertzel, Vitaly Bogdanov, Michael Duncan, Deborah Duong, Zarathustra Amadeus Goertzel, Jan Horlings, Matthew Iklé, Lucius Gregory Meredith, Alexey Potapov, Andre Luiz de Senna, Hedra Seid, Andres Suarez, Adam Vandervorst, Robert Werko </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OpenCog Hyperon: A Framework for AGI at the Human Level and Beyond. </t>
+          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -31189,28 +31189,28 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2310.18318 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
         </is>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2310.18318 (2023).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Make E Smart Again (Short Paper). </t>
+          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -31219,28 +31219,28 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51054-1_26 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
         </is>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part II: 408-415 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
+          <t xml:space="preserve">Lasse Blaauwbroek </t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Make E Smart Again. </t>
+          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -31249,12 +31249,12 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.08858 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2004.08858 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
         </is>
       </c>
     </row>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1192"/>
+  <dimension ref="A1:F1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34386,7 +34386,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -34399,12 +34399,12 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
         </is>
       </c>
       <c r="F1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
         </is>
       </c>
     </row>
@@ -34416,7 +34416,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -34429,28 +34429,28 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
@@ -34459,28 +34459,28 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
@@ -34489,12 +34489,12 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
@@ -34519,28 +34519,28 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
@@ -34549,28 +34549,28 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
@@ -34579,24 +34579,24 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -34609,24 +34609,24 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -34639,28 +34639,28 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
@@ -34669,24 +34669,24 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1143" t="n">
@@ -34699,24 +34699,24 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1144" t="n">
@@ -34729,24 +34729,24 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -34759,24 +34759,24 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1146" t="n">
@@ -34789,24 +34789,24 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -34819,24 +34819,24 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1148" t="n">
@@ -34849,28 +34849,28 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
@@ -34879,24 +34879,24 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -34909,24 +34909,24 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -34939,24 +34939,24 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1152" t="n">
@@ -34969,24 +34969,24 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -34999,24 +34999,24 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1154" t="n">
@@ -35029,28 +35029,28 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1155" t="inlineStr">
         <is>
@@ -35059,24 +35059,24 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1156" t="n">
@@ -35089,24 +35089,24 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1157" t="n">
@@ -35119,28 +35119,28 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1158" t="inlineStr">
         <is>
@@ -35149,28 +35149,28 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
@@ -35179,28 +35179,28 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
@@ -35209,24 +35209,24 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1161" t="n">
@@ -35239,24 +35239,24 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -35269,28 +35269,28 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1163" t="inlineStr">
         <is>
@@ -35299,12 +35299,12 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
@@ -35316,7 +35316,7 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1164" t="n">
@@ -35329,28 +35329,28 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
@@ -35359,12 +35359,12 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
@@ -35376,7 +35376,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1166" t="n">
@@ -35389,24 +35389,24 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1167" t="n">
@@ -35419,24 +35419,24 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -35449,28 +35449,28 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
@@ -35479,28 +35479,28 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
@@ -35509,12 +35509,12 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
@@ -35526,11 +35526,11 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
@@ -35539,24 +35539,24 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1172" t="n">
@@ -35569,28 +35569,28 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
@@ -35599,24 +35599,24 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1174" t="n">
@@ -35629,28 +35629,28 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1175" t="inlineStr">
         <is>
@@ -35659,28 +35659,28 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
@@ -35689,28 +35689,28 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
@@ -35719,24 +35719,24 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1178" t="n">
@@ -35749,24 +35749,24 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -35779,24 +35779,24 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1180" t="n">
@@ -35809,28 +35809,28 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
@@ -35839,24 +35839,24 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1182" t="n">
@@ -35869,7 +35869,7 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1182" t="inlineStr">
@@ -35881,12 +35881,12 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1183" t="n">
@@ -35899,24 +35899,24 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -35929,24 +35929,24 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -35959,24 +35959,24 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1186" t="n">
@@ -35989,28 +35989,28 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
@@ -36019,12 +36019,12 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -36049,28 +36049,28 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
@@ -36079,24 +36079,24 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1190" t="n">
@@ -36109,28 +36109,28 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
@@ -36139,40 +36139,70 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1192" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1192" t="inlineStr">
+      <c r="B1193" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1192" t="n">
+      <c r="C1193" t="n">
         <v>2021</v>
       </c>
-      <c r="D1192" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1192" t="inlineStr">
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1192" t="inlineStr">
+      <c r="F1193" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1193"/>
+  <dimension ref="A1:F1194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28591,7 +28591,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
+          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang H. Nguyen, Marcelo Menegali, Junehyuk Jung, Junsu Kim, Vikas Verma, Quoc V. Le, Thang Luong </t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -28609,54 +28609,54 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2502.03544 </t>
+          <t xml:space="preserve"> https://jmlr.org/papers/v26/25-1654.html </t>
         </is>
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2502.03544 (2025/02).</t>
+          <t xml:space="preserve"> J. Mach. Learn. Res. 26: 241:1-241:39 (2025).</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
+          <t xml:space="preserve"> Gold-medalist Performance in Solving Olympiad Geometry with AlphaGeometry2. </t>
         </is>
       </c>
       <c r="C941" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2502.03544 </t>
         </is>
       </c>
       <c r="F941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2502.03544 (2025/02).</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simon Frieder, Mirek Olsák, Julius Berner, Thomas Lukasiewicz </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The IMO Small Challenge: Not-Too-Hard Olympiad Math Datasets for LLMs. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -28664,29 +28664,29 @@
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=HYuKXhgzjm </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
         </is>
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Second Tiny Papers Track at ICLR 2024, Tiny Papers @ ICLR 2024, Vienna, Austria, May 11, 2024: (2024).</t>
+          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Simon Frieder, Mirek Olsák, Julius Berner, Thomas Lukasiewicz </t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
+          <t xml:space="preserve"> The IMO Small Challenge: Not-Too-Hard Olympiad Math Datasets for LLMs. </t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -28694,29 +28694,29 @@
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=HYuKXhgzjm </t>
         </is>
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
+          <t xml:space="preserve"> The Second Tiny Papers Track at ICLR 2024, Tiny Papers @ ICLR 2024, Vienna, Austria, May 11, 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
+          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -28729,24 +28729,24 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
         </is>
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
+          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -28759,54 +28759,54 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
         </is>
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Erratum: Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
+          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
         </is>
       </c>
       <c r="C946" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1142/S021906132192001X </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
         </is>
       </c>
       <c r="F946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Math. Log. 21: (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Maltsev conditions for General Congruence Meet-semidistributive Algebras. </t>
+          <t xml:space="preserve"> Erratum: Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -28819,24 +28819,24 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2021.14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1142/S021906132192001X </t>
         </is>
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Log. 86: 1432-1451 (2021).</t>
+          <t xml:space="preserve"> J. Math. Log. 21: (2021).</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Miroslav Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
+          <t xml:space="preserve"> Maltsev conditions for General Congruence Meet-semidistributive Algebras. </t>
         </is>
       </c>
       <c r="C948" t="n">
@@ -28849,19 +28849,19 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://proceedings.neurips.cc/paper/2021/hash/cf708fc1decf0337aded484f8f4519ae-Abstract.html </t>
+          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2021.14 </t>
         </is>
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 34: Annual Conference on Neural Information Processing Systems 2021, NeurIPS 2021, December 6-14, 2021, virtual.: 24707-24718 (2021).</t>
+          <t xml:space="preserve"> J. Symb. Log. 86: 1432-1451 (2021).</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Mirek Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Marco Bagatella, Miroslav Olsák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -28879,28 +28879,28 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2110.06149 </t>
+          <t xml:space="preserve"> https://proceedings.neurips.cc/paper/2021/hash/cf708fc1decf0337aded484f8f4519ae-Abstract.html </t>
         </is>
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2110.06149 (2021).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 34: Annual Conference on Neural Information Processing Systems 2021, NeurIPS 2021, December 6-14, 2021, virtual.: 24707-24718 (2021).</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Marco Bagatella, Mirek Olsák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Loop conditions for strongly connected digraphs. </t>
+          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
         </is>
       </c>
       <c r="C950" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -28909,12 +28909,12 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114614801 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2110.06149 </t>
         </is>
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Int. J. Algebra Comput. 30: 467-499 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2110.06149 (2021).</t>
         </is>
       </c>
     </row>
@@ -28926,7 +28926,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GeoLogic - Graphical Interactive Theorem Prover for Euclidean Geometry. </t>
+          <t xml:space="preserve"> Loop conditions for strongly connected digraphs. </t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -28939,12 +28939,12 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-52200-1_26 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114614801 </t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mathematical Software - ICMS 2020 - 7th International Conference, Braunschweig, Germany, July 13-16, 2020, Proceedings: 263-271 (2020).</t>
+          <t xml:space="preserve"> Int. J. Algebra Comput. 30: 467-499 (2020).</t>
         </is>
       </c>
     </row>
@@ -28956,7 +28956,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GeoLogic - Graphical interactive theorem prover for Euclidean geometry. </t>
+          <t xml:space="preserve"> GeoLogic - Graphical Interactive Theorem Prover for Euclidean Geometry. </t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -28969,24 +28969,24 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.03586 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-52200-1_26 </t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.03586 (2020).</t>
+          <t xml:space="preserve"> Mathematical Software - ICMS 2020 - 7th International Conference, Braunschweig, Germany, July 13-16, 2020, Proceedings: 263-271 (2020).</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ω-categorical structures avoiding height 1 identities. </t>
+          <t xml:space="preserve"> GeoLogic - Graphical interactive theorem prover for Euclidean geometry. </t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -28999,28 +28999,28 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2006.12254 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.03586 </t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2006.12254 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.03586 (2020).</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Van Trung Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
+          <t xml:space="preserve"> ω-categorical structures avoiding height 1 identities. </t>
         </is>
       </c>
       <c r="C954" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -29029,24 +29029,24 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1142/S0219061319500107 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2006.12254 </t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Math. Log. 19: 1950010:1-1950010:31 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2006.12254 (2020).</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Van Trung Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dichotomy for Symmetric Boolean PCSPs. </t>
+          <t xml:space="preserve"> Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -29059,24 +29059,24 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ICALP.2019.57 </t>
+          <t xml:space="preserve"> https://doi.org/10.1142/S0219061319500107 </t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 46th International Colloquium on Automata, Languages, and Programming, ICALP 2019, Patras, Greece, July 9-12, 2019: 57:1-57:12 (2019).</t>
+          <t xml:space="preserve"> J. Math. Log. 19: 1950010:1-1950010:31 (2019).</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Topology is relevant (in a dichotomy conjecture for infinite-domain constraint satisfaction problems). </t>
+          <t xml:space="preserve"> Dichotomy for Symmetric Boolean PCSPs. </t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -29089,12 +29089,12 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/LICS.2019.8785883 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ICALP.2019.57 </t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 34th Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2019, Vancouver, BC, Canada, June 24-27, 2019: 1-12 (2019).</t>
+          <t xml:space="preserve"> 46th International Colloquium on Automata, Languages, and Programming, ICALP 2019, Patras, Greece, July 9-12, 2019: 57:1-57:12 (2019).</t>
         </is>
       </c>
     </row>
@@ -29106,7 +29106,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Topology is relevant (in the infinite-domain dichotomy conjecture for constraint satisfaction problems). </t>
+          <t xml:space="preserve"> Topology is relevant (in a dichotomy conjecture for infinite-domain constraint satisfaction problems). </t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -29119,24 +29119,24 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1901.04237 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/LICS.2019.8785883 </t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1901.04237 (2019).</t>
+          <t xml:space="preserve"> 34th Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2019, Vancouver, BC, Canada, June 24-27, 2019: 1-12 (2019).</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dichotomy for symmetric Boolean PCSPs. </t>
+          <t xml:space="preserve"> Topology is relevant (in the infinite-domain dichotomy conjecture for constraint satisfaction problems). </t>
         </is>
       </c>
       <c r="C958" t="n">
@@ -29149,28 +29149,28 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.12424 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1901.04237 </t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.12424 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1901.04237 (2019).</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The equivalence of two dichotomy conjectures for infinite domain constraint satisfaction problems. </t>
+          <t xml:space="preserve"> Dichotomy for symmetric Boolean PCSPs. </t>
         </is>
       </c>
       <c r="C959" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -29179,28 +29179,28 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/LICS.2017.8005128 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.12424 </t>
         </is>
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 32nd Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2017, Reykjavik, Iceland, June 20-23, 2017: 1-12 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.12424 (2019).</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Michael Pinsker, Van Trung Pham </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Equations in oligomorphic clones and the Constraint Satisfaction Problem for $ω$-categorical structures. </t>
+          <t xml:space="preserve"> The equivalence of two dichotomy conjectures for infinite domain constraint satisfaction problems. </t>
         </is>
       </c>
       <c r="C960" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -29209,28 +29209,28 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1612.07551 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/LICS.2017.8005128 </t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1612.07551 (2016).</t>
+          <t xml:space="preserve"> 32nd Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2017, Reykjavik, Iceland, June 20-23, 2017: 1-12 (2017).</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Michael Pinsker, Van Trung Pham </t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> Equations in oligomorphic clones and the Constraint Satisfaction Problem for $ω$-categorical structures. </t>
         </is>
       </c>
       <c r="C961" t="n">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -29239,24 +29239,24 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1612.07551 </t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 11176-11184 (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1612.07551 (2016).</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -29269,24 +29269,24 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
+          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 11176-11184 (2025).</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C963" t="n">
@@ -29299,24 +29299,24 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
+          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -29329,24 +29329,24 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
+          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -29359,24 +29359,24 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
+          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -29389,24 +29389,24 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C967" t="n">
@@ -29419,28 +29419,28 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
         </is>
       </c>
       <c r="C968" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -29449,24 +29449,24 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C969" t="n">
@@ -29479,24 +29479,24 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
+          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -29509,24 +29509,24 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
+          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C971" t="n">
@@ -29539,24 +29539,24 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
+          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -29569,24 +29569,24 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
         </is>
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
+          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -29599,28 +29599,28 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -29629,24 +29629,24 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2023/12)</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
+          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -29659,24 +29659,24 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
+          <t xml:space="preserve"> Zenodo (2023/12)</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
         </is>
       </c>
       <c r="C976" t="n">
@@ -29689,7 +29689,7 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
@@ -29701,16 +29701,16 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C977" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -29719,24 +29719,24 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -29749,12 +29749,12 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
+          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
         </is>
       </c>
     </row>
@@ -29779,28 +29779,28 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
+          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C980" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -29809,24 +29809,24 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -29839,24 +29839,24 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C982" t="n">
@@ -29869,28 +29869,28 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
+          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -29899,24 +29899,24 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
         </is>
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -29929,24 +29929,24 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
+          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C985" t="n">
@@ -29959,24 +29959,24 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
+          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -29989,24 +29989,24 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -30019,28 +30019,28 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
         </is>
       </c>
       <c r="C988" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -30049,24 +30049,24 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -30079,24 +30079,24 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
+          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C990" t="n">
@@ -30109,12 +30109,12 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
         </is>
       </c>
     </row>
@@ -30139,12 +30139,12 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
         </is>
       </c>
     </row>
@@ -30156,7 +30156,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
         </is>
       </c>
       <c r="C992" t="n">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
@@ -30181,16 +30181,16 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -30199,12 +30199,12 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
         </is>
       </c>
     </row>
@@ -30216,7 +30216,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
+          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -30229,24 +30229,24 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
+          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -30259,24 +30259,24 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
+          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -30289,7 +30289,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
@@ -30301,16 +30301,16 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Nicholas Chew </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> QBF proof complexity. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -30319,24 +30319,24 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Nicholas Chew </t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> QBF proof complexity. </t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -30349,12 +30349,12 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
+          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
@@ -30366,7 +30366,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -30379,12 +30379,12 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
+          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
         </is>
       </c>
     </row>
@@ -30400,7 +30400,7 @@
         </is>
       </c>
       <c r="C1000" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -30409,24 +30409,24 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
+          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
         </is>
       </c>
       <c r="C1001" t="n">
@@ -30439,24 +30439,24 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
+          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -30469,12 +30469,12 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
         </is>
       </c>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1003" t="n">
@@ -30499,12 +30499,12 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
+          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
         </is>
       </c>
     </row>
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="C1004" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -30529,24 +30529,24 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -30559,24 +30559,24 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
+          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
+          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -30589,24 +30589,24 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
+          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
         </is>
       </c>
       <c r="C1007" t="n">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -30649,7 +30649,7 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
@@ -30661,16 +30661,16 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1009" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -30679,12 +30679,12 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
         </is>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
         </is>
       </c>
     </row>
@@ -30696,7 +30696,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -30709,12 +30709,12 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
+          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
         </is>
       </c>
     </row>
@@ -30726,7 +30726,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -30739,12 +30739,12 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
         </is>
       </c>
     </row>
@@ -30756,7 +30756,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1012" t="n">
@@ -30769,7 +30769,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
         </is>
       </c>
       <c r="F1012" t="inlineStr">
@@ -30781,12 +30781,12 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1013" t="n">
@@ -30799,7 +30799,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
@@ -30811,30 +30811,30 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
         </is>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
         </is>
       </c>
     </row>
@@ -30846,11 +30846,11 @@
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
+          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
         </is>
       </c>
     </row>
@@ -30876,11 +30876,11 @@
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
+          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
         </is>
       </c>
       <c r="C1016" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -30889,12 +30889,12 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
         </is>
       </c>
     </row>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C1017" t="n">
@@ -30919,12 +30919,12 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
+          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
         </is>
       </c>
     </row>
@@ -30949,28 +30949,28 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
+          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -30979,24 +30979,24 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
+          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
         </is>
       </c>
       <c r="C1020" t="n">
@@ -31009,28 +31009,28 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
+          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -31039,28 +31039,28 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -31069,12 +31069,12 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
         </is>
       </c>
     </row>
@@ -31086,7 +31086,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -31099,12 +31099,12 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
         </is>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
+          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
         </is>
       </c>
     </row>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -31129,12 +31129,12 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
+          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
         </is>
       </c>
     </row>
@@ -31146,7 +31146,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -31159,28 +31159,28 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
         </is>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -31189,24 +31189,24 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
         </is>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
+          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -31219,12 +31219,12 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
         </is>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
+          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
         </is>
       </c>
     </row>
@@ -31236,7 +31236,7 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
+          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -31249,28 +31249,28 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
+          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -31279,28 +31279,28 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
         </is>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Lasse Blaauwbroek </t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
         </is>
       </c>
       <c r="C1030" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -31309,12 +31309,12 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
         </is>
       </c>
     </row>
@@ -31326,11 +31326,11 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
+          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1031" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -31339,12 +31339,12 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
         </is>
       </c>
     </row>
@@ -31356,7 +31356,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
         </is>
       </c>
       <c r="C1032" t="n">
@@ -31369,12 +31369,12 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
         </is>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
+          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1033" t="n">
@@ -31399,12 +31399,12 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
         </is>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
         </is>
       </c>
     </row>
@@ -31416,7 +31416,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -31429,12 +31429,12 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
         </is>
       </c>
     </row>
@@ -31446,7 +31446,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -31459,12 +31459,12 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
         </is>
       </c>
     </row>
@@ -31476,7 +31476,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
+          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -31489,12 +31489,12 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
         </is>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
         </is>
       </c>
     </row>
@@ -31506,7 +31506,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -31519,12 +31519,12 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
         </is>
       </c>
     </row>
@@ -31536,11 +31536,11 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1038" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -31549,12 +31549,12 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
         </is>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
         </is>
       </c>
     </row>
@@ -31566,7 +31566,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -31579,12 +31579,12 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
         </is>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
+          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
         </is>
       </c>
     </row>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -31609,12 +31609,12 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
         </is>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
         </is>
       </c>
     </row>
@@ -31626,7 +31626,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -31639,12 +31639,12 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
         </is>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31656,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Designing Game of Theorems. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -31669,12 +31669,12 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
         </is>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
         </is>
       </c>
     </row>
@@ -31686,7 +31686,7 @@
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
+          <t xml:space="preserve"> Designing Game of Theorems. </t>
         </is>
       </c>
       <c r="C1043" t="n">
@@ -31699,28 +31699,28 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
         </is>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -31729,24 +31729,24 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
         </is>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
+          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -31759,12 +31759,12 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
         </is>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
+          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
         </is>
       </c>
     </row>
@@ -31789,24 +31789,24 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
         </is>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -31819,24 +31819,24 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
+          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -31849,28 +31849,28 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
         </is>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
         </is>
       </c>
       <c r="C1049" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -31879,24 +31879,24 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
         </is>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1050" t="n">
@@ -31909,12 +31909,12 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
         </is>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
         </is>
       </c>
     </row>
@@ -31926,11 +31926,11 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Strategy Language. </t>
+          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
         </is>
       </c>
       <c r="C1051" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -31939,24 +31939,24 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
         </is>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
+          <t xml:space="preserve"> Proof Strategy Language. </t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -31969,24 +31969,24 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
         </is>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
+          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
+          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -31999,24 +31999,24 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
+          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
+          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
         </is>
       </c>
       <c r="C1054" t="n">
@@ -32029,24 +32029,24 @@
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
         </is>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
+          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
+          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -32059,24 +32059,24 @@
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
         </is>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
+          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
+          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -32089,24 +32089,24 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
         </is>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -32119,54 +32119,54 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
         </is>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
+          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
+          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
+          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
         </is>
       </c>
       <c r="C1059" t="n">
@@ -32179,19 +32179,19 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
@@ -32209,28 +32209,28 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -32239,24 +32239,24 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
         </is>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -32269,24 +32269,24 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
         </is>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
+          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -32299,28 +32299,28 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
         </is>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -32329,28 +32329,28 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
         </is>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
+          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
+          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
         </is>
       </c>
       <c r="C1065" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -32359,24 +32359,24 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
         </is>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
+          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
+          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
+          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -32389,28 +32389,28 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
         </is>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
+          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
+          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1067" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -32419,24 +32419,24 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
         </is>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
+          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -32449,24 +32449,24 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
         </is>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
+          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -32479,12 +32479,12 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
         </is>
       </c>
     </row>
@@ -32496,7 +32496,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -32509,24 +32509,24 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
         </is>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
+          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C1071" t="n">
@@ -32539,28 +32539,28 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
+          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1072" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -32569,24 +32569,24 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
         </is>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -32599,19 +32599,19 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
         </is>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
+          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
@@ -32629,24 +32629,24 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
         </is>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2025/08)</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -32659,24 +32659,24 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
         </is>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
+          <t xml:space="preserve"> Zenodo (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -32689,58 +32689,58 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
         </is>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Frantisek Dusek, Marco Tuccio, Clément Hongler </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Visualizing the Structure of Lenia Parameter Space. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FAI </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2601.01932 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
         </is>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2601.01932 (2026/01).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
+          <t xml:space="preserve">Barbora Hudcová, Frantisek Dusek, Marco Tuccio, Clément Hongler </t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
+          <t xml:space="preserve"> Visualizing the Structure of Lenia Parameter Space. </t>
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -32749,24 +32749,24 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2601.01932 </t>
         </is>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2601.01932 (2026/01).</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
+          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
+          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -32779,28 +32779,28 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
+          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
+          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -32809,24 +32809,24 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
+          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
+          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -32839,12 +32839,12 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
+          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
         </is>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
+          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
         </is>
       </c>
     </row>
@@ -32856,11 +32856,11 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
+          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -32869,54 +32869,54 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
+          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
+          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
+          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
         </is>
       </c>
       <c r="C1083" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ML </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
         </is>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
+          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
+          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
         </is>
       </c>
       <c r="C1084" t="n">
@@ -32929,28 +32929,28 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
         </is>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
+          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
+          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -32959,28 +32959,28 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
         </is>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
+          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
+          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
         </is>
       </c>
       <c r="C1086" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -32989,24 +32989,24 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
+          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
         </is>
       </c>
       <c r="C1087" t="n">
@@ -33019,28 +33019,28 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
+          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
         </is>
       </c>
       <c r="C1088" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -33049,24 +33049,24 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
+          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -33079,7 +33079,7 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
@@ -33091,16 +33091,16 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
+          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -33109,28 +33109,28 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
+          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
+          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -33139,12 +33139,12 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
         </is>
       </c>
     </row>
@@ -33160,7 +33160,7 @@
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -33169,24 +33169,24 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sensors 19: (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
+          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
         </is>
       </c>
       <c r="C1093" t="n">
@@ -33199,28 +33199,28 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
+          <t xml:space="preserve"> Sensors 19: (2019).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
+          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -33229,28 +33229,28 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
+          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
+          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
+          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -33259,24 +33259,24 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
+          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
+          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -33289,28 +33289,28 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
+          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
+          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -33319,24 +33319,24 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
+          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
+          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
         </is>
       </c>
       <c r="C1098" t="n">
@@ -33349,24 +33349,24 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
+          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
+          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -33379,28 +33379,28 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
+          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -33409,24 +33409,24 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
+          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
+          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -33439,24 +33439,24 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
+          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
+          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
+          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -33469,24 +33469,24 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
+          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
+          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
         </is>
       </c>
       <c r="C1103" t="n">
@@ -33499,28 +33499,28 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
+          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -33529,24 +33529,24 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -33559,24 +33559,24 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
+          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
+          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -33589,24 +33589,24 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
+          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
+          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -33619,28 +33619,28 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
+          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
+          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
@@ -33649,24 +33649,24 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
+          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
+          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -33679,24 +33679,24 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
         </is>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
+          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1110" t="n">
@@ -33709,24 +33709,24 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
         </is>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -33739,24 +33739,24 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
         </is>
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -33769,24 +33769,24 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
+          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
         </is>
       </c>
       <c r="C1113" t="n">
@@ -33799,24 +33799,24 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -33829,28 +33829,28 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D1115" t="inlineStr">
         <is>
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
         </is>
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
         </is>
       </c>
     </row>
@@ -33876,7 +33876,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
+          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -33889,12 +33889,12 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
         </is>
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
         </is>
       </c>
     </row>
@@ -33906,7 +33906,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -33919,24 +33919,24 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
         </is>
       </c>
       <c r="F1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
+          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -33949,28 +33949,28 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
         </is>
       </c>
       <c r="F1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
+          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D1119" t="inlineStr">
         <is>
@@ -33979,28 +33979,28 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
         </is>
       </c>
       <c r="F1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
+          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
@@ -34009,28 +34009,28 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
         </is>
       </c>
       <c r="F1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
@@ -34039,24 +34039,24 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
         </is>
       </c>
       <c r="F1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
+          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -34069,24 +34069,24 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
         </is>
       </c>
       <c r="F1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
+          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
+          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -34099,28 +34099,28 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
         </is>
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
+          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
+          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
@@ -34129,24 +34129,24 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
         </is>
       </c>
       <c r="F1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
+          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
+          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
         </is>
       </c>
       <c r="C1125" t="n">
@@ -34159,28 +34159,28 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
         </is>
       </c>
       <c r="F1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
+          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
+          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
+          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
@@ -34189,24 +34189,24 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
         </is>
       </c>
       <c r="F1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
+          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
         </is>
       </c>
       <c r="C1127" t="n">
@@ -34219,24 +34219,24 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
         </is>
       </c>
       <c r="F1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
+          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
+          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
+          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -34249,28 +34249,28 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
         </is>
       </c>
       <c r="F1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
+          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D1129" t="inlineStr">
         <is>
@@ -34279,28 +34279,28 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
         </is>
       </c>
       <c r="F1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
+          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
@@ -34309,24 +34309,24 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
         </is>
       </c>
       <c r="F1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
+          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
+          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
         </is>
       </c>
       <c r="C1131" t="n">
@@ -34339,24 +34339,24 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
         </is>
       </c>
       <c r="F1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
+          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
+          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
         </is>
       </c>
       <c r="C1132" t="n">
@@ -34374,23 +34374,23 @@
       </c>
       <c r="F1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
+          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
+          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
+          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>2026</v>
+        <v>2002</v>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
@@ -34399,12 +34399,12 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
+          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
         </is>
       </c>
     </row>
@@ -34416,7 +34416,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
         </is>
       </c>
     </row>
@@ -34446,7 +34446,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
         </is>
       </c>
       <c r="C1135" t="n">
@@ -34459,28 +34459,28 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
@@ -34489,28 +34489,28 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
@@ -34519,12 +34519,12 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
@@ -34549,28 +34549,28 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
@@ -34579,28 +34579,28 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
@@ -34609,24 +34609,24 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -34639,24 +34639,24 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1142" t="n">
@@ -34669,28 +34669,28 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
@@ -34699,24 +34699,24 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1144" t="n">
@@ -34729,24 +34729,24 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -34759,24 +34759,24 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1146" t="n">
@@ -34789,24 +34789,24 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -34819,24 +34819,24 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1148" t="n">
@@ -34849,24 +34849,24 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1149" t="n">
@@ -34879,28 +34879,28 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1150" t="inlineStr">
         <is>
@@ -34909,24 +34909,24 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -34939,24 +34939,24 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1152" t="n">
@@ -34969,24 +34969,24 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -34999,24 +34999,24 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1154" t="n">
@@ -35029,24 +35029,24 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -35059,28 +35059,28 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
@@ -35089,24 +35089,24 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1157" t="n">
@@ -35119,24 +35119,24 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -35149,28 +35149,28 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
@@ -35179,28 +35179,28 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
@@ -35209,28 +35209,28 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
@@ -35239,24 +35239,24 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -35269,24 +35269,24 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1163" t="n">
@@ -35299,28 +35299,28 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1164" t="inlineStr">
         <is>
@@ -35329,12 +35329,12 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
@@ -35346,7 +35346,7 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1165" t="n">
@@ -35359,28 +35359,28 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
@@ -35389,12 +35389,12 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
@@ -35406,7 +35406,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1167" t="n">
@@ -35419,24 +35419,24 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -35449,24 +35449,24 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1169" t="n">
@@ -35479,28 +35479,28 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
@@ -35509,28 +35509,28 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
@@ -35539,12 +35539,12 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
@@ -35556,11 +35556,11 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
@@ -35569,24 +35569,24 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1173" t="n">
@@ -35599,28 +35599,28 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
@@ -35629,24 +35629,24 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1175" t="n">
@@ -35659,28 +35659,28 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
@@ -35689,28 +35689,28 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
@@ -35719,28 +35719,28 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
@@ -35749,24 +35749,24 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -35779,24 +35779,24 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1180" t="n">
@@ -35809,24 +35809,24 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1181" t="n">
@@ -35839,28 +35839,28 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
@@ -35869,24 +35869,24 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1183" t="n">
@@ -35899,7 +35899,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1183" t="inlineStr">
@@ -35911,12 +35911,12 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -35929,24 +35929,24 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -35959,24 +35959,24 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1186" t="n">
@@ -35989,24 +35989,24 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1187" t="n">
@@ -36019,28 +36019,28 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
@@ -36049,12 +36049,12 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -36079,28 +36079,28 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
@@ -36109,24 +36109,24 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1191" t="n">
@@ -36139,28 +36139,28 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
@@ -36169,40 +36169,70 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1193" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1193" t="inlineStr">
+      <c r="B1194" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1193" t="n">
+      <c r="C1194" t="n">
         <v>2021</v>
       </c>
-      <c r="D1193" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1193" t="inlineStr">
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1193" t="inlineStr">
+      <c r="F1194" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 649-657 (2025).</t>
+          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 649-657 (2025).</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 11194-11202 (2025).</t>
+          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 11194-11202 (2025).</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 11246-11254 (2025).</t>
+          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 11246-11254 (2025).</t>
         </is>
       </c>
     </row>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AAAI-25, Sponsored by the Association for the Advancement of Artificial Intelligence, February 25 - March 4, 2025, Philadelphia, PA, USA: 11176-11184 (2025).</t>
+          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 11176-11184 (2025).</t>
         </is>
       </c>
     </row>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1194"/>
+  <dimension ref="A1:F1195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33061,16 +33061,16 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Erik Derner </t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
+          <t xml:space="preserve"> Efektivní metody pro učení modelů a řízení v robotice ; Data-efficient methods for model learning and control in robotics. </t>
         </is>
       </c>
       <c r="C1089" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -33079,24 +33079,24 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
+          <t xml:space="preserve"> https://www.base-search.net/Record/3b90c2a04826d994a37adc80910808ac880f4b67e04d4782e78b8061204064db </t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
+          <t xml:space="preserve"> Thesis (2022).</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
+          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -33109,7 +33109,7 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
@@ -33121,16 +33121,16 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
+          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -33139,28 +33139,28 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
+          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
+          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -33169,12 +33169,12 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
         </is>
       </c>
     </row>
@@ -33190,7 +33190,7 @@
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -33199,24 +33199,24 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sensors 19: (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
+          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -33229,28 +33229,28 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
+          <t xml:space="preserve"> Sensors 19: (2019).</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
+          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -33259,28 +33259,28 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
+          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
+          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
+          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -33289,24 +33289,24 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
+          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
+          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
         </is>
       </c>
       <c r="C1097" t="n">
@@ -33319,28 +33319,28 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
+          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
+          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -33349,24 +33349,24 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
+          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
+          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -33379,24 +33379,24 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
+          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
+          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
         </is>
       </c>
       <c r="C1100" t="n">
@@ -33409,28 +33409,28 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
+          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -33439,24 +33439,24 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
+          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
+          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -33469,24 +33469,24 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
+          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
+          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
+          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
         </is>
       </c>
       <c r="C1103" t="n">
@@ -33499,24 +33499,24 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
+          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
+          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -33529,28 +33529,28 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
+          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -33559,24 +33559,24 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -33589,24 +33589,24 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
+          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
+          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -33619,24 +33619,24 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
+          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
+          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -33649,28 +33649,28 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
+          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
+          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1109" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
@@ -33679,24 +33679,24 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
         </is>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
+          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
+          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
         </is>
       </c>
       <c r="C1110" t="n">
@@ -33709,24 +33709,24 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
         </is>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
+          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -33739,24 +33739,24 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
         </is>
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -33769,24 +33769,24 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1113" t="n">
@@ -33799,24 +33799,24 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
+          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -33829,24 +33829,24 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
         </is>
       </c>
       <c r="C1115" t="n">
@@ -33859,28 +33859,28 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
         </is>
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
@@ -33889,12 +33889,12 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
         </is>
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
         </is>
       </c>
     </row>
@@ -33906,7 +33906,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
+          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -33919,12 +33919,12 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
         </is>
       </c>
       <c r="F1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
         </is>
       </c>
     </row>
@@ -33936,7 +33936,7 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -33949,24 +33949,24 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
         </is>
       </c>
       <c r="F1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
+          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1119" t="n">
@@ -33979,28 +33979,28 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
         </is>
       </c>
       <c r="F1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
+          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
@@ -34009,28 +34009,28 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
         </is>
       </c>
       <c r="F1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
+          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
@@ -34039,28 +34039,28 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
         </is>
       </c>
       <c r="F1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
@@ -34069,24 +34069,24 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
         </is>
       </c>
       <c r="F1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
+          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -34099,24 +34099,24 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
         </is>
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
+          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
+          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -34129,28 +34129,28 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
         </is>
       </c>
       <c r="F1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
+          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
+          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
@@ -34159,24 +34159,24 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
         </is>
       </c>
       <c r="F1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
+          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
+          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
         </is>
       </c>
       <c r="C1126" t="n">
@@ -34189,28 +34189,28 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
         </is>
       </c>
       <c r="F1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
+          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
+          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
+          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
@@ -34219,24 +34219,24 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
         </is>
       </c>
       <c r="F1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
+          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -34249,24 +34249,24 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
         </is>
       </c>
       <c r="F1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
+          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
+          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
+          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
         </is>
       </c>
       <c r="C1129" t="n">
@@ -34279,28 +34279,28 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
         </is>
       </c>
       <c r="F1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
+          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
@@ -34309,28 +34309,28 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
         </is>
       </c>
       <c r="F1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
+          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
@@ -34339,24 +34339,24 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
         </is>
       </c>
       <c r="F1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
+          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
+          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
         </is>
       </c>
       <c r="C1132" t="n">
@@ -34369,24 +34369,24 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
         </is>
       </c>
       <c r="F1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
+          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
+          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -34404,23 +34404,23 @@
       </c>
       <c r="F1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
+          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
+          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
+          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>2026</v>
+        <v>2002</v>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
+          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
         </is>
       </c>
     </row>
@@ -34446,7 +34446,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
         </is>
       </c>
       <c r="C1135" t="n">
@@ -34459,12 +34459,12 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
         </is>
       </c>
     </row>
@@ -34476,7 +34476,7 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
         </is>
       </c>
       <c r="C1136" t="n">
@@ -34489,28 +34489,28 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
@@ -34519,28 +34519,28 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
         </is>
       </c>
       <c r="F1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
@@ -34549,12 +34549,12 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
@@ -34579,28 +34579,28 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
@@ -34609,28 +34609,28 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
@@ -34639,24 +34639,24 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1142" t="n">
@@ -34669,24 +34669,24 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1143" t="n">
@@ -34699,28 +34699,28 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
@@ -34729,24 +34729,24 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -34759,24 +34759,24 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1146" t="n">
@@ -34789,24 +34789,24 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -34819,24 +34819,24 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1148" t="n">
@@ -34849,24 +34849,24 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1149" t="n">
@@ -34879,24 +34879,24 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -34909,28 +34909,28 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1151" t="inlineStr">
         <is>
@@ -34939,24 +34939,24 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1152" t="n">
@@ -34969,24 +34969,24 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -34999,24 +34999,24 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1154" t="n">
@@ -35029,24 +35029,24 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -35059,24 +35059,24 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1156" t="n">
@@ -35089,28 +35089,28 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1157" t="inlineStr">
         <is>
@@ -35119,24 +35119,24 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -35149,24 +35149,24 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1159" t="n">
@@ -35179,28 +35179,28 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
@@ -35209,28 +35209,28 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
@@ -35239,28 +35239,28 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
@@ -35269,24 +35269,24 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1163" t="n">
@@ -35299,24 +35299,24 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1164" t="n">
@@ -35329,28 +35329,28 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
@@ -35359,12 +35359,12 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
@@ -35376,7 +35376,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1166" t="n">
@@ -35389,28 +35389,28 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
@@ -35419,12 +35419,12 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -35449,24 +35449,24 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1169" t="n">
@@ -35479,24 +35479,24 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1170" t="n">
@@ -35509,28 +35509,28 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
@@ -35539,28 +35539,28 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
@@ -35569,12 +35569,12 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
@@ -35586,11 +35586,11 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
@@ -35599,24 +35599,24 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1174" t="n">
@@ -35629,28 +35629,28 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1175" t="inlineStr">
         <is>
@@ -35659,24 +35659,24 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1176" t="n">
@@ -35689,28 +35689,28 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
@@ -35719,28 +35719,28 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
@@ -35749,28 +35749,28 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
@@ -35779,24 +35779,24 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1180" t="n">
@@ -35809,24 +35809,24 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1181" t="n">
@@ -35839,24 +35839,24 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1182" t="n">
@@ -35869,28 +35869,28 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
@@ -35899,24 +35899,24 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
@@ -35941,12 +35941,12 @@
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -35959,24 +35959,24 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1186" t="n">
@@ -35989,24 +35989,24 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1187" t="n">
@@ -36019,24 +36019,24 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1188" t="n">
@@ -36049,28 +36049,28 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
@@ -36079,12 +36079,12 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -36109,28 +36109,28 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
@@ -36139,24 +36139,24 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1192" t="n">
@@ -36169,28 +36169,28 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
@@ -36199,40 +36199,70 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1194" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1194" t="inlineStr">
+      <c r="B1195" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1194" t="n">
+      <c r="C1195" t="n">
         <v>2021</v>
       </c>
-      <c r="D1194" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1194" t="inlineStr">
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1194" t="inlineStr">
+      <c r="F1195" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1199"/>
+  <dimension ref="A1:F1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33091,12 +33091,12 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
+          <t xml:space="preserve"> Can ChatGPT read who you are? </t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -33109,28 +33109,28 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.chbah.2024.100088 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
+          <t xml:space="preserve"> Comput. Hum. Behav. Artif. Humans 2: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
+          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
+          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -33139,24 +33139,24 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
+          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
         </is>
       </c>
       <c r="C1092" t="n">
@@ -33169,28 +33169,28 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efektivní metody pro učení modelů a řízení v robotice ; Data-efficient methods for model learning and control in robotics. </t>
+          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -33199,28 +33199,28 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.base-search.net/Record/3b90c2a04826d994a37adc80910808ac880f4b67e04d4782e78b8061204064db </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Erik Derner </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
+          <t xml:space="preserve"> Efektivní metody pro učení modelů a řízení v robotice ; Data-efficient methods for model learning and control in robotics. </t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -33229,24 +33229,24 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
+          <t xml:space="preserve"> https://www.base-search.net/Record/3b90c2a04826d994a37adc80910808ac880f4b67e04d4782e78b8061204064db </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
+          <t xml:space="preserve"> Thesis (2022).</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
+          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
         </is>
       </c>
       <c r="C1095" t="n">
@@ -33259,7 +33259,7 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
@@ -33271,16 +33271,16 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
+          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -33289,28 +33289,28 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
+          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
+          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -33319,12 +33319,12 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
         </is>
       </c>
     </row>
@@ -33340,7 +33340,7 @@
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -33349,24 +33349,24 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sensors 19: (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
+          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
         </is>
       </c>
       <c r="C1099" t="n">
@@ -33379,28 +33379,28 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
+          <t xml:space="preserve"> Sensors 19: (2019).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
+          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -33409,28 +33409,28 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
+          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
+          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
+          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -33439,24 +33439,24 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
+          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
+          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -33469,28 +33469,28 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
+          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
+          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -33499,24 +33499,24 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
+          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
+          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -33529,24 +33529,24 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
+          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
+          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -33559,28 +33559,28 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
+          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -33589,24 +33589,24 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
+          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
+          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -33619,24 +33619,24 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
+          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
+          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
+          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -33649,24 +33649,24 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
+          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
+          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -33679,28 +33679,28 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
         </is>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
+          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
@@ -33709,24 +33709,24 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
         </is>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -33739,24 +33739,24 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
         </is>
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
+          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
+          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -33769,24 +33769,24 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
+          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
+          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
         </is>
       </c>
       <c r="C1113" t="n">
@@ -33799,28 +33799,28 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
+          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
+          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
@@ -33829,24 +33829,24 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
+          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
+          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
         </is>
       </c>
       <c r="C1115" t="n">
@@ -33859,24 +33859,24 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
         </is>
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
+          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -33889,24 +33889,24 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
         </is>
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -33919,24 +33919,24 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
         </is>
       </c>
       <c r="F1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -33949,24 +33949,24 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
         </is>
       </c>
       <c r="F1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
+          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
         </is>
       </c>
       <c r="C1119" t="n">
@@ -33979,24 +33979,24 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
         </is>
       </c>
       <c r="F1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
         </is>
       </c>
       <c r="C1120" t="n">
@@ -34009,28 +34009,28 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
         </is>
       </c>
       <c r="F1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
@@ -34039,12 +34039,12 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
         </is>
       </c>
       <c r="F1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
         </is>
       </c>
     </row>
@@ -34056,7 +34056,7 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
+          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -34069,12 +34069,12 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
         </is>
       </c>
       <c r="F1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -34099,24 +34099,24 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
         </is>
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
+          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -34129,28 +34129,28 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
         </is>
       </c>
       <c r="F1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
+          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
@@ -34159,28 +34159,28 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
         </is>
       </c>
       <c r="F1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
+          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
@@ -34189,28 +34189,28 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
         </is>
       </c>
       <c r="F1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
@@ -34219,24 +34219,24 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
         </is>
       </c>
       <c r="F1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
+          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -34249,24 +34249,24 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
         </is>
       </c>
       <c r="F1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
+          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
+          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1129" t="n">
@@ -34279,28 +34279,28 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
         </is>
       </c>
       <c r="F1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
+          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
+          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
@@ -34309,24 +34309,24 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
         </is>
       </c>
       <c r="F1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
+          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
+          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
         </is>
       </c>
       <c r="C1131" t="n">
@@ -34339,28 +34339,28 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
         </is>
       </c>
       <c r="F1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
+          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
+          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
+          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
@@ -34369,24 +34369,24 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
         </is>
       </c>
       <c r="F1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
+          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -34399,24 +34399,24 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
         </is>
       </c>
       <c r="F1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
+          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
+          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
+          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -34429,28 +34429,28 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
+          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
@@ -34459,28 +34459,28 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
+          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
@@ -34489,24 +34489,24 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
+          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
+          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
         </is>
       </c>
       <c r="C1137" t="n">
@@ -34519,24 +34519,24 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
         </is>
       </c>
       <c r="F1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
+          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
+          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
         </is>
       </c>
       <c r="C1138" t="n">
@@ -34554,23 +34554,23 @@
       </c>
       <c r="F1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
+          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
+          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
+          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>2026</v>
+        <v>2002</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
@@ -34579,12 +34579,12 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
+          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
         </is>
       </c>
     </row>
@@ -34596,7 +34596,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -34609,12 +34609,12 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
         </is>
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -34639,28 +34639,28 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
         </is>
       </c>
       <c r="F1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
@@ -34669,28 +34669,28 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
         </is>
       </c>
       <c r="F1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
@@ -34729,28 +34729,28 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
@@ -34759,28 +34759,28 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
@@ -34789,24 +34789,24 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -34819,24 +34819,24 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1148" t="n">
@@ -34849,28 +34849,28 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
@@ -34879,24 +34879,24 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -34909,24 +34909,24 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -34939,24 +34939,24 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1152" t="n">
@@ -34969,24 +34969,24 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -34999,24 +34999,24 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1154" t="n">
@@ -35029,24 +35029,24 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -35059,28 +35059,28 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
@@ -35089,24 +35089,24 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1157" t="n">
@@ -35119,24 +35119,24 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -35149,24 +35149,24 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1159" t="n">
@@ -35179,24 +35179,24 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1160" t="n">
@@ -35209,24 +35209,24 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1161" t="n">
@@ -35239,28 +35239,28 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
@@ -35269,24 +35269,24 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1163" t="n">
@@ -35299,24 +35299,24 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1164" t="n">
@@ -35329,28 +35329,28 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
@@ -35359,28 +35359,28 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
@@ -35389,28 +35389,28 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
@@ -35419,24 +35419,24 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -35449,24 +35449,24 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1169" t="n">
@@ -35479,28 +35479,28 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
@@ -35509,12 +35509,12 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1171" t="n">
@@ -35539,28 +35539,28 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
@@ -35569,12 +35569,12 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
@@ -35586,7 +35586,7 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1173" t="n">
@@ -35599,24 +35599,24 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1174" t="n">
@@ -35629,24 +35629,24 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1175" t="n">
@@ -35659,28 +35659,28 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
@@ -35689,28 +35689,28 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
@@ -35719,12 +35719,12 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
@@ -35736,11 +35736,11 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
@@ -35749,24 +35749,24 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -35779,28 +35779,28 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
@@ -35809,24 +35809,24 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1181" t="n">
@@ -35839,28 +35839,28 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
@@ -35869,28 +35869,28 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
@@ -35899,28 +35899,28 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
@@ -35929,24 +35929,24 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -35959,24 +35959,24 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1186" t="n">
@@ -35989,24 +35989,24 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1187" t="n">
@@ -36019,28 +36019,28 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
@@ -36049,24 +36049,24 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1189" t="n">
@@ -36079,7 +36079,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
@@ -36091,12 +36091,12 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1190" t="n">
@@ -36109,24 +36109,24 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1191" t="n">
@@ -36139,24 +36139,24 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1192" t="n">
@@ -36169,24 +36169,24 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1193" t="n">
@@ -36199,28 +36199,28 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
@@ -36229,12 +36229,12 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -36259,28 +36259,28 @@
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1196" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1196" t="inlineStr">
         <is>
@@ -36289,24 +36289,24 @@
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1197" t="n">
@@ -36319,28 +36319,28 @@
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1198" t="inlineStr">
         <is>
@@ -36349,40 +36349,70 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1199" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1199" t="inlineStr">
+      <c r="B1200" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1199" t="n">
+      <c r="C1200" t="n">
         <v>2021</v>
       </c>
-      <c r="D1199" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1199" t="inlineStr">
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1199" t="inlineStr">
+      <c r="F1200" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1208"/>
+  <dimension ref="A1:F1209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36211,12 +36211,12 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1194" t="n">
@@ -36229,24 +36229,24 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51701.2025.00732 </t>
         </is>
       </c>
       <c r="F1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2025, Honolulu, HI, USA, October 19-25, 2025: 7808-7817 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1195" t="n">
@@ -36259,24 +36259,24 @@
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1196" t="n">
@@ -36289,28 +36289,28 @@
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1197" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1197" t="inlineStr">
         <is>
@@ -36319,24 +36319,24 @@
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1198" t="n">
@@ -36349,7 +36349,7 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1198" t="inlineStr">
@@ -36361,12 +36361,12 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1199" t="n">
@@ -36379,24 +36379,24 @@
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1200" t="n">
@@ -36409,24 +36409,24 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1201" t="n">
@@ -36439,24 +36439,24 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1202" t="n">
@@ -36469,28 +36469,28 @@
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1203" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1203" t="inlineStr">
         <is>
@@ -36499,12 +36499,12 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -36529,28 +36529,28 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1205" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1205" t="inlineStr">
         <is>
@@ -36559,24 +36559,24 @@
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1206" t="n">
@@ -36589,28 +36589,28 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1207" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1207" t="inlineStr">
         <is>
@@ -36619,40 +36619,70 @@
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1208" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1208" t="inlineStr">
+      <c r="B1209" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1208" t="n">
+      <c r="C1209" t="n">
         <v>2021</v>
       </c>
-      <c r="D1208" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1208" t="inlineStr">
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1208" t="inlineStr">
+      <c r="F1209" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -32574,7 +32574,7 @@
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="F1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
@@ -36444,7 +36444,7 @@
       </c>
       <c r="F1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1211"/>
+  <dimension ref="A1:F1212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27901,12 +27901,12 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sergey Rodionov, Zarathustra Amadeus Goertzel, Ben Goertzel </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Evaluation of GPT-4 on the ETHICS Dataset. </t>
+          <t xml:space="preserve"> Strojové učení pro řízení inferencí a v automatickém dokazování vět ; Learning Inference Guidance in Automated Theorem Proving. </t>
         </is>
       </c>
       <c r="C917" t="n">
@@ -27919,24 +27919,24 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2309.10492 </t>
+          <t xml:space="preserve"> https://www.base-search.net/Record/6c7e6a927aa76dbcdb3148bb498eb1deef1b2edd32688ce87717ee8219dc1853 </t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2309.10492 (2023).</t>
+          <t xml:space="preserve"> Thesis (2023).</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ben Goertzel, Vitaly Bogdanov, Michael Duncan, Deborah Duong, Zarathustra Amadeus Goertzel, Jan Horlings, Matthew Iklé, Lucius Gregory Meredith, Alexey Potapov, Andre Luiz de Senna, Hedra Seid, Andres Suarez, Adam Vandervorst, Robert Werko </t>
+          <t xml:space="preserve">Sergey Rodionov, Zarathustra Amadeus Goertzel, Ben Goertzel </t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OpenCog Hyperon: A Framework for AGI at the Human Level and Beyond. </t>
+          <t xml:space="preserve"> An Evaluation of GPT-4 on the ETHICS Dataset. </t>
         </is>
       </c>
       <c r="C918" t="n">
@@ -27949,28 +27949,28 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2310.18318 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2309.10492 </t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2310.18318 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2309.10492 (2023).</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
+          <t xml:space="preserve">Ben Goertzel, Vitaly Bogdanov, Michael Duncan, Deborah Duong, Zarathustra Amadeus Goertzel, Jan Horlings, Matthew Iklé, Lucius Gregory Meredith, Alexey Potapov, Andre Luiz de Senna, Hedra Seid, Andres Suarez, Adam Vandervorst, Robert Werko </t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Make E Smart Again (Short Paper). </t>
+          <t xml:space="preserve"> OpenCog Hyperon: A Framework for AGI at the Human Level and Beyond. </t>
         </is>
       </c>
       <c r="C919" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -27979,12 +27979,12 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51054-1_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2310.18318 </t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part II: 408-415 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2310.18318 (2023).</t>
         </is>
       </c>
     </row>
@@ -27996,7 +27996,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Make E Smart Again. </t>
+          <t xml:space="preserve"> Make E Smart Again (Short Paper). </t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -28009,28 +28009,28 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.08858 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51054-1_26 </t>
         </is>
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2004.08858 (2020).</t>
+          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part II: 408-415 (2020).</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Gary K. L. Tam </t>
+          <t xml:space="preserve">Zarathustra Amadeus Goertzel </t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust point cloud completion under corruption. </t>
+          <t xml:space="preserve"> Make E Smart Again. </t>
         </is>
       </c>
       <c r="C921" t="n">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -28039,12 +28039,12 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cag.2025.104401 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2004.08858 </t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Graph. 132: (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2004.08858 (2020).</t>
         </is>
       </c>
     </row>
@@ -28056,7 +28056,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust Point Cloud Completion Under Corruption. </t>
+          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust point cloud completion under corruption. </t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -28069,28 +28069,28 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.16743 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cag.2025.104401 </t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.16743 (2025/07).</t>
+          <t xml:space="preserve"> Comput. Graph. 132: (2025).</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Muneeb Imtiaz Ahmad, Gary K. L. Tam </t>
+          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Gary K. L. Tam </t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Point Cloud Completion: A Survey. </t>
+          <t xml:space="preserve"> Denoising-While-Completing Network (DWCNet): Robust Point Cloud Completion Under Corruption. </t>
         </is>
       </c>
       <c r="C923" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -28099,28 +28099,28 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TVCG.2023.3344935 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.16743 </t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 30: 6880-6899 (2024/10).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.16743 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Keneni W. Tesema, Lyndon Hill, Mark W. Jones, Muneeb Imtiaz Ahmad, Gary K. L. Tam </t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Wos Challenge Met. </t>
+          <t xml:space="preserve"> Point Cloud Completion: A Survey. </t>
         </is>
       </c>
       <c r="C924" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -28129,28 +28129,28 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114264018 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TVCG.2023.3344935 </t>
         </is>
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 66: 565-574 (2022).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 30: 6880-6899 (2024/10).</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stepan Holub, Robert Veroff </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Formalizing a Fragment of Combinatorics on Words. </t>
+          <t xml:space="preserve"> A Wos Challenge Met. </t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -28159,28 +28159,28 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-58741-7_3 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114264018 </t>
         </is>
       </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unveiling Dynamics and Complexity - 13th Conference on Computability in Europe, CiE 2017, Turku, Finland, June 12-16, 2017, Proceedings: 24-31 (2017).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 66: 565-574 (2022).</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Spinks, Robert J. Bignall, Robert Veroff </t>
+          <t xml:space="preserve">Stepan Holub, Robert Veroff </t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discriminator logics (Research announcement). </t>
+          <t xml:space="preserve"> Formalizing a Fragment of Combinatorics on Words. </t>
         </is>
       </c>
       <c r="C926" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -28189,28 +28189,28 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.26686/ajl.v11i2.2020 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-58741-7_3 </t>
         </is>
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Australas. J. Log. 11: (2014).</t>
+          <t xml:space="preserve"> Unveiling Dynamics and Complexity - 13th Conference on Computability in Europe, CiE 2017, Turku, Finland, June 12-16, 2017, Proceedings: 24-31 (2017).</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranganathan Padmanabhan, Robert Veroff </t>
+          <t xml:space="preserve">Matthew Spinks, Robert J. Bignall, Robert Veroff </t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Geometric Procedure with Prover9. </t>
+          <t xml:space="preserve"> Discriminator logics (Research announcement). </t>
         </is>
       </c>
       <c r="C927" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -28219,24 +28219,24 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_7 </t>
+          <t xml:space="preserve"> https://doi.org/10.26686/ajl.v11i2.2020 </t>
         </is>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 139-150 (2013).</t>
+          <t xml:space="preserve"> Australas. J. Log. 11: (2014).</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael K. Kinyon, Robert Veroff, Petr Vojtechovský </t>
+          <t xml:space="preserve">Ranganathan Padmanabhan, Robert Veroff </t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Loops with Abelian Inner Mapping Groups: An Application of Automated Deduction. </t>
+          <t xml:space="preserve"> A Geometric Procedure with Prover9. </t>
         </is>
       </c>
       <c r="C928" t="n">
@@ -28249,28 +28249,28 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_7 </t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 151-164 (2013).</t>
+          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 139-150 (2013).</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francesco Paoli, Matthew Spinks, Robert Veroff </t>
+          <t xml:space="preserve">Michael K. Kinyon, Robert Veroff, Petr Vojtechovský </t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Abelian Logic and the Logics of Pointed Lattice-Ordered Varieties. </t>
+          <t xml:space="preserve"> Loops with Abelian Inner Mapping Groups: An Application of Automated Deduction. </t>
         </is>
       </c>
       <c r="C929" t="n">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -28279,24 +28279,24 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11787-008-0034-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-36675-8_8 </t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logica Universalis 2: 209-233 (2008).</t>
+          <t xml:space="preserve"> Automated Reasoning and Mathematics - Essays in Memory of William W. McCune: 151-164 (2013).</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
+          <t xml:space="preserve">Francesco Paoli, Matthew Spinks, Robert Veroff </t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. I. </t>
+          <t xml:space="preserve"> Abelian Logic and the Logics of Pointed Lattice-Ordered Varieties. </t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -28309,12 +28309,12 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9113-x </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11787-008-0034-2 </t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 88: 325-348 (2008).</t>
+          <t xml:space="preserve"> Logica Universalis 2: 209-233 (2008).</t>
         </is>
       </c>
     </row>
@@ -28326,7 +28326,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. II. </t>
+          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. I. </t>
         </is>
       </c>
       <c r="C931" t="n">
@@ -28339,28 +28339,28 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9138-1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9113-x </t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 89: 401-425 (2008).</t>
+          <t xml:space="preserve"> Stud Logica 88: 325-348 (2008).</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frank Gilfeather, Vikas Hamine, Paul Helman, Julie Hutt, Terry Loring, C. Rick Lyons, Robert Veroff </t>
+          <t xml:space="preserve">Matthew Spinks, Robert Veroff </t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learning and modeling biosignatures from tissue images. </t>
+          <t xml:space="preserve"> Constructive Logic with Strong Negation is a Substructural Logic. II. </t>
         </is>
       </c>
       <c r="C932" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -28369,28 +28369,28 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33282059 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s11225-008-9138-1 </t>
         </is>
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Biol. Medicine 37: 1539-1552 (2007).</t>
+          <t xml:space="preserve"> Stud Logica 89: 401-425 (2008).</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff, Matthew Spinks </t>
+          <t xml:space="preserve">Frank Gilfeather, Vikas Hamine, Paul Helman, Julie Hutt, Terry Loring, C. Rick Lyons, Robert Veroff </t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Axiomatizing the Skew Boolean Propositional Calculus. </t>
+          <t xml:space="preserve"> Learning and modeling biosignatures from tissue images. </t>
         </is>
       </c>
       <c r="C933" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -28399,28 +28399,28 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-006-9029-y </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33282059 </t>
         </is>
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 37: 3-20 (2006).</t>
+          <t xml:space="preserve"> Comput. Biol. Medicine 37: 1539-1552 (2007).</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
+          <t xml:space="preserve">Robert Veroff, Matthew Spinks </t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics. </t>
+          <t xml:space="preserve"> Axiomatizing the Skew Boolean Propositional Calculus. </t>
         </is>
       </c>
       <c r="C934" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -28429,28 +28429,28 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262834 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-006-9029-y </t>
         </is>
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stud Logica 80: 195-234 (2005).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 37: 3-20 (2006).</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff, Susan R. Atlas, Cheryl Willman </t>
+          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Bayesian Network Classification Methodology for Gene Expression Data. </t>
+          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics. </t>
         </is>
       </c>
       <c r="C935" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -28459,28 +28459,28 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33209551 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262834 </t>
         </is>
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Comput. Biol. 11: 581-615 (2004).</t>
+          <t xml:space="preserve"> Stud Logica 80: 195-234 (2005).</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff, Susan R. Atlas, Cheryl Willman </t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Shortest 2-Basis for Boolean Algebra in Terms of the Sheffer Stroke. </t>
+          <t xml:space="preserve"> A Bayesian Network Classification Methodology for Gene Expression Data. </t>
         </is>
       </c>
       <c r="C936" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -28489,24 +28489,24 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1027322305654 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q33209551 </t>
         </is>
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 31: 1-9 (2003).</t>
+          <t xml:space="preserve"> J. Comput. Biol. 11: 581-615 (2004).</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics </t>
+          <t xml:space="preserve"> A Shortest 2-Basis for Boolean Algebra in Terms of the Sheffer Stroke. </t>
         </is>
       </c>
       <c r="C937" t="n">
@@ -28519,28 +28519,28 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/cs/0301026 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1027322305654 </t>
         </is>
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR cs.LO/0301026 (2003).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 31: 1-9 (2003).</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t xml:space="preserve">William McCune, Robert Veroff, Branden Fitelson, Kenneth Harris, Andrew Feist, Larry Wos </t>
+          <t xml:space="preserve">Michael Beeson, Robert Veroff, Larry Wos </t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Single Axioms for Boolean Algebra. </t>
+          <t xml:space="preserve"> Double-Negation Elimination in Some Propositional Logics </t>
         </is>
       </c>
       <c r="C938" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -28549,28 +28549,28 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q60061107 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/cs/0301026 </t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 29: 1-16 (2002).</t>
+          <t xml:space="preserve"> arXiv CoRR cs.LO/0301026 (2003).</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
+          <t xml:space="preserve">William McCune, Robert Veroff, Branden Fitelson, Kenneth Harris, Andrew Feist, Larry Wos </t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The application of automated reasoning to formal models of combinatorial optimization. </t>
+          <t xml:space="preserve"> Short Single Axioms for Boolean Algebra. </t>
         </is>
       </c>
       <c r="C939" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -28579,24 +28579,24 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q127517130 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q60061107 </t>
         </is>
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Math. Comput. 120: 175-194 (2001).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 29: 1-16 (2002).</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Finding Shortest Proofs: An Application of Linked Inference Rules. </t>
+          <t xml:space="preserve"> The application of automated reasoning to formal models of combinatorial optimization. </t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1010635625063 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q127517130 </t>
         </is>
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 27: 123-139 (2001).</t>
+          <t xml:space="preserve"> Appl. Math. Comput. 120: 175-194 (2001).</t>
         </is>
       </c>
     </row>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving Open Questions and Other Challenge Problems Using Proof Sketches. </t>
+          <t xml:space="preserve"> Finding Shortest Proofs: An Application of Linked Inference Rules. </t>
         </is>
       </c>
       <c r="C941" t="n">
@@ -28639,28 +28639,28 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1023/A:1010639725972 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1010635625063 </t>
         </is>
       </c>
       <c r="F941" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 27: 157-174 (2001).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 27: 123-139 (2001).</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gregory H. Chisholm, Steven T. Eckmann, Christopher M. Lain, Robert Veroff </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Integrated Circuits. </t>
+          <t xml:space="preserve"> Solving Open Questions and Other Challenge Problems Using Proof Sketches. </t>
         </is>
       </c>
       <c r="C942" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -28669,28 +28669,28 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://doi.ieeecomputersociety.org/10.1109/54.765201 </t>
+          <t xml:space="preserve"> https://doi.org/10.1023/A:1010639725972 </t>
         </is>
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Des. Test Comput. 16: 26-37 (1999).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 27: 157-174 (2001).</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Gregory H. Chisholm, Steven T. Eckmann, Christopher M. Lain, Robert Veroff </t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Using Hints to Increase the Effectiveness of an Automated Reasoning Program: Case Studies. </t>
+          <t xml:space="preserve"> Understanding Integrated Circuits. </t>
         </is>
       </c>
       <c r="C943" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -28699,28 +28699,28 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/BF00252178 </t>
+          <t xml:space="preserve"> http://doi.ieeecomputersociety.org/10.1109/54.765201 </t>
         </is>
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 16: 223-239 (1996).</t>
+          <t xml:space="preserve"> IEEE Des. Test Comput. 16: 26-37 (1999).</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Robert Veroff </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logical basis for the automation of reasoning: Case studies. </t>
+          <t xml:space="preserve"> Using Hints to Increase the Effectiveness of an Automated Reasoning Program: Case Studies. </t>
         </is>
       </c>
       <c r="C944" t="n">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -28729,28 +28729,28 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/BF00252178 </t>
         </is>
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Handbook of Logic in Artificial Intelligence and Logic Programming, Volume2, Deduction Methodologies: 1-40 (1994).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 16: 223-239 (1996).</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff </t>
+          <t xml:space="preserve">Larry Wos, Robert Veroff </t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Linked Inference Principle, I: The Formal Treatment. </t>
+          <t xml:space="preserve"> Logical basis for the automation of reasoning: Case studies. </t>
         </is>
       </c>
       <c r="C945" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -28759,28 +28759,28 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114267080 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 8: 213-274 (1992).</t>
+          <t xml:space="preserve"> Handbook of Logic in Artificial Intelligence and Logic Programming, Volume2, Deduction Methodologies: 1-40 (1994).</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff, Frank R. Carrano </t>
+          <t xml:space="preserve">Robert Veroff </t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intermediate problem solving and data structures - walls and mirrors (2. ed.). </t>
+          <t xml:space="preserve"> The Linked Inference Principle, I: The Formal Treatment. </t>
         </is>
       </c>
       <c r="C946" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -28789,28 +28789,28 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114267080 </t>
         </is>
       </c>
       <c r="F946" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Benjamin/Cummings series in computer science, Benjamin/Cummings (1991).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 8: 213-274 (1992).</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff, Frank R. Carrano </t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Designing Deductive Databases. </t>
+          <t xml:space="preserve"> Intermediate problem solving and data structures - walls and mirrors (2. ed.). </t>
         </is>
       </c>
       <c r="C947" t="n">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -28819,28 +28819,28 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/BF00244512 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 4: 29-68 (1988).</t>
+          <t xml:space="preserve"> Benjamin/Cummings series in computer science, Benjamin/Cummings (1991).</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Steve Winker, Barry Smith, Robert Veroff, Lawrence J. Henschen </t>
+          <t xml:space="preserve">Paul Helman, Robert Veroff </t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A New Use of an Automated Reasoning Assistant: Open Questions in Equivalential Calculus and the Study of Infinite Domains. </t>
+          <t xml:space="preserve"> Designing Deductive Databases. </t>
         </is>
       </c>
       <c r="C948" t="n">
-        <v>1984</v>
+        <v>1988</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -28849,24 +28849,24 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262293 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/BF00244512 </t>
         </is>
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. 22: 303-356 (1984).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 4: 29-68 (1988).</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Wos, Robert Veroff, Barry Smith, William McCune </t>
+          <t xml:space="preserve">Larry Wos, Steve Winker, Barry Smith, Robert Veroff, Lawrence J. Henschen </t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Linked Inference Principle, II: The User's Viewpoint. </t>
+          <t xml:space="preserve"> A New Use of an Automated Reasoning Assistant: Open Questions in Equivalential Calculus and the Study of Infinite Domains. </t>
         </is>
       </c>
       <c r="C949" t="n">
@@ -28879,28 +28879,28 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-0-387-34768-4_19 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114262293 </t>
         </is>
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7th International Conference on Automated Deduction, Napa, California, USA, May 14-16, 1984, Proceedings: 316-332 (1984).</t>
+          <t xml:space="preserve"> Artif. Intell. 22: 303-356 (1984).</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t xml:space="preserve">Larry Henschen, Barry Smith, Robert Veroff, Steve Winker, Larry Wos </t>
+          <t xml:space="preserve">Larry Wos, Robert Veroff, Barry Smith, William McCune </t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Questions concerning possible shortest single axioms for the equivalential calculus: an application of automated theorem proving to infinite domains. </t>
+          <t xml:space="preserve"> The Linked Inference Principle, II: The User's Viewpoint. </t>
         </is>
       </c>
       <c r="C950" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -28909,28 +28909,28 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114254310 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-0-387-34768-4_19 </t>
         </is>
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Notre Dame J. Formal Log. 24: 205-223 (1983).</t>
+          <t xml:space="preserve"> 7th International Conference on Automated Deduction, Napa, California, USA, May 14-16, 1984, Proceedings: 316-332 (1984).</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Veroff, Lawrence J. Henschen </t>
+          <t xml:space="preserve">Larry Henschen, Barry Smith, Robert Veroff, Steve Winker, Larry Wos </t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Automatic Transformations to Program Verification. </t>
+          <t xml:space="preserve"> Questions concerning possible shortest single axioms for the equivalential calculus: an application of automated theorem proving to infinite domains. </t>
         </is>
       </c>
       <c r="C951" t="n">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -28939,49 +28939,49 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://ijcai.org/Proceedings/81-1/Papers/087.pdf </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114254310 </t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 7th International Joint Conference on Artificial Intelligence, IJCAI '81, Vancouver, BC, Canada, August 24-28, 1981: 472-479 (1981).</t>
+          <t xml:space="preserve"> Notre Dame J. Formal Log. 24: 205-223 (1983).</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang H. Nguyen, Marcelo Menegali, Junehyuk Jung, Junsu Kim, Vikas Verma, Quoc V. Le, Thang Luong </t>
+          <t xml:space="preserve">Robert Veroff, Lawrence J. Henschen </t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Gold-medalist Performance in Solving Olympiad Geometry with AlphaGeometry2. </t>
+          <t xml:space="preserve"> Application of Automatic Transformations to Program Verification. </t>
         </is>
       </c>
       <c r="C952" t="n">
-        <v>2025</v>
+        <v>1981</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://jmlr.org/papers/v26/25-1654.html </t>
+          <t xml:space="preserve"> http://ijcai.org/Proceedings/81-1/Papers/087.pdf </t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Mach. Learn. Res. 26: 241:1-241:39 (2025).</t>
+          <t xml:space="preserve"> Proceedings of the 7th International Joint Conference on Artificial Intelligence, IJCAI '81, Vancouver, BC, Canada, August 24-28, 1981: 472-479 (1981).</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
+          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang H. Nguyen, Marcelo Menegali, Junehyuk Jung, Junsu Kim, Vikas Verma, Quoc V. Le, Thang Luong </t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -28999,54 +28999,54 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2502.03544 </t>
+          <t xml:space="preserve"> https://jmlr.org/papers/v26/25-1654.html </t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2502.03544 (2025/02).</t>
+          <t xml:space="preserve"> J. Mach. Learn. Res. 26: 241:1-241:39 (2025).</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Yuri Chervonyi, Trieu H. Trinh, Miroslav Olsák, Xiaomeng Yang, Hoang Nguyen, Marcelo Menegali, Junehyuk Jung, Vikas Verma, Quoc V. Le, Thang Luong </t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
+          <t xml:space="preserve"> Gold-medalist Performance in Solving Olympiad Geometry with AlphaGeometry2. </t>
         </is>
       </c>
       <c r="C954" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2502.03544 </t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2502.03544 (2025/02).</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simon Frieder, Mirek Olsák, Julius Berner, Thomas Lukasiewicz </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The IMO Small Challenge: Not-Too-Hard Olympiad Math Datasets for LLMs. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive 𝛼-Equivalence. </t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -29054,29 +29054,29 @@
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=HYuKXhgzjm </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3656459 </t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Second Tiny Papers Track at ICLR 2024, Tiny Papers @ ICLR 2024, Vienna, Austria, May 11, 2024: (2024).</t>
+          <t xml:space="preserve"> Proc. ACM Program. Lang. 8: 2027-2050 (2024).</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Simon Frieder, Mirek Olsák, Julius Berner, Thomas Lukasiewicz </t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
+          <t xml:space="preserve"> The IMO Small Challenge: Not-Too-Hard Olympiad Math Datasets for LLMs. </t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -29084,29 +29084,29 @@
       </c>
       <c r="D956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR, FM </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=HYuKXhgzjm </t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
+          <t xml:space="preserve"> The Second Tiny Papers Track at ICLR 2024, Tiny Papers @ ICLR 2024, Vienna, Austria, May 11, 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Mirek Olsák, Jason Rute, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
+          <t xml:space="preserve"> Graph2Tac: Online Representation Learning of Formal Math Concepts. </t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -29119,24 +29119,24 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=A7CtiozznN </t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
+          <t xml:space="preserve"> Forty-first International Conference on Machine Learning, ICML 2024, Vienna, Austria, July 21-27, 2024: 4046-4076 (2024).</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
+          <t xml:space="preserve">Lasse Blaauwbroek, Miroslav Olsák, Herman Geuvers </t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
+          <t xml:space="preserve"> Hashing Modulo Context-Sensitive α-Equivalence. </t>
         </is>
       </c>
       <c r="C958" t="n">
@@ -29149,54 +29149,54 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02948 </t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02948 (2024).</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Jason Rute, Miroslav Olsák, Lasse Blaauwbroek, Fidel Ivan Schaposnik Massolo, Jelle Piepenbrock, Vasily Pestun </t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Erratum: Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
+          <t xml:space="preserve"> Graph2Tac: Learning Hierarchical Representations of Math Concepts in Theorem proving. </t>
         </is>
       </c>
       <c r="C959" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR, FM </t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1142/S021906132192001X </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02949 </t>
         </is>
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Math. Log. 21: (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02949 (2024).</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Maltsev conditions for General Congruence Meet-semidistributive Algebras. </t>
+          <t xml:space="preserve"> Erratum: Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -29209,24 +29209,24 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2021.14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1142/S021906132192001X </t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Log. 86: 1432-1451 (2021).</t>
+          <t xml:space="preserve"> J. Math. Log. 21: (2021).</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Miroslav Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
+          <t xml:space="preserve"> Maltsev conditions for General Congruence Meet-semidistributive Algebras. </t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -29239,19 +29239,19 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://proceedings.neurips.cc/paper/2021/hash/cf708fc1decf0337aded484f8f4519ae-Abstract.html </t>
+          <t xml:space="preserve"> https://doi.org/10.1017/jsl.2021.14 </t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 34: Annual Conference on Neural Information Processing Systems 2021, NeurIPS 2021, December 6-14, 2021, virtual.: 24707-24718 (2021).</t>
+          <t xml:space="preserve"> J. Symb. Log. 86: 1432-1451 (2021).</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco Bagatella, Mirek Olsák, Michal Rolínek, Georg Martius </t>
+          <t xml:space="preserve">Marco Bagatella, Miroslav Olsák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
@@ -29269,28 +29269,28 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2110.06149 </t>
+          <t xml:space="preserve"> https://proceedings.neurips.cc/paper/2021/hash/cf708fc1decf0337aded484f8f4519ae-Abstract.html </t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2110.06149 (2021).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 34: Annual Conference on Neural Information Processing Systems 2021, NeurIPS 2021, December 6-14, 2021, virtual.: 24707-24718 (2021).</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Olsák </t>
+          <t xml:space="preserve">Marco Bagatella, Mirek Olsák, Michal Rolínek, Georg Martius </t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Loop conditions for strongly connected digraphs. </t>
+          <t xml:space="preserve"> Planning from Pixels in Environments with Combinatorially Hard Search Spaces. </t>
         </is>
       </c>
       <c r="C963" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -29299,12 +29299,12 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114614801 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2110.06149 </t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Int. J. Algebra Comput. 30: 467-499 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2110.06149 (2021).</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GeoLogic - Graphical Interactive Theorem Prover for Euclidean Geometry. </t>
+          <t xml:space="preserve"> Loop conditions for strongly connected digraphs. </t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -29329,12 +29329,12 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-52200-1_26 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q114614801 </t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mathematical Software - ICMS 2020 - 7th International Conference, Braunschweig, Germany, July 13-16, 2020, Proceedings: 263-271 (2020).</t>
+          <t xml:space="preserve"> Int. J. Algebra Comput. 30: 467-499 (2020).</t>
         </is>
       </c>
     </row>
@@ -29346,7 +29346,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GeoLogic - Graphical interactive theorem prover for Euclidean geometry. </t>
+          <t xml:space="preserve"> GeoLogic - Graphical Interactive Theorem Prover for Euclidean Geometry. </t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -29359,24 +29359,24 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.03586 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-52200-1_26 </t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.03586 (2020).</t>
+          <t xml:space="preserve"> Mathematical Software - ICMS 2020 - 7th International Conference, Braunschweig, Germany, July 13-16, 2020, Proceedings: 263-271 (2020).</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Miroslav Olsák </t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ω-categorical structures avoiding height 1 identities. </t>
+          <t xml:space="preserve"> GeoLogic - Graphical interactive theorem prover for Euclidean geometry. </t>
         </is>
       </c>
       <c r="C966" t="n">
@@ -29389,28 +29389,28 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2006.12254 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.03586 </t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2006.12254 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.03586 (2020).</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Van Trung Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
+          <t xml:space="preserve"> ω-categorical structures avoiding height 1 identities. </t>
         </is>
       </c>
       <c r="C967" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -29419,24 +29419,24 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1142/S0219061319500107 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2006.12254 </t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Math. Log. 19: 1950010:1-1950010:31 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2006.12254 (2020).</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Van Trung Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dichotomy for Symmetric Boolean PCSPs. </t>
+          <t xml:space="preserve"> Equations in oligomorphic clones and the constraint satisfaction problem for ω-categorical structures. </t>
         </is>
       </c>
       <c r="C968" t="n">
@@ -29449,24 +29449,24 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ICALP.2019.57 </t>
+          <t xml:space="preserve"> https://doi.org/10.1142/S0219061319500107 </t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 46th International Colloquium on Automata, Languages, and Programming, ICALP 2019, Patras, Greece, July 9-12, 2019: 57:1-57:12 (2019).</t>
+          <t xml:space="preserve"> J. Math. Log. 19: 1950010:1-1950010:31 (2019).</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Topology is relevant (in a dichotomy conjecture for infinite-domain constraint satisfaction problems). </t>
+          <t xml:space="preserve"> Dichotomy for Symmetric Boolean PCSPs. </t>
         </is>
       </c>
       <c r="C969" t="n">
@@ -29479,12 +29479,12 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/LICS.2019.8785883 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.ICALP.2019.57 </t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 34th Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2019, Vancouver, BC, Canada, June 24-27, 2019: 1-12 (2019).</t>
+          <t xml:space="preserve"> 46th International Colloquium on Automata, Languages, and Programming, ICALP 2019, Patras, Greece, July 9-12, 2019: 57:1-57:12 (2019).</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29496,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Topology is relevant (in the infinite-domain dichotomy conjecture for constraint satisfaction problems). </t>
+          <t xml:space="preserve"> Topology is relevant (in a dichotomy conjecture for infinite-domain constraint satisfaction problems). </t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -29509,24 +29509,24 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1901.04237 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/LICS.2019.8785883 </t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1901.04237 (2019).</t>
+          <t xml:space="preserve"> 34th Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2019, Vancouver, BC, Canada, June 24-27, 2019: 1-12 (2019).</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
+          <t xml:space="preserve">Manuel Bodirsky, Antoine Mottet, Miroslav Olsák, Jakub Oprsal, Michael Pinsker, Ross Willard </t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dichotomy for symmetric Boolean PCSPs. </t>
+          <t xml:space="preserve"> Topology is relevant (in the infinite-domain dichotomy conjecture for constraint satisfaction problems). </t>
         </is>
       </c>
       <c r="C971" t="n">
@@ -29539,28 +29539,28 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.12424 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1901.04237 </t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.12424 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1901.04237 (2019).</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
+          <t xml:space="preserve">Miron Ficak, Marcin Kozik, Miroslav Olsák, Szymon Stankiewicz </t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The equivalence of two dichotomy conjectures for infinite domain constraint satisfaction problems. </t>
+          <t xml:space="preserve"> Dichotomy for symmetric Boolean PCSPs. </t>
         </is>
       </c>
       <c r="C972" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -29569,28 +29569,28 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/LICS.2017.8005128 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.12424 </t>
         </is>
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 32nd Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2017, Reykjavik, Iceland, June 20-23, 2017: 1-12 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.12424 (2019).</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Michael Pinsker, Van Trung Pham </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Trung Van Pham, Michael Pinsker </t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Equations in oligomorphic clones and the Constraint Satisfaction Problem for $ω$-categorical structures. </t>
+          <t xml:space="preserve"> The equivalence of two dichotomy conjectures for infinite domain constraint satisfaction problems. </t>
         </is>
       </c>
       <c r="C973" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -29599,28 +29599,28 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1612.07551 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/LICS.2017.8005128 </t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1612.07551 (2016).</t>
+          <t xml:space="preserve"> 32nd Annual ACM/IEEE Symposium on Logic in Computer Science, LICS 2017, Reykjavik, Iceland, June 20-23, 2017: 1-12 (2017).</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Libor Barto, Michael Kompatscher, Miroslav Olsák, Michael Pinsker, Van Trung Pham </t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> Equations in oligomorphic clones and the Constraint Satisfaction Problem for $ω$-categorical structures. </t>
         </is>
       </c>
       <c r="C974" t="n">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -29629,24 +29629,24 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1612.07551 </t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 11176-11184 (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1612.07551 (2016).</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -29659,24 +29659,24 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
+          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 11176-11184 (2025).</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C976" t="n">
@@ -29689,24 +29689,24 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
+          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -29719,24 +29719,24 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
+          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -29749,24 +29749,24 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
+          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -29779,24 +29779,24 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -29809,28 +29809,28 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
         </is>
       </c>
       <c r="C981" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -29839,24 +29839,24 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C982" t="n">
@@ -29869,24 +29869,24 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
+          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -29899,24 +29899,24 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
         </is>
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
+          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -29929,24 +29929,24 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
+          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
         </is>
       </c>
       <c r="C985" t="n">
@@ -29959,24 +29959,24 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
+          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -29989,28 +29989,28 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C987" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -30019,24 +30019,24 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2023/12)</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
+          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
         </is>
       </c>
       <c r="C988" t="n">
@@ -30049,24 +30049,24 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
+          <t xml:space="preserve"> Zenodo (2023/12)</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
@@ -30091,16 +30091,16 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C990" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -30109,24 +30109,24 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -30139,12 +30139,12 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
+          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
         </is>
       </c>
     </row>
@@ -30169,28 +30169,28 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
+          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C993" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -30199,24 +30199,24 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -30229,24 +30229,24 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -30259,28 +30259,28 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
+          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C996" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -30289,24 +30289,24 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
         </is>
       </c>
       <c r="C997" t="n">
@@ -30319,24 +30319,24 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
+          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -30349,24 +30349,24 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
+          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -30379,24 +30379,24 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C1000" t="n">
@@ -30409,28 +30409,28 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
         </is>
       </c>
       <c r="C1001" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -30439,24 +30439,24 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -30469,24 +30469,24 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
+          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C1003" t="n">
@@ -30499,12 +30499,12 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
         </is>
       </c>
     </row>
@@ -30529,12 +30529,12 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
         </is>
       </c>
     </row>
@@ -30546,7 +30546,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
@@ -30571,16 +30571,16 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C1006" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -30589,12 +30589,12 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
         </is>
       </c>
     </row>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
+          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
         </is>
       </c>
       <c r="C1007" t="n">
@@ -30619,24 +30619,24 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
+          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -30649,24 +30649,24 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
+          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
         </is>
       </c>
       <c r="F1009" t="inlineStr">
@@ -30691,16 +30691,16 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Nicholas Chew </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> QBF proof complexity. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C1010" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -30709,24 +30709,24 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Nicholas Chew </t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> QBF proof complexity. </t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -30739,12 +30739,12 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
+          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
@@ -30756,7 +30756,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1012" t="n">
@@ -30769,12 +30769,12 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
+          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
         </is>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
         </is>
       </c>
     </row>
@@ -30790,7 +30790,7 @@
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -30799,24 +30799,24 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
+          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -30829,24 +30829,24 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
         </is>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
+          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
         </is>
       </c>
       <c r="C1015" t="n">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
         </is>
       </c>
     </row>
@@ -30876,7 +30876,7 @@
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1016" t="n">
@@ -30889,12 +30889,12 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
+          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
         </is>
       </c>
     </row>
@@ -30910,7 +30910,7 @@
         </is>
       </c>
       <c r="C1017" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -30919,24 +30919,24 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -30949,24 +30949,24 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
+          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
+          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
         </is>
       </c>
       <c r="C1019" t="n">
@@ -30979,24 +30979,24 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
+          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
         </is>
       </c>
       <c r="C1020" t="n">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1021" t="n">
@@ -31039,7 +31039,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
@@ -31051,16 +31051,16 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -31069,12 +31069,12 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
         </is>
       </c>
     </row>
@@ -31086,7 +31086,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -31099,12 +31099,12 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
         </is>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
+          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
         </is>
       </c>
     </row>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -31129,12 +31129,12 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
         </is>
       </c>
     </row>
@@ -31146,7 +31146,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -31159,7 +31159,7 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
         </is>
       </c>
       <c r="F1025" t="inlineStr">
@@ -31171,12 +31171,12 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -31189,7 +31189,7 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
         </is>
       </c>
       <c r="F1026" t="inlineStr">
@@ -31201,30 +31201,30 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C1027" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
         </is>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
         </is>
       </c>
     </row>
@@ -31236,11 +31236,11 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
+          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
         </is>
       </c>
       <c r="C1028" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -31249,12 +31249,12 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
         </is>
       </c>
     </row>
@@ -31266,11 +31266,11 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
+          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -31279,12 +31279,12 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
         </is>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
         </is>
       </c>
     </row>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C1030" t="n">
@@ -31309,12 +31309,12 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
+          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
         </is>
       </c>
     </row>
@@ -31339,28 +31339,28 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
+          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
         </is>
       </c>
       <c r="C1032" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -31369,24 +31369,24 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
         </is>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
+          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
         </is>
       </c>
       <c r="C1033" t="n">
@@ -31399,28 +31399,28 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
         </is>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
+          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
         </is>
       </c>
       <c r="C1034" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -31429,28 +31429,28 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
         </is>
       </c>
       <c r="C1035" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -31459,12 +31459,12 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
         </is>
       </c>
     </row>
@@ -31476,7 +31476,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -31489,12 +31489,12 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
         </is>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
+          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
         </is>
       </c>
     </row>
@@ -31506,7 +31506,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -31519,12 +31519,12 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
+          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
         </is>
       </c>
     </row>
@@ -31536,7 +31536,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -31549,28 +31549,28 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
         </is>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -31579,24 +31579,24 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
         </is>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
+          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -31609,12 +31609,12 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
         </is>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
+          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
         </is>
       </c>
     </row>
@@ -31626,7 +31626,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
+          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -31639,28 +31639,28 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
         </is>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
+          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
         </is>
       </c>
       <c r="C1042" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -31669,28 +31669,28 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
         </is>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Lasse Blaauwbroek </t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
         </is>
       </c>
       <c r="C1043" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -31699,12 +31699,12 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
         </is>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
         </is>
       </c>
     </row>
@@ -31716,11 +31716,11 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
+          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -31729,12 +31729,12 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
         </is>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
         </is>
       </c>
     </row>
@@ -31746,7 +31746,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -31759,12 +31759,12 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
         </is>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
+          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
         </is>
       </c>
     </row>
@@ -31776,7 +31776,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1046" t="n">
@@ -31789,12 +31789,12 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
         </is>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
         </is>
       </c>
     </row>
@@ -31806,7 +31806,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -31819,12 +31819,12 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
         </is>
       </c>
     </row>
@@ -31836,7 +31836,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -31849,12 +31849,12 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
         </is>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
         </is>
       </c>
     </row>
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
+          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -31879,12 +31879,12 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
         </is>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
         </is>
       </c>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
         </is>
       </c>
       <c r="C1050" t="n">
@@ -31909,12 +31909,12 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
         </is>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
         </is>
       </c>
     </row>
@@ -31926,11 +31926,11 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1051" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -31939,12 +31939,12 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
         </is>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
         </is>
       </c>
     </row>
@@ -31956,7 +31956,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -31969,12 +31969,12 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
         </is>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
+          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
         </is>
       </c>
     </row>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -31999,12 +31999,12 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1054" t="n">
@@ -32029,12 +32029,12 @@
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
         </is>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Designing Game of Theorems. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -32059,12 +32059,12 @@
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
         </is>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
         </is>
       </c>
     </row>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
+          <t xml:space="preserve"> Designing Game of Theorems. </t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -32089,28 +32089,28 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
         </is>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
         </is>
       </c>
       <c r="C1057" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -32119,24 +32119,24 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
         </is>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
+          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1058" t="n">
@@ -32149,12 +32149,12 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
+          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
         </is>
       </c>
     </row>
@@ -32179,24 +32179,24 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1060" t="n">
@@ -32209,24 +32209,24 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
+          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1061" t="n">
@@ -32239,28 +32239,28 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
         </is>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
         </is>
       </c>
       <c r="C1062" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -32269,24 +32269,24 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
         </is>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -32299,12 +32299,12 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
         </is>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
         </is>
       </c>
     </row>
@@ -32316,11 +32316,11 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Strategy Language. </t>
+          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -32329,24 +32329,24 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
         </is>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
+          <t xml:space="preserve"> Proof Strategy Language. </t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -32359,24 +32359,24 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
         </is>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
+          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
+          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
         </is>
       </c>
       <c r="C1066" t="n">
@@ -32389,24 +32389,24 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
         </is>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
+          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
+          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -32419,24 +32419,24 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
         </is>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
+          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
+          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -32449,24 +32449,24 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
         </is>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
+          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
+          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -32479,24 +32479,24 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -32509,54 +32509,54 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
         </is>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
+          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
+          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
+          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
         </is>
       </c>
       <c r="C1072" t="n">
@@ -32569,19 +32569,19 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
         </is>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
@@ -32599,28 +32599,28 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -32629,24 +32629,24 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
         </is>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C1075" t="n">
@@ -32659,24 +32659,24 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
         </is>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
+          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -32689,28 +32689,28 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
         </is>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C1077" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -32719,28 +32719,28 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
         </is>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
+          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
+          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
         </is>
       </c>
       <c r="C1078" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -32749,24 +32749,24 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
         </is>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
+          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
+          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
+          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -32779,28 +32779,28 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
+          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
+          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -32809,24 +32809,24 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
+          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -32839,24 +32839,24 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
         </is>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
+          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
         </is>
       </c>
       <c r="C1082" t="n">
@@ -32869,12 +32869,12 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
         </is>
       </c>
     </row>
@@ -32886,7 +32886,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
         </is>
       </c>
       <c r="C1083" t="n">
@@ -32899,24 +32899,24 @@
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
         </is>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
+          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C1084" t="n">
@@ -32929,28 +32929,28 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
         </is>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
+          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1085" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -32959,24 +32959,24 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
         </is>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C1086" t="n">
@@ -32989,19 +32989,19 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
+          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
@@ -33019,24 +33019,24 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2025/08)</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -33049,24 +33049,24 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
+          <t xml:space="preserve"> Zenodo (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -33079,58 +33079,58 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Frantisek Dusek, Marco Tuccio, Clément Hongler </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Visualizing the Structure of Lenia Parameter Space. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1090" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FAI </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2601.01932 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2601.01932 (2026/01).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
+          <t xml:space="preserve">Barbora Hudcová, Frantisek Dusek, Marco Tuccio, Clément Hongler </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
+          <t xml:space="preserve"> Visualizing the Structure of Lenia Parameter Space. </t>
         </is>
       </c>
       <c r="C1091" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -33139,24 +33139,24 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2601.01932 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2601.01932 (2026/01).</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
+          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
+          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
         </is>
       </c>
       <c r="C1092" t="n">
@@ -33169,28 +33169,28 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
+          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
+          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -33199,24 +33199,24 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
+          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
+          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -33229,12 +33229,12 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
+          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
+          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
         </is>
       </c>
     </row>
@@ -33246,11 +33246,11 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
+          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -33259,58 +33259,58 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
+          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Aditya Gulati, Ayoub Bagheri, Nuria Oliver </t>
+          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mind the Style: Impact of Communication Style on Human-Chatbot Interaction. </t>
+          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
         </is>
       </c>
       <c r="C1096" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ML </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2602.17850 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2602.17850 (2026/02).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Aditya Gulati, Ayoub Bagheri, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
+          <t xml:space="preserve"> Mind the Style: Impact of Communication Style on Human-Chatbot Interaction. </t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -33319,24 +33319,24 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2602.17850 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2602.17850 (2026/02).</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
+          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
+          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
         </is>
       </c>
       <c r="C1098" t="n">
@@ -33349,28 +33349,28 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT read who you are? </t>
+          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -33379,24 +33379,24 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.chbah.2024.100088 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Hum. Behav. Artif. Humans 2: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
+          <t xml:space="preserve"> Can ChatGPT read who you are? </t>
         </is>
       </c>
       <c r="C1100" t="n">
@@ -33409,28 +33409,28 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.chbah.2024.100088 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
+          <t xml:space="preserve"> Comput. Hum. Behav. Artif. Humans 2: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
+          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
+          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -33439,24 +33439,24 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
+          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -33469,28 +33469,28 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efektivní metody pro učení modelů a řízení v robotice ; Data-efficient methods for model learning and control in robotics. </t>
+          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -33499,28 +33499,28 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.base-search.net/Record/3b90c2a04826d994a37adc80910808ac880f4b67e04d4782e78b8061204064db </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Erik Derner </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
+          <t xml:space="preserve"> Efektivní metody pro učení modelů a řízení v robotice ; Data-efficient methods for model learning and control in robotics. </t>
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -33529,24 +33529,24 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
+          <t xml:space="preserve"> https://www.base-search.net/Record/3b90c2a04826d994a37adc80910808ac880f4b67e04d4782e78b8061204064db </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
+          <t xml:space="preserve"> Thesis (2022).</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
+          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
@@ -33571,16 +33571,16 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
+          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -33589,28 +33589,28 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
+          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
+          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
         </is>
       </c>
       <c r="C1107" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
@@ -33619,12 +33619,12 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
         </is>
       </c>
     </row>
@@ -33640,7 +33640,7 @@
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
@@ -33649,24 +33649,24 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2007.10085 </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sensors 19: (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2007.10085 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
+          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> An Integrated Approach to Goal Selection in Mobile Robot Exploration. </t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -33679,28 +33679,28 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q64068119 </t>
         </is>
       </c>
       <c r="F1109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
+          <t xml:space="preserve"> Sensors 19: (2019).</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Kadera, Václav Jirkovský, Lukás Kurilla, Simon Prokop </t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
+          <t xml:space="preserve"> Plant Layout Optimization Using Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1110" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
@@ -33709,28 +33709,28 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-27878-6_14 </t>
         </is>
       </c>
       <c r="F1110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
+          <t xml:space="preserve"> Industrial Applications of Holonic and Multi-Agent Systems - 9th International Conference, HoloMAS 2019, Linz, Austria, August 26-29, 2019, Proceedings: 173-188 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
+          <t xml:space="preserve">Frantisek Hruska, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
+          <t xml:space="preserve"> Selection Hyper-Heuristic Using a Portfolio of Derivative Heuristics. </t>
         </is>
       </c>
       <c r="C1111" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
@@ -33739,24 +33739,24 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2739482.2764686 </t>
         </is>
       </c>
       <c r="F1111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2015, Madrid, Spain, July 11-15, 2015, Companion Material Proceedings: 1401-1402 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
+          <t xml:space="preserve">Jirí Kubalík, Michal Snizek </t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
+          <t xml:space="preserve"> A novel evolutionary algorithm with indirect representation and extended nearest neighbor constructive procedure for solving routing problems. </t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -33769,28 +33769,28 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISDA.2014.7066254 </t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
+          <t xml:space="preserve"> 14th International Conference on Intelligent Systems Design and Applications, ISDA 2014, Okinawa, Japan, November 28-30, 2014: 156-161 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Jaroslav Pokorný, Martin Víta, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
+          <t xml:space="preserve"> Generic Private Social Network for Knowledge Management. </t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
@@ -33799,24 +33799,24 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-20370-6_3 </t>
         </is>
       </c>
       <c r="F1113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
+          <t xml:space="preserve"> Web Information Systems Engineering - WISE 2014 Workshops - 15th International Workshops IWCSN 2014, Org2 2014, PCS 2014, and QUAT 2014, Thessaloniki, Greece, October 12-14, 2014, Revised Selected Papers: 27-41 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
+          <t xml:space="preserve"> Co-evolutionary Approach to Design of Robotic Gait. </t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -33829,24 +33829,24 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-37192-9_55 </t>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
+          <t xml:space="preserve"> Applications of Evolutionary Computation - 16th European Conference, EvoApplications 2013, Vienna, Austria, April 3-5, 2013. Proceedings: 550-559 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
+          <t xml:space="preserve">Jaromír Mlejnek, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
+          <t xml:space="preserve"> Evolutionary hyperheuristic for capacitated vehicle routing problem. </t>
         </is>
       </c>
       <c r="C1115" t="n">
@@ -33859,28 +33859,28 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2464576.2464684 </t>
         </is>
       </c>
       <c r="F1115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO '13, Amsterdam, The Netherlands, July 6-10, 2013, Companion Material Proceedings: 219-220 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Ján Cerný, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
+          <t xml:space="preserve"> Analysis of Co-evolutionary Approach for Robotic Gait Generation. </t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
@@ -33889,24 +33889,24 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004554900370046 </t>
         </is>
       </c>
       <c r="F1116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
+          <t xml:space="preserve"> IJCCI 2013 - Proceedings of the 5th International Joint Conference on Computational Intelligence, Vilamoura, Algarve, Portugal, 20-22 September, 2013: 37-46 (2013).</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
+          <t xml:space="preserve"> Experimental Comparison of Six Population-Based Algorithms for Continuous Black Box Optimization. </t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -33919,24 +33919,24 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51353740 </t>
         </is>
       </c>
       <c r="F1117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
+          <t xml:space="preserve"> Evol. Comput. 20: 483-508 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
+          <t xml:space="preserve">Kamil Matousek, Jirí Kubalík, Martin Necaský, Peter Vojtás </t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
+          <t xml:space="preserve"> Exploiting Potential of the Professional Social Network Portal "SitIT". </t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -33949,24 +33949,24 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-32518-2_28 </t>
         </is>
       </c>
       <c r="F1118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
+          <t xml:space="preserve"> New Trends in Databases and Information Systems, Workshop Proceedings of the 16th East European Conference, ADBIS 2012, Poznań, Poland, September 17-21, 2012: 295-304 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Michal Kopecky, Jaroslav Pokorný, Peter Vojtás, Jirí Kubalík, Kamil Matousek, Milos Maryska, Ota Novotný, Ladislav Peska </t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
+          <t xml:space="preserve"> Testing and Evaluating Software in a Social Network Creating Baseline Knowledge. </t>
         </is>
       </c>
       <c r="C1119" t="n">
@@ -33979,28 +33979,28 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.3233/978-1-61499-177-9-127 </t>
         </is>
       </c>
       <c r="F1119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
+          <t xml:space="preserve"> Information Modelling and Knowledge Bases XXIV, 22nd European-Japanese Conference on Information Modelling and Knowledge Bases (EJC 2012), Prague, Czech Republic, June, 4-9, 2012: 127-141 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Hyper-Heuristic Based on Iterated Local Search Driven by Evolutionary Algorithm. </t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
@@ -34009,24 +34009,24 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-29124-1_13 </t>
         </is>
       </c>
       <c r="F1120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization - 12th European Conference, EvoCOP 2012, Málaga, Spain, April 11-13, 2012. Proceedings: 148-159 (2012).</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochastic optimisation algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1121" t="n">
@@ -34039,24 +34039,24 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10462-010-9181-y </t>
         </is>
       </c>
       <c r="F1121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
+          <t xml:space="preserve"> Artif. Intell. Rev. 35: 19-36 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
+          <t xml:space="preserve"> Software project portfolio optimization with advanced multiobjective evolutionary algorithms. </t>
         </is>
       </c>
       <c r="C1122" t="n">
@@ -34069,24 +34069,24 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
+          <t xml:space="preserve"> https://orkg.org/orkg/resource/R28870 </t>
         </is>
       </c>
       <c r="F1122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
+          <t xml:space="preserve"> Appl. Soft Comput. 11: 1416-1426 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Peter Vojtás, Jaroslav Pokorný, Martin Necaský, Tomás Skopal, Kamil Matousek, Jirí Kubalík, Ota Novotný, Milos Maryska </t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> SoSIReČR - IT professional social network. </t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -34099,28 +34099,28 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57240537 </t>
         </is>
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
+          <t xml:space="preserve"> International Conference on Computational Aspects of Social Networks, CASoN 2011, Salamanca, Spain, October 19-21, 2011: 108-113 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
+          <t xml:space="preserve"> Evolutionary-based iterative local search algorithm for the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
@@ -34129,24 +34129,24 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2001576.2001620 </t>
         </is>
       </c>
       <c r="F1124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
+          <t xml:space="preserve"> 13th Annual Genetic and Evolutionary Computation Conference, GECCO 2011, Proceedings, Dublin, Ireland, July 12-16, 2011: 315-322 (2011).</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
+          <t xml:space="preserve">Jirí Kubalík, Pavel Tichý, Radek Sindelár, Raymond J. Staron </t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Clustering Methods for Agent Distribution Optimization. </t>
         </is>
       </c>
       <c r="C1125" t="n">
@@ -34159,24 +34159,24 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TSMCC.2009.2031093 </t>
         </is>
       </c>
       <c r="F1125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
+          <t xml:space="preserve"> IEEE Trans. Syst. Man Cybern. Part C 40: 78-86 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Buryan, Libor Wagner </t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
+          <t xml:space="preserve"> Solving the DNA fragment assembly problem efficiently using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1126" t="n">
@@ -34189,24 +34189,24 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830522 </t>
         </is>
       </c>
       <c r="F1126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 213-214 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
+          <t xml:space="preserve"> Efficient stochastic local search algorithm for solving the shortest common supersequence problem. </t>
         </is>
       </c>
       <c r="C1127" t="n">
@@ -34219,24 +34219,24 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830529 </t>
         </is>
       </c>
       <c r="F1127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 249-256 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
+          <t xml:space="preserve"> Context-sensitive refinements for stochasticoptimization algorithms in inductive logic programming. </t>
         </is>
       </c>
       <c r="C1128" t="n">
@@ -34249,24 +34249,24 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130887640 </t>
         </is>
       </c>
       <c r="F1128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1071-1072 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Thomas Kremmel, Jirí Kubalík, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
+          <t xml:space="preserve"> Multiobjective evolutionary algorithm for software project portfolio optimization. </t>
         </is>
       </c>
       <c r="C1129" t="n">
@@ -34279,24 +34279,24 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830483.1830738 </t>
         </is>
       </c>
       <c r="F1129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010: 1389-1390 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of two variants of the POEMS algorithm on the noiseless testbed. </t>
         </is>
       </c>
       <c r="C1130" t="n">
@@ -34309,28 +34309,28 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830774 </t>
         </is>
       </c>
       <c r="F1130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1567-1574 (2010).</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Petr Posík, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
+          <t xml:space="preserve"> Comparison of cauchy EDA and pPOEMS algorithms on the BBOB noiseless testbed. </t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
@@ -34339,12 +34339,12 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1830761.1830792 </t>
         </is>
       </c>
       <c r="F1131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2010, Proceedings, Portland, Oregon, USA, July 7-11, 2010, Companion Material: 1703-1710 (2010).</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34356,7 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
+          <t xml:space="preserve"> Solving the sorting network problem using iterative optimization with evolved hypermutations. </t>
         </is>
       </c>
       <c r="C1132" t="n">
@@ -34369,12 +34369,12 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1569901.1569944 </t>
         </is>
       </c>
       <c r="F1132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009: 301-308 (2009).</t>
         </is>
       </c>
     </row>
@@ -34386,7 +34386,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Black-box optimization benchmarking of prototype optimization with evolved improvement steps for noiseless function testbed. </t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -34399,24 +34399,24 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/1570256.1570321 </t>
         </is>
       </c>
       <c r="F1133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
+          <t xml:space="preserve"> Genetic and Evolutionary Computation Conference, GECCO 2009, Proceedings, Montreal, Québec, Canada, July 8-12, 2009, Companion Material: 2303-2308 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
+          <t xml:space="preserve"> Solving the Multiple Sequence Alignment Problem Using Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -34429,28 +34429,28 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-642-04921-7_19 </t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
+          <t xml:space="preserve"> Adaptive and Natural Computing Algorithms, 9th International Conference, ICANNGA 2009, Kuopio, Finland, April 23-25, 2009, Revised Selected Papers: 183-192 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
+          <t xml:space="preserve">Petr Buryan, Jirí Kubalík, Katsumi Inoue </t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Grammatical Concept Representation for Randomised Optimisation Algorithms in Relational Learning. </t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
@@ -34459,28 +34459,28 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ISDA.2009.156 </t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
+          <t xml:space="preserve"> Ninth International Conference on Intelligent Systems Design and Applications, ISDA 2009, Pisa, Italy , November 30-December 2, 2009: 1450-1455 (2009).</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi, Stefan Biffl </t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
+          <t xml:space="preserve"> Multiobjective Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
@@ -34489,28 +34489,28 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-78604-7_19 </t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
+          <t xml:space="preserve"> Evolutionary Computation in Combinatorial Optimization, 8th European Conference, EvoCOP 2008, Naples, Italy, March 26-28, 2008. Proceedings: 218-229 (2008).</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kubalík, Richard Mordinyi </t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Optimizing Events Traffic in Event-based Systems by means of Evolutionary Algorithms. </t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
@@ -34519,24 +34519,24 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/ARES.2007.113 </t>
         </is>
       </c>
       <c r="F1137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
+          <t xml:space="preserve"> Proceedings of the The Second International Conference on Availability, Reliability and Security, ARES 2007, The International Dependability Conference - Bridging Theory and Practice, April 10-13 2007, Vienna, Austria: 1101-1107 (2007).</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
+          <t xml:space="preserve">Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
+          <t xml:space="preserve"> Real-Parameter Optimization by Iterative Prototype Optimization with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1138" t="n">
@@ -34549,24 +34549,24 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/CEC.2006.1688543 </t>
         </is>
       </c>
       <c r="F1138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
+          <t xml:space="preserve"> IEEE International Conference on Evolutionary Computation, CEC 2006, part of WCCI 2006, Vancouver, BC, Canada, 16-21 July 2006: 1932-1938 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Faigl </t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
+          <t xml:space="preserve"> Iterative Prototype Optimisation with Evolved Improvement Steps. </t>
         </is>
       </c>
       <c r="C1139" t="n">
@@ -34579,28 +34579,28 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11729976_14 </t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
+          <t xml:space="preserve"> Genetic Programming, 9th European Conference, EuroGP 2006, Budapest, Hungary, April 10-12, 2006, Proceedings: 154-165 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
+          <t xml:space="preserve">Jirí Kubalík, Petr Posík, Jan Herold </t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
+          <t xml:space="preserve"> A Selecto-recombinative Genetic Algorithm with Continuous Chromosome Reconfiguration. </t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
@@ -34609,24 +34609,24 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/11844297_97 </t>
         </is>
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
+          <t xml:space="preserve"> Parallel Problem Solving from Nature - PPSN IX, 9th International Conference, Reykjavik, Iceland, September 9-13, 2006, Procedings: 959-968 (2006).</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Lenka Lhotská </t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
+          <t xml:space="preserve"> Optimized model tuning in medical systems. </t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -34639,28 +34639,28 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q51984282 </t>
         </is>
       </c>
       <c r="F1141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
+          <t xml:space="preserve"> Comput. Methods Programs Biomed. 80: S17-S28 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
+          <t xml:space="preserve">Jan Suchý, Jirí Kubalík </t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
+          <t xml:space="preserve"> Inducing Diverse Decision Forests with Genetic Programing. </t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
@@ -34669,24 +34669,24 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-31989-4_27 </t>
         </is>
       </c>
       <c r="F1142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
+          <t xml:space="preserve"> Genetic Programming, 8th European Conference, EuroGP2005, Lausanne, Switzerland, March 30 - April 1, 2005, Proceedings: 301-310 (2005).</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Kléma, Miroslav Kulich </t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Rescue Operation Planning. </t>
         </is>
       </c>
       <c r="C1143" t="n">
@@ -34699,24 +34699,24 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-540-24844-6_139 </t>
         </is>
       </c>
       <c r="F1143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
+          <t xml:space="preserve"> Artificial Intelligence and Soft Computing - ICAISC 2004, 7th International Conference, Zakopane, Poland, June 7-11, 2004, Proceedings: 897-902 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
+          <t xml:space="preserve">Milan Rollo, Petr Novák, Jirí Kubalík, Michal Pechoucek </t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
+          <t xml:space="preserve"> Alarm Root Cause Detection System. </t>
         </is>
       </c>
       <c r="C1144" t="n">
@@ -34729,28 +34729,28 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_12 </t>
         </is>
       </c>
       <c r="F1144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 109-116 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
+          <t xml:space="preserve">Jirí Kubalík, Marcel Jirina, Oldrich Starý, Lenka Lhotská, Jan Suchý </t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
+          <t xml:space="preserve"> Application of Soft Computing Techniques to Classification of Licensed Subjects. </t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
@@ -34759,28 +34759,28 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/0-387-22829-2_52 </t>
         </is>
       </c>
       <c r="F1145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
+          <t xml:space="preserve"> Emerging Solutions for Future Manufacturing Systems, IFIP TC5 / WG5.5 Sixth IFIP International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services, 27-29 September 2004, Vienna, Austria: 481-488 (2004).</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
+          <t xml:space="preserve">Jirí Kubalík, Jan Koutník, Léon J. M. Rothkrantz </t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
+          <t xml:space="preserve"> Grammatical Evolution with Bidirectional Representation. </t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
@@ -34789,24 +34789,24 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/3-540-36599-0_33 </t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
+          <t xml:space="preserve"> Genetic Programming, 6th European Conference, EuroGP 2003, Essex, UK, April 14-16, 2003. Proceedings: 354-363 (2003).</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
+          <t xml:space="preserve">Jirí Kléma, Jirí Kubalík, Jiri Palous </t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
+          <t xml:space="preserve"> Optimized Model Tuning in Medical Systems. </t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -34819,24 +34819,24 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/CBMS.2002.1011355 </t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
+          <t xml:space="preserve"> 15th IEEE Symposium on Computer-Based Medical Systems (CBMS 2002), 4-7 June 2002, Maribor, Slovenia: 59-64 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
+          <t xml:space="preserve">Jirí Kubalík, Jirí Lazanský, Petr Zikl </t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
+          <t xml:space="preserve"> Layout Problem Optimization Using Genetic Algorithms. </t>
         </is>
       </c>
       <c r="C1148" t="n">
@@ -34854,23 +34854,23 @@
       </c>
       <c r="F1148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
+          <t xml:space="preserve"> Knowledge and Technology Integration in Production and Services: Balancing Knowledge in Product and Service Life Cycle, IFIP TC5/WG5.3 Fifth IFIP/IEEE International Conference on Information Technology for Balanced Automation Systems in Manufacturing and Services (BASYS'02), September 25-27, 2002, Cancun, Mexico: 493-500 (2002).</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
+          <t xml:space="preserve">Jirí Kubalík, Léon J. M. Rothkrantz, Jirí Lazanský </t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
+          <t xml:space="preserve"> Genetic Algorithm with Limited Convergence. </t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>2026</v>
+        <v>2002</v>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
@@ -34879,12 +34879,12 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
+          <t>  </t>
         </is>
       </c>
       <c r="F1149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
+          <t xml:space="preserve"> Proceedings of the 6th Joint Conference on Information Science, March 8-13, 2002, Research Triangle Park, North Carolina, USA: 610-613 (2002).</t>
         </is>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part I </t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -34909,12 +34909,12 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6950-2 </t>
         </is>
       </c>
       <c r="F1150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16412 (2026).</t>
         </is>
       </c>
     </row>
@@ -34926,7 +34926,7 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part II </t>
         </is>
       </c>
       <c r="C1151" t="n">
@@ -34939,28 +34939,28 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6957-1 </t>
         </is>
       </c>
       <c r="F1151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16413 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
+          <t xml:space="preserve">Jakub Lokoc, Ladislav Peska, Jan Zahálka, Stevan Rudinac, Marc A. Kastner, Jingjing Chen, Min-Chun Hu, Jiaxin Wu, Ujjwal Sharma </t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
+          <t xml:space="preserve"> MultiMedia Modeling - 32nd International Conference on Multimedia Modeling, MMM 2026, Prague, Czech Republic, January 29-31, 2026, Proceedings, Part IV </t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
@@ -34969,28 +34969,28 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-981-95-6963-2 </t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
+          <t xml:space="preserve"> Lecture Notes in Computer Science 16415 (2026).</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
+          <t xml:space="preserve">Marcel Worring, Jan Zahálka, Stef van den Elzen, Maximilian T. Fischer, Daniel A. Keim </t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
+          <t xml:space="preserve"> A Multimedia Analytics Model for the Foundation Model Era. </t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1153" t="inlineStr">
         <is>
@@ -34999,12 +34999,12 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.06138 </t>
         </is>
       </c>
       <c r="F1153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.06138 (2025/04).</t>
         </is>
       </c>
     </row>
@@ -35029,28 +35029,28 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-91585-7_22 </t>
         </is>
       </c>
       <c r="F1154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
+          <t xml:space="preserve"> Computer Vision - ECCV 2024 Workshops - Milan, Italy, September 29-October 4, 2024, Proceedings, Part XVII: 363-381 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka </t>
+          <t xml:space="preserve">Max van Spengler, Jan Zahálka, Pascal Mettes </t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
+          <t xml:space="preserve"> Adversarial Attacks on Hyperbolic Networks. </t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1155" t="inlineStr">
         <is>
@@ -35059,28 +35059,28 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2412.01495 </t>
         </is>
       </c>
       <c r="F1155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2412.01495 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jan Zahálka </t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
+          <t xml:space="preserve"> Trainwreck: A damaging adversarial attack on image classifiers. </t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
@@ -35089,24 +35089,24 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14772 </t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14772 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Kim I. Schild, Alexandra M. Bagi, Magnus Holm Mamsen, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
+          <t xml:space="preserve"> XQM: Search-Oriented vs. Classifier-Oriented Relevance Feedback on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1157" t="n">
@@ -35119,24 +35119,24 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_39 </t>
         </is>
       </c>
       <c r="F1157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 458-464 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Ujjwal Sharma, Björn Þór Jónsson, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2022. </t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -35149,28 +35149,28 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-98355-0_47 </t>
         </is>
       </c>
       <c r="F1158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 28th International Conference, MMM 2022, Phu Quoc, Vietnam, June 6-10, 2022, Proceedings, Part II: 511-517 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by $p$-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
@@ -35179,24 +35179,24 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2209.00526 </t>
         </is>
       </c>
       <c r="F1159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2209.00526 (2022).</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1160" t="n">
@@ -35209,24 +35209,24 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q100732326 </t>
         </is>
       </c>
       <c r="F1160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
+          <t xml:space="preserve"> IEEE Trans. Vis. Comput. Graph. 27: 422-431 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Aaron Duane, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1161" t="n">
@@ -35239,24 +35239,24 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3463948.3469255 </t>
         </is>
       </c>
       <c r="F1161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
+          <t xml:space="preserve"> Proceedings of the 4th Annual on Lifelog Search Challenge, LSC@ICMR 2021, Taipei, Taiwan, 21 August 2021: 3-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
+          <t xml:space="preserve"> Impact of Interaction Strategies on User Relevance Feedback. </t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -35269,24 +35269,24 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3460426.3463663 </t>
         </is>
       </c>
       <c r="F1162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
+          <t xml:space="preserve"> ICMR '21: International Conference on Multimedia Retrieval, Taipei, Taiwan, August 21-24, 2021: 590-598 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
+          <t xml:space="preserve">Serhan Gül, Sebastian Bosse, Dimitri Podborski, Thomas Schierl, Cornelius Hellge, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Kalman Filter-Based Head Motion Prediction for Cloud-Based Mixed Reality. </t>
         </is>
       </c>
       <c r="C1163" t="n">
@@ -35299,24 +35299,24 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477936 </t>
         </is>
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3619-3621 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
+          <t xml:space="preserve">Jakub Nawala, Lucjan Janowski, Bogdan Cmiel, Krzysztof Rusek, Marc A. Kastner, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Describing Subjective Experiment Consistency by p-Value P-P Plot. </t>
         </is>
       </c>
       <c r="C1164" t="n">
@@ -35329,24 +35329,24 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3474085.3477935 </t>
         </is>
       </c>
       <c r="F1164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
+          <t xml:space="preserve"> MM '21: ACM Multimedia Conference, Virtual Event, China, October 20 - 24, 2021: 3627-3629 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Alexandra M. Bagi, Kim I. Schild, Omar Shahbaz Khan, Jan Zahálka, Björn Þór Jónsson </t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
+          <t xml:space="preserve"> XQM: Interactive Learning on Mobile Phones. </t>
         </is>
       </c>
       <c r="C1165" t="n">
@@ -35359,28 +35359,28 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_24 </t>
         </is>
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 281-293 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2021: Relationships Between Semantic Classifiers. </t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
@@ -35389,24 +35389,24 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-67835-7_37 </t>
         </is>
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 27th International Conference, MMM 2021, Prague, Czech Republic, June 22-24, 2021, Proceedings, Part II: 410-416 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Stevan Rudinac, Jan Zahálka, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
+          <t xml:space="preserve"> Interactive Learning for Multimedia at Large. </t>
         </is>
       </c>
       <c r="C1167" t="n">
@@ -35419,24 +35419,24 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-45439-5_33 </t>
         </is>
       </c>
       <c r="F1167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
+          <t xml:space="preserve"> Advances in Information Retrieval - 42nd European Conference on IR Research, ECIR 2020, Lisbon, Portugal, April 14-17, 2020, Proceedings, Part I: 495-510 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Mathias Dybkjær Larsen, Liam Alex Sonto Poulsen, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2020. </t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -35449,24 +35449,24 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3379172.3391718 </t>
         </is>
       </c>
       <c r="F1168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Third ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2020, Dublin, Ireland, June 8-11, 2020.: 19-22 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
+          <t xml:space="preserve">Xin Wang, Bo Wu, Yueqi Zhong, Wei Hu, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Outfit Compatibility Prediction and Diagnosis with Multi-Layered Comparison Network. </t>
         </is>
       </c>
       <c r="C1169" t="n">
@@ -35479,24 +35479,24 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414812 </t>
         </is>
       </c>
       <c r="F1169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4439-4443 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
+          <t xml:space="preserve">Tuan Hoang, Thanh-Toan Do, Ngai-Man Cheung, Michael Riegler, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
+          <t xml:space="preserve"> Reproducibility Companion Paper: Selective Deep Convolutional Features for Image Retrieval. </t>
         </is>
       </c>
       <c r="C1170" t="n">
@@ -35509,24 +35509,24 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3394171.3414814 </t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
+          <t xml:space="preserve"> MM '20: The 28th ACM International Conference on Multimedia, Virtual Event / Seattle, WA, USA, October 12-16, 2020: 4448-4452 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Dennis C. Koelma, Stevan Rudinac, Marcel Worring, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
+          <t xml:space="preserve"> Exquisitor at the Video Browser Showdown 2020. </t>
         </is>
       </c>
       <c r="C1171" t="n">
@@ -35539,28 +35539,28 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-37734-2_72 </t>
         </is>
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 26th International Conference, MMM 2020, Daejeon, South Korea, January 5-8, 2020, Proceedings, Part II: 796-802 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring, Jarke J. van Wijk </t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
+          <t xml:space="preserve"> II-20: Intelligent and pragmatic analytic categorization of image collections. </t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
@@ -35569,24 +35569,24 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.02149 </t>
         </is>
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.02149 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Omar Shahbaz Khan, Björn Þór Jónsson, Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
+          <t xml:space="preserve"> Exquisitor at the Lifelog Search Challenge 2019. </t>
         </is>
       </c>
       <c r="C1173" t="n">
@@ -35599,24 +35599,24 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3326460.3329156 </t>
         </is>
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the ACM Workshop on Lifelog Search Challenge, LSC@ICMR 2019, Ottawa, ON, Canada, 10 June 2019.: 7-11 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
+          <t xml:space="preserve">Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Omar Shahbaz Khan, Björn Þór Jónsson, Gylfi Þór Guðmundsson, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
+          <t xml:space="preserve"> Exquisitor: Breaking the Interaction Barrier for Exploration of 100 Million Images. </t>
         </is>
       </c>
       <c r="C1174" t="n">
@@ -35629,28 +35629,28 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3343031.3350580 </t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the 27th ACM International Conference on Multimedia, MM 2019, Nice, France, October 21-25, 2019: 1029-1031 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Omar Shahbaz Khan, Hanna Ragnarsdóttir, Þórhildur Þorleiksdóttir, Jan Zahálka, Stevan Rudinac, Gylfi Þór Guðmundsson, Laurent Amsaleg, Marcel Worring </t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
+          <t xml:space="preserve"> Exquisitor: Interactive Learning at Large. </t>
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1175" t="inlineStr">
         <is>
@@ -35659,28 +35659,28 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08689 </t>
         </is>
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08689 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
+          <t xml:space="preserve"> Blackthorn: Large-Scale Interactive Multimodal Learning. </t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
@@ -35689,28 +35689,28 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2017.2755986 </t>
         </is>
       </c>
       <c r="F1176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 20: 687-698 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
+          <t xml:space="preserve">Stevan Rudinac, Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
+          <t xml:space="preserve"> Discovering Geographic Regions in the City Using Social Multimedia and Open Data. </t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
@@ -35719,24 +35719,24 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-51814-5_13 </t>
         </is>
       </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 23rd International Conference, MMM 2017, Reykjavik, Iceland, January 4-6, 2017, Proceedings, Part II: 148-159 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
+          <t xml:space="preserve">Marcel Worring, Dennis C. Koelma, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
+          <t xml:space="preserve"> Multimedia Pivot Tables for Multimedia Analytics on Image Collections. </t>
         </is>
       </c>
       <c r="C1178" t="n">
@@ -35749,24 +35749,24 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2016.2614380 </t>
         </is>
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 18: 2217-2227 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Björn Þór Jónsson, Dennis C. Koelma, Marcel Worring </t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning on 100 Million Images. </t>
         </is>
       </c>
       <c r="C1179" t="n">
@@ -35779,28 +35779,28 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2911996.2912062 </t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM on International Conference on Multimedia Retrieval, ICMR 2016, New York, New York, USA, June 6-9, 2016: 333-337 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Björn Þór Jónsson, Marcel Worring, Jan Zahálka, Stevan Rudinac, Laurent Amsaleg </t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
+          <t xml:space="preserve"> Ten Research Questions for Scalable Multimedia Analytics. </t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
@@ -35809,12 +35809,12 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-27674-8_26 </t>
         </is>
       </c>
       <c r="F1180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
+          <t xml:space="preserve"> MultiMedia Modeling - 22nd International Conference, MMM 2016, Miami, FL, USA, January 4-6, 2016, Proceedings, Part II: 290-302 (2016).</t>
         </is>
       </c>
     </row>
@@ -35826,7 +35826,7 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
+          <t xml:space="preserve"> Interactive Multimodal Learning for Venue Recommendation. </t>
         </is>
       </c>
       <c r="C1181" t="n">
@@ -35839,28 +35839,28 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/TMM.2015.2480007 </t>
         </is>
       </c>
       <c r="F1181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
+          <t xml:space="preserve"> IEEE Trans. Multim. 17: 2235-2244 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Analytic Quality: Evaluation of Performance and Insight in Multimedia Collection Analysis. </t>
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
@@ -35869,12 +35869,12 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2733373.2806279 </t>
         </is>
       </c>
       <c r="F1182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
+          <t xml:space="preserve"> Proceedings of the 23rd Annual ACM Conference on Multimedia Conference, MM '15, Brisbane, Australia, October 26 - 30, 2015: 231-240 (2015).</t>
         </is>
       </c>
     </row>
@@ -35886,7 +35886,7 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
+          <t xml:space="preserve"> Knowledge-based Subtractive Integration of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1183" t="n">
@@ -35899,24 +35899,24 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
+          <t xml:space="preserve"> https://doi.org/10.5220/0004752200310039 </t>
         </is>
       </c>
       <c r="F1183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
+          <t xml:space="preserve"> BIOINFORMATICS 2014 - Proceedings of the International Conference on Bioinformatics Models, Methods and Algorithms, ESEO, Angers, Loire Valley, France, 3-6 March, 2014: 31-39 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
+          <t xml:space="preserve">Jirí Kléma, Jan Zahálka, Michael Andel, Zdenek Krejcík </t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
+          <t xml:space="preserve"> Interaction-Based Aggregation of mRNA and miRNA Expression Profiles to Differentiate Myelodysplastic Syndrome. </t>
         </is>
       </c>
       <c r="C1184" t="n">
@@ -35929,24 +35929,24 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-26129-4_11 </t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
+          <t xml:space="preserve"> Biomedical Engineering Systems and Technologies - 7th International Joint Conference, BIOSTEC 2014, Angers, France, March 3-6, 2014, Revised Selected Papers: 165-180 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
+          <t xml:space="preserve">Jan Zahálka, Marcel Worring </t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
+          <t xml:space="preserve"> Towards interactive, intelligent, and integrated multimedia analytics. </t>
         </is>
       </c>
       <c r="C1185" t="n">
@@ -35959,28 +35959,28 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
+          <t xml:space="preserve"> https://doi.ieeecomputersociety.org/10.1109/VAST.2014.7042476 </t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
+          <t xml:space="preserve"> 9th IEEE Conference on Visual Analytics Science and Technology, IEEE VAST 2014, Paris, France, October 25-31, 2014: 3-12 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
+          <t xml:space="preserve">Jan Zahálka, Stevan Rudinac, Marcel Worring </t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
+          <t xml:space="preserve"> New Yorker Melange: Interactive Brew of Personalized Venue Recommendations. </t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
@@ -35989,28 +35989,28 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2647868.2656403 </t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
+          <t xml:space="preserve"> Proceedings of the ACM International Conference on Multimedia, MM '14, Orlando, FL, USA, November 03 - 07, 2014: 205-208 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
+          <t xml:space="preserve">Jan Zahálka, Filip Zelezný </t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
+          <t xml:space="preserve"> An experimental test of Occam's razor in classification. </t>
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
@@ -36019,12 +36019,12 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10994-010-5227-2 </t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
+          <t xml:space="preserve"> Mach. Learn. 82: 475-481 (2011).</t>
         </is>
       </c>
     </row>
@@ -36036,11 +36036,11 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
+          <t xml:space="preserve"> A polynomial-time scheduling approach to minimise idle energy consumption: An application to an industrial furnace. </t>
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
@@ -36049,24 +36049,24 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.cor.2020.105167 </t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
+          <t xml:space="preserve"> Comput. Oper. Res. 128: (2021).</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
+          <t xml:space="preserve">Ondrej Benedikt, Baran Alikoc, Premysl Sucha, Sergej Celikovský, Zdenek Hanzálek </t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
+          <t xml:space="preserve"> A scheduling and control approach for an industrial furnace to minimize idle energy consumption. </t>
         </is>
       </c>
       <c r="C1189" t="n">
@@ -36079,28 +36079,28 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.07501 </t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.07501 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Kristian Hengster-Movric </t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
+          <t xml:space="preserve"> Robust cooperative synchronization of homogeneous agents with delays on directed communication graphs. </t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
@@ -36109,24 +36109,24 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1911.10359 </t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1911.10359 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
+          <t xml:space="preserve">Baran Alikoc </t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
+          <t xml:space="preserve"> Stability analysis of multiple time-delay systems and design of time-delay filters (Çoklu zaman gecikmeli sistemlerin kararlılık analizi ve gecikme tabanlı filtre tasarımı) </t>
         </is>
       </c>
       <c r="C1191" t="n">
@@ -36139,28 +36139,28 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
+          <t xml:space="preserve"> https://tez.yok.gov.tr/UlusalTezMerkezi/tezDetay.jsp?id=gLpBbQbOR-wukzWI3gxnEA&amp;no=wMc2iygZhjj_Ym6dqKnlyw </t>
         </is>
       </c>
       <c r="F1191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
+          <t xml:space="preserve">Baran Alikoc, Ali Fuat Ergenç </t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
+          <t xml:space="preserve"> A Polynomial Method for Stability Analysis of LTI Systems Independent of Delays. </t>
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
@@ -36169,28 +36169,28 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
+          <t xml:space="preserve"> https://doi.org/10.1137/16M1077726 </t>
         </is>
       </c>
       <c r="F1192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
+          <t xml:space="preserve"> SIAM J. Control. Optim. 55: 2661-2683 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
+          <t xml:space="preserve">Deniz Engules, Murat Hot, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
+          <t xml:space="preserve"> Level control of a coupled-tank system via eigenvalue assignment and LQG control. </t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
@@ -36199,28 +36199,28 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/MED.2015.7158918 </t>
         </is>
       </c>
       <c r="F1193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
+          <t xml:space="preserve"> 23rd Mediterranean Conference on Control and Automation, MED 2015, Torremolinos, Malaga, Spain, June 16-19, 2015: 1198-1203 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Warchocki, Xi Wang, Jonas Kulhanek, Jan van Gemert </t>
+          <t xml:space="preserve">Ali Fuat Ergenç, Baran Alikoc </t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Bringing a Personal Point of View: Evaluating Dynamic 3D Gaussian Splatting for Egocentric Scene Reconstruction. </t>
+          <t xml:space="preserve"> Reduced order digital controller design for plants with large time delays. </t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
@@ -36229,28 +36229,28 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2604.23803 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ISCCSP.2014.6877865 </t>
         </is>
       </c>
       <c r="F1194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2604.23803 (2026/04).</t>
+          <t xml:space="preserve"> 6th International Symposium on Communications, Control and Signal Processing, ISCCSP 2014, Athens, Greece, May 21-23, 2014: 266-269 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jan Warchocki, Xi Wang, Jonas Kulhanek, Jan van Gemert </t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> Bringing a Personal Point of View: Evaluating Dynamic 3D Gaussian Splatting for Egocentric Scene Reconstruction. </t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1195" t="inlineStr">
         <is>
@@ -36259,24 +36259,24 @@
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2604.23803 </t>
         </is>
       </c>
       <c r="F1195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2604.23803 (2026/04).</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1196" t="n">
@@ -36289,24 +36289,24 @@
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51701.2025.00732 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/3DV66043.2025.00094 </t>
         </is>
       </c>
       <c r="F1196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2025, Honolulu, HI, USA, October 19-25, 2025: 7808-7817 (2025).</t>
+          <t xml:space="preserve"> International Conference on 3D Vision, 3DV 2025, Singapore, March 25-28, 2025: 969-978 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1197" t="n">
@@ -36319,24 +36319,24 @@
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51701.2025.00732 </t>
         </is>
       </c>
       <c r="F1197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2025, Honolulu, HI, USA, October 19-25, 2025: 7808-7817 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1198" t="n">
@@ -36349,24 +36349,24 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1199" t="n">
@@ -36379,28 +36379,28 @@
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1200" t="inlineStr">
         <is>
@@ -36409,24 +36409,24 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1201" t="n">
@@ -36439,7 +36439,7 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1201" t="inlineStr">
@@ -36451,12 +36451,12 @@
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1202" t="n">
@@ -36469,24 +36469,24 @@
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -36499,24 +36499,24 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1204" t="n">
@@ -36529,24 +36529,24 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1205" t="n">
@@ -36559,28 +36559,28 @@
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1206" t="inlineStr">
         <is>
@@ -36589,12 +36589,12 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -36619,28 +36619,28 @@
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1208" t="inlineStr">
         <is>
@@ -36649,24 +36649,24 @@
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1209" t="n">
@@ -36679,28 +36679,28 @@
       </c>
       <c r="E1209" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1209" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1210" t="inlineStr">
         <is>
@@ -36709,40 +36709,70 @@
       </c>
       <c r="E1210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1211" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1211" t="inlineStr">
+      <c r="B1212" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1211" t="n">
+      <c r="C1212" t="n">
         <v>2021</v>
       </c>
-      <c r="D1211" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1211" t="inlineStr">
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1211" t="inlineStr">
+      <c r="F1212" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1213"/>
+  <dimension ref="A1:F1214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36379,24 +36379,24 @@
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2025/hash/f00475398609746d67821a02765eb8e8-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 38: Annual Conference on Neural Information Processing Systems 2025, NeurIPS 2025, San Diago, CA, USA, December 2-7, 2025 / Mexico City, Mexico, November 30 - December 5, 2025.: (2025).</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
+          <t xml:space="preserve">Jonas Kulhanek, Marie-Julie Rakotosaona, Fabian Manhardt, Christina Tsalicoglou, Michael Niemeyer, Torsten Sattler, Songyou Peng, Federico Tombari </t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
+          <t xml:space="preserve"> LODGE: Level-of-Detail Large-Scale Gaussian Splatting with Efficient Rendering. </t>
         </is>
       </c>
       <c r="C1200" t="n">
@@ -36409,24 +36409,24 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.23158 </t>
         </is>
       </c>
       <c r="F1200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.23158 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
+          <t xml:space="preserve">Jan Ackermann, Jonas Kulhanek, Shengqu Cai, Haofei Xu, Marc Pollefeys, Gordon Wetzstein, Leonidas J. Guibas, Songyou Peng </t>
         </is>
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
+          <t xml:space="preserve"> CL-Splats: Continual Learning of Gaussian Splatting with Local Optimization. </t>
         </is>
       </c>
       <c r="C1201" t="n">
@@ -36439,28 +36439,28 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.21117 </t>
         </is>
       </c>
       <c r="F1201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.21117 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Brent Yi, Chung Min Kim, Justin Kerr, Gina Wu, Rebecca Feng, Anthony Zhang, Jonas Kulhanek, Hongsuk Choi, Yi Ma, Matthew Tancik, Angjoo Kanazawa </t>
         </is>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> Viser: Imperative, Web-based 3D Visualization in Python. </t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1202" t="inlineStr">
         <is>
@@ -36469,24 +36469,24 @@
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.22885 </t>
         </is>
       </c>
       <c r="F1202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.22885 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1203" t="n">
@@ -36499,7 +36499,7 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/93397b489222f1e66a862f795fc32b96-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1203" t="inlineStr">
@@ -36511,12 +36511,12 @@
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting In the Wild. </t>
         </is>
       </c>
       <c r="C1204" t="n">
@@ -36529,24 +36529,24 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/25c0fe7b157821dd3140727dc07461da-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Tobias Fischer, Jonas Kulhanek, Samuel Rota Bulò, Lorenzo Porzi, Marc Pollefeys, Peter Kontschieder </t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
+          <t xml:space="preserve"> Dynamic 3D Gaussian Fields for Urban Areas. </t>
         </is>
       </c>
       <c r="C1205" t="n">
@@ -36559,24 +36559,24 @@
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.03175 </t>
         </is>
       </c>
       <c r="F1205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.03175 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
+          <t xml:space="preserve"> NerfBaselines: Consistent and Reproducible Evaluation of Novel View Synthesis Methods. </t>
         </is>
       </c>
       <c r="C1206" t="n">
@@ -36589,24 +36589,24 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.17345 </t>
         </is>
       </c>
       <c r="F1206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.17345 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Songyou Peng, Zuzana Kukelova, Marc Pollefeys, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
+          <t xml:space="preserve"> WildGaussians: 3D Gaussian Splatting in the Wild. </t>
         </is>
       </c>
       <c r="C1207" t="n">
@@ -36619,28 +36619,28 @@
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2407.08447 </t>
         </is>
       </c>
       <c r="F1207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2407.08447 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
+          <t xml:space="preserve">Huapeng Li, Wenxuan Song, Tianao Xu, Alexandre Elsig, Jonas Kulhanek </t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
+          <t xml:space="preserve"> WaterSplatting: Fast Underwater 3D Scene Reconstruction Using Gaussian Splatting. </t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1208" t="inlineStr">
         <is>
@@ -36649,12 +36649,12 @@
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2408.08206 </t>
         </is>
       </c>
       <c r="F1208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2408.08206 (2024).</t>
         </is>
       </c>
     </row>
@@ -36679,28 +36679,28 @@
       </c>
       <c r="E1209" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ICCV51070.2023.01692 </t>
         </is>
       </c>
       <c r="F1209" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
+          <t xml:space="preserve"> IEEE/CVF International Conference on Computer Vision, ICCV 2023, Paris, France, October 1-6, 2023: 18412-18423 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
+          <t xml:space="preserve">Jonas Kulhanek, Torsten Sattler </t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
+          <t xml:space="preserve"> Tetra-NeRF: Representing Neural Radiance Fields Using Tetrahedra. </t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D1210" t="inlineStr">
         <is>
@@ -36709,24 +36709,24 @@
       </c>
       <c r="E1210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.09987 </t>
         </is>
       </c>
       <c r="F1210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.09987 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
+          <t xml:space="preserve">Jonas Kulhanek, Vojtech Hudecek, Tomás Nekvinda, Ondrej Dusek </t>
         </is>
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
+          <t xml:space="preserve"> AuGPT: Dialogue with Pre-trained Language Models and Data Augmentation. </t>
         </is>
       </c>
       <c r="C1211" t="n">
@@ -36739,28 +36739,28 @@
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2102.05126 </t>
         </is>
       </c>
       <c r="F1211" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2102.05126 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+          <t xml:space="preserve">Niyati Bafna, Martin Vastl, Ondrej Bojar </t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+          <t xml:space="preserve"> Constrained Decoding for Technical Term Retention in English-Hindi MT. </t>
         </is>
       </c>
       <c r="C1212" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1212" t="inlineStr">
         <is>
@@ -36769,40 +36769,70 @@
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+          <t xml:space="preserve"> https://aclanthology.org/2021.icon-main.1 </t>
         </is>
       </c>
       <c r="F1212" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 18th International Conference on Natural Language Processing (ICON 2021), National Institute of Technology Silchar, Silchar, India, December 16 - 19, 2021.: 1-6 (2021).</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martin Vastl, Daniel Zeman, Rudolf Rosa </t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Predicting Typological Features in WALS using Language Embeddings and Conditional Probabilities: ÚFAL Submission to the SIGTYP 2020 Shared Task. </t>
+        </is>
+      </c>
+      <c r="C1213" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.03920 </t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.03920 (2020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
           <t xml:space="preserve">Eduard Alibekov </t>
         </is>
       </c>
-      <c r="B1213" t="inlineStr">
+      <c r="B1214" t="inlineStr">
         <is>
           <t xml:space="preserve"> Symbolická regrese pro posilováné učení ve spojitých prostorech ; Symbolic Regression for Reinforcement Learning in Continuous Spaces. </t>
         </is>
       </c>
-      <c r="C1213" t="n">
+      <c r="C1214" t="n">
         <v>2021</v>
       </c>
-      <c r="D1213" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ML </t>
-        </is>
-      </c>
-      <c r="E1213" t="inlineStr">
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ML </t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
         <is>
           <t xml:space="preserve"> https://www.base-search.net/Record/adc5665431fac69d2897c0473e98e72c38f733324eec38c258b5d74cb3cb3c95 </t>
         </is>
       </c>
-      <c r="F1213" t="inlineStr">
+      <c r="F1214" t="inlineStr">
         <is>
           <t xml:space="preserve"> Thesis (2021).</t>
         </is>

--- a/docs/download/publications.xlsx
+++ b/docs/download/publications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1214"/>
+  <dimension ref="A1:F1215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29671,16 +29671,16 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Paths with Applications to Proof Checking. </t>
         </is>
       </c>
       <c r="C976" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -29689,24 +29689,24 @@
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2605.29763 </t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 11176-11184 (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2605.29763 (2026/05).</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -29719,24 +29719,24 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v39i11.33215 </t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
+          <t xml:space="preserve"> Thirty-Ninth AAAI Conference on Artificial Intelligence, Thirty-Seventh Conference on Innovative Applications of Artificial Intelligence, Fifteenth Symposium on Educational Advances in Artificial Intelligence, AAAI 2025, Philadelphia, PA, USA, February 25 - March 4, 2025: 11176-11184 (2025).</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C978" t="n">
@@ -29749,24 +29749,24 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.CP.2025.12 </t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
+          <t xml:space="preserve"> 31st International Conference on Principles and Practice of Constraint Programming, CP 2025, Glasgow, Scotland, August 10-15, 2025: 12:1-12:26 (2025).</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -29779,24 +29779,24 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2025.11 </t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
+          <t xml:space="preserve"> 28th International Conference on Theory and Applications of Satisfiability Testing, SAT 2025, Glasgow, Scotland, August 12-15, 2025: 11:1-11:24 (2025).</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
+          <t xml:space="preserve"> MichaelHartisch/EQuIPS. </t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -29809,24 +29809,24 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/artifacts.24095 </t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
+          <t xml:space="preserve"> DROPS Artifacts (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
+          <t xml:space="preserve"> Better Extension Variables in DQBF via Independence. </t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -29839,24 +29839,24 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2505.20069 </t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2505.20069 (2025/05).</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
+          <t xml:space="preserve">Michael Hartisch, Leroy Chew </t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
+          <t xml:space="preserve"> An Expansion-Based Approach for Quantified Integer Programming. </t>
         </is>
       </c>
       <c r="C982" t="n">
@@ -29869,28 +29869,28 @@
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2506.04452 </t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2506.04452 (2025/06).</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Leroy Chew, Tomás Peitl </t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Strong (D)QBF Dependency Schemes via Pure Universal Resolution Paths. </t>
         </is>
       </c>
       <c r="C983" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -29899,24 +29899,24 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2025/149 </t>
         </is>
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2025).</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C984" t="n">
@@ -29929,24 +29929,24 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
+          <t xml:space="preserve"> https://doi.org/10.46298/lmcs-20(1:14)2024 </t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 20: (2024).</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C985" t="n">
@@ -29959,24 +29959,24 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/aaai.v38i8.28635 </t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
+          <t xml:space="preserve"> Thirty-Eighth AAAI Conference on Artificial Intelligence, AAAI 2024, Thirty-Sixth Conference on Innovative Applications of Artificial Intelligence, IAAI 2024, Fourteenth Symposium on Educational Advances in Artificial Intelligence, EAAI 2014, February 20-27, 2024, Vancouver, Canada: 7978-7986 (2024).</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -29989,24 +29989,24 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2024.18 </t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
+          <t xml:space="preserve"> 44th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2024, Gandhinagar, Gujarat, India, December 16-18, 2024: 18:1-18:23 (2024).</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Stefan Szeider </t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
+          <t xml:space="preserve"> ASP-QRAT: A Conditionally Optimal Dual Proof System for ASP. </t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -30019,24 +30019,24 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/kr.2024/24 </t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
+          <t xml:space="preserve"> Proceedings of the 21st International Conference on Principles of Knowledge Representation and Reasoning, KR 2024, Hanoi, Vietnam. November 2-8, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
+          <t xml:space="preserve"> Hardness of Random Reordered Encodings of Parity for Resolution and CDCL. </t>
         </is>
       </c>
       <c r="C988" t="n">
@@ -30049,28 +30049,28 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2402.00542 </t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2402.00542 (2024).</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Anil Shukla </t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
+          <t xml:space="preserve"> Circuits, Proofs and Propositional Model Counting. </t>
         </is>
       </c>
       <c r="C989" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -30079,24 +30079,24 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2024/081 </t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2023/12)</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2024).</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Alexis de Colnet, Friedrich Slivovsky, Stefan Szeider </t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
+          <t xml:space="preserve"> Dataset of Random Reordered Encodings of Parity Problems. </t>
         </is>
       </c>
       <c r="C990" t="n">
@@ -30109,24 +30109,24 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.10391790 </t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
+          <t xml:space="preserve"> Zenodo (2023/12)</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Sravanthi Chede, Leroy Chew, Balesh Kumar, Anil Shukla </t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
+          <t xml:space="preserve"> Understanding Nullstellensatz for QBFs. </t>
         </is>
       </c>
       <c r="C991" t="n">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/129 </t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
@@ -30151,16 +30151,16 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
+          <t xml:space="preserve"> Proof Simulation via Round-based Strategy Extraction for QBF. </t>
         </is>
       </c>
       <c r="C992" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -30169,24 +30169,24 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2023/053 </t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2023).</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Relating Existing Powerful Proof Systems for QBF. </t>
         </is>
       </c>
       <c r="C993" t="n">
@@ -30199,12 +30199,12 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.SAT.2022.10 </t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
+          <t xml:space="preserve"> 25th International Conference on Theory and Applications of Satisfiability Testing, SAT 2022, Haifa, Israel, August 2-5, 2022: 10:1-10:22 (2022).</t>
         </is>
       </c>
     </row>
@@ -30229,28 +30229,28 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2022.22 </t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
+          <t xml:space="preserve"> 39th International Symposium on Theoretical Aspects of Computer Science, STACS 2022, Marseille, France (Virtual Conference), March 15-18, 2022: 22:1-22:23 (2022).</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C995" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -30259,24 +30259,24 @@
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2210.07085 </t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2210.07085 (2022).</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C996" t="n">
@@ -30289,24 +30289,24 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-80223-3_8 </t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2021 - 24th International Conference, Barcelona, Spain, July 5-9, 2021, Proceedings: 98-115 (2021).</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C997" t="n">
@@ -30319,28 +30319,28 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
+          <t xml:space="preserve"> https://doi.org/10.1609/socs.v12i1.18591 </t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
+          <t xml:space="preserve"> Proceedings of the Fourteenth International Symposium on Combinatorial Search, SOCS 2021, Virtual Conference [Jinan, China], July 26-30, 2021: 225-227 (2021).</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
+          <t xml:space="preserve">Leroy Chew, Friedrich Slivovsky </t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
+          <t xml:space="preserve"> Towards Uniform Certification in QBF. </t>
         </is>
       </c>
       <c r="C998" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -30349,24 +30349,24 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2021/144 </t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2021).</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew, Ján Pich </t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> Frege Systems for Quantified Boolean Logic. </t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -30379,24 +30379,24 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q118123548 </t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
+          <t xml:space="preserve"> J. ACM 67: 9:1-9:36 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C1000" t="n">
@@ -30409,24 +30409,24 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51074-9_5 </t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
+          <t xml:space="preserve"> Automated Reasoning - 10th International Joint Conference, IJCAR 2020, Paris, France, July 1-4, 2020, Proceedings, Part I: 66-82 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
+          <t xml:space="preserve">Leroy Chew, Marijn J. H. Heule </t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
+          <t xml:space="preserve"> Sorting Parity Encodings by Reusing Variables. </t>
         </is>
       </c>
       <c r="C1001" t="n">
@@ -30439,24 +30439,24 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-51825-7_1 </t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2020 - 23rd International Conference, Alghero, Italy, July 3-10, 2020, Proceedings: 1-10 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Zhenjun Liu, Leroy Chew, Marijn Heule </t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
+          <t xml:space="preserve"> Avoiding Monochromatic Rectangles Using Shift Patterns. </t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -30469,28 +30469,28 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2012.12582 </t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2012.12582 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Relating existing powerful proof systems for QBF. </t>
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -30499,24 +30499,24 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2020/159 </t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2020).</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C1004" t="n">
@@ -30529,24 +30529,24 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835449 </t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
+          <t xml:space="preserve"> J. Comput. Syst. Sci. 104: 82-101 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -30559,12 +30559,12 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_2 </t>
         </is>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 19-35 (2019).</t>
         </is>
       </c>
     </row>
@@ -30589,12 +30589,12 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-24258-9_7 </t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
+          <t xml:space="preserve"> Theory and Applications of Satisfiability Testing - SAT 2019 - 22nd International Conference, SAT 2019, Lisbon, Portugal, July 9-12, 2019, Proceedings: 100-116 (2019).</t>
         </is>
       </c>
     </row>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
+          <t xml:space="preserve"> The Equivalences of Refutational QRAT. </t>
         </is>
       </c>
       <c r="C1007" t="n">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/076 </t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
@@ -30631,16 +30631,16 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Chew, Judith Clymo </t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
+          <t xml:space="preserve"> How QBF Expansion Makes Strategy Extraction Hard. </t>
         </is>
       </c>
       <c r="C1008" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -30649,12 +30649,12 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2019/157 </t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2019).</t>
         </is>
       </c>
     </row>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
+          <t xml:space="preserve"> Understanding cutting planes for QBFs. </t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -30679,24 +30679,24 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q63378008 </t>
         </is>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
+          <t xml:space="preserve"> Inf. Comput. 262: 141-161 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution Is &lt;i&gt;Not&lt;/i&gt; So Simple. </t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -30709,24 +30709,24 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59885771 </t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
+          <t xml:space="preserve"> ACM Trans. Comput. Log. 19: 1:1-1:26 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Judith Clymo, Meena Mahajan </t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
+          <t xml:space="preserve"> Short Proofs in QBF Expansion. </t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -30739,7 +30739,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/102 </t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
@@ -30751,16 +30751,16 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leroy Nicholas Chew </t>
+          <t xml:space="preserve">Leroy Chew </t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> QBF proof complexity. </t>
+          <t xml:space="preserve"> Hardness and Optimality in QBF Proof Systems Modulo NP. </t>
         </is>
       </c>
       <c r="C1012" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -30769,24 +30769,24 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2018/178 </t>
         </is>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2017).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2018).</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Leroy Nicholas Chew </t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> QBF proof complexity. </t>
         </is>
       </c>
       <c r="C1013" t="n">
@@ -30799,12 +30799,12 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
+          <t xml:space="preserve"> http://etheses.whiterose.ac.uk/18281/ </t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
+          <t xml:space="preserve"> Thesis (2017).</t>
         </is>
       </c>
     </row>
@@ -30816,7 +30816,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1014" t="n">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
+          <t xml:space="preserve"> https://doi.org/10.23638/LMCS-13(2:7)2017 </t>
         </is>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
+          <t xml:space="preserve"> Log. Methods Comput. Sci. 13: (2017).</t>
         </is>
       </c>
     </row>
@@ -30850,7 +30850,7 @@
         </is>
       </c>
       <c r="C1015" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -30859,24 +30859,24 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2017/037 </t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2017).</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
+          <t xml:space="preserve"> Understanding Cutting Planes for QBFs. </t>
         </is>
       </c>
       <c r="C1016" t="n">
@@ -30889,24 +30889,24 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.FSTTCS.2016.40 </t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
+          <t xml:space="preserve"> 36th IARCS Annual Conference on Foundations of Software Technology and Theoretical Computer Science, FSTTCS 2016, Chennai, India, December 13-15, 2016: 40:1-40:15 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Lower Bounds: From Circuits to QBF Proof Systems. </t>
         </is>
       </c>
       <c r="C1017" t="n">
@@ -30919,12 +30919,12 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59895095 </t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 2016 ACM Conference on Innovations in Theoretical Computer Science, Cambridge, MA, USA, January 14-16, 2016: 249-260 (2016).</t>
         </is>
       </c>
     </row>
@@ -30936,7 +30936,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -30949,12 +30949,12 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
+          <t xml:space="preserve"> https://doi.org/10.4230/LIPIcs.STACS.2016.15 </t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
+          <t xml:space="preserve"> 33rd Symposium on Theoretical Aspects of Computer Science, STACS 2016, Orléans, France, February 17-20, 2016: 15:1-15:14 (2016).</t>
         </is>
       </c>
     </row>
@@ -30970,7 +30970,7 @@
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -30979,24 +30979,24 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1611.01328 </t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1611.01328 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1020" t="n">
@@ -31009,24 +31009,24 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835453 </t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
+          <t xml:space="preserve"> Automata, Languages, and Programming - 42nd International Colloquium, ICALP 2015, Kyoto, Japan, July 6-10, 2015, Proceedings, Part I: 180-192 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
+          <t xml:space="preserve"> A Game Characterisation of Tree-like Q-resolution Size. </t>
         </is>
       </c>
       <c r="C1021" t="n">
@@ -31039,24 +31039,24 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q61835452 </t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
+          <t xml:space="preserve"> Language and Automata Theory and Applications - 9th International Conference, LATA 2015, Nice, France, March 2-6, 2015, Proceedings: 486-498 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Ilario Bonacina, Leroy Chew </t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
+          <t xml:space="preserve"> Lower bounds: from circuits to QBF proof systems. </t>
         </is>
       </c>
       <c r="C1022" t="n">
@@ -31069,7 +31069,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/133 </t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
@@ -31086,7 +31086,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
+          <t xml:space="preserve"> Feasible Interpolation for QBF Resolution Calculi. </t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -31099,7 +31099,7 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/059 </t>
         </is>
       </c>
       <c r="F1023" t="inlineStr">
@@ -31111,16 +31111,16 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Meena Mahajan, Anil Shukla </t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Are Short Proofs Narrow? QBF Resolution is not Simple. </t>
         </is>
       </c>
       <c r="C1024" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -31129,12 +31129,12 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2015/152 </t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2015).</t>
         </is>
       </c>
     </row>
@@ -31146,7 +31146,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -31159,12 +31159,12 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q59900280 </t>
         </is>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
+          <t xml:space="preserve"> Automated Reasoning - 7th International Joint Conference, IJCAR 2014, Held as Part of the Vienna Summer of Logic, VSL 2014, Vienna, Austria, July 19-22, 2014. Proceedings: 403-417 (2014).</t>
         </is>
       </c>
     </row>
@@ -31176,7 +31176,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -31189,12 +31189,12 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.1565 </t>
         </is>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
-          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.1565 (2014).</t>
         </is>
       </c>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
+          <t xml:space="preserve"> The Complexity of Theorem Proving in Circumscription and Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/014 </t>
         </is>
       </c>
       <c r="F1027" t="inlineStr">
@@ -31231,12 +31231,12 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew </t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
+          <t xml:space="preserve"> Tableau vs. Sequent Calculi for Minimal Entailment. </t>
         </is>
       </c>
       <c r="C1028" t="n">
@@ -31249,7 +31249,7 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/032 </t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
@@ -31261,30 +31261,30 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Olaf Beyersdorff, Leroy Chew, Karteek Sreenivasaiah </t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
+          <t xml:space="preserve"> A game characterisation of tree-like Q-Resolution size. </t>
         </is>
       </c>
       <c r="C1029" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AR </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
+          <t xml:space="preserve"> https://eccc.weizmann.ac.il/report/2014/131 </t>
         </is>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
+          <t xml:space="preserve"> informal Electron. Colloquium Comput. Complex. (2014).</t>
         </is>
       </c>
     </row>
@@ -31296,11 +31296,11 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
+          <t xml:space="preserve"> Program Synthesis for the OEIS. </t>
         </is>
       </c>
       <c r="C1030" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -31309,12 +31309,12 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2202.11908 </t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2202.11908 (2022).</t>
         </is>
       </c>
     </row>
@@ -31326,11 +31326,11 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
+          <t xml:space="preserve"> Learned Provability Likelihood for Tactical Search. </t>
         </is>
       </c>
       <c r="C1031" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -31339,12 +31339,12 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2109.03234 </t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the 9th International Symposium on Symbolic Computation in Software Science, SCSS 2021, Hagenberg, Austria, September 8-10, 2021.: 78-85 (2021).</t>
         </is>
       </c>
     </row>
@@ -31356,7 +31356,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning for Synthesizing Functions in Higher-Order Logic. </t>
         </is>
       </c>
       <c r="C1032" t="n">
@@ -31369,12 +31369,12 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/7jmg </t>
         </is>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
+          <t xml:space="preserve"> LPAR 2020: 23rd International Conference on Logic for Programming, Artificial Intelligence and Reasoning, Alicante, Spain, May 22-27, 2020.: 230-248 (2020).</t>
         </is>
       </c>
     </row>
@@ -31399,28 +31399,28 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_18 </t>
         </is>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 278-283 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
+          <t xml:space="preserve"> Tree Neural Networks in HOL4. </t>
         </is>
       </c>
       <c r="C1034" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -31429,24 +31429,24 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.01827 </t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.01827 (2020).</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
+          <t xml:space="preserve"> Aligning concepts across proof assistant libraries. </t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -31459,28 +31459,28 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482111 </t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
+          <t xml:space="preserve"> J. Symb. Comput. 90: 89-123 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
+          <t xml:space="preserve">Thibault Gauthier </t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
+          <t xml:space="preserve"> Deep Reinforcement Learning in HOL4. </t>
         </is>
       </c>
       <c r="C1036" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -31489,28 +31489,28 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1910.11797 </t>
         </is>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1910.11797 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Dennis Müller, Thibault Gauthier, Cezary Kaliszyk, Michael Kohlhase, Florian Rabe </t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Classification of Alignments Between Concepts of Formal Mathematical Systems. </t>
         </is>
       </c>
       <c r="C1037" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -31519,12 +31519,12 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q57389271 </t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 10th International Conference, CICM 2017, Edinburgh, UK, July 17-21, 2017, Proceedings: 83-98 (2017).</t>
         </is>
       </c>
     </row>
@@ -31536,7 +31536,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -31549,12 +31549,12 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482158 </t>
         </is>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
+          <t xml:space="preserve"> Proceedings of the 2015 Conference on Certified Programs and Proofs, CPP 2015, Mumbai, India, January 15-17, 2015: 49-57 (2015).</t>
         </is>
       </c>
     </row>
@@ -31566,7 +31566,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light Proof Knowledge. </t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -31579,12 +31579,12 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482162 </t>
         </is>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
+          <t xml:space="preserve"> Logic for Programming, Artificial Intelligence, and Reasoning - 20th International Conference, LPAR-20 2015, Suva, Fiji, November 24-28, 2015, Proceedings: 372-386 (2015).</t>
         </is>
       </c>
     </row>
@@ -31596,7 +31596,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
+          <t xml:space="preserve"> Sharing HOL4 and HOL Light proof knowledge. </t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -31609,28 +31609,28 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03527 </t>
         </is>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03527 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
+          <t xml:space="preserve"> Premise Selection and External Provers for HOL4. </t>
         </is>
       </c>
       <c r="C1041" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -31639,24 +31639,24 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1509.03534 </t>
         </is>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1509.03534 (2015).</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk, Chantal Keller, Michael Norrish </t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
+          <t xml:space="preserve"> Beagle as a HOL4 external ATP method. </t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -31669,12 +31669,12 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
+          <t xml:space="preserve"> https://doi.org/10.29007/8xbv </t>
         </is>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
+          <t xml:space="preserve"> 4th Workshop on Practical Aspects of Automated Reasoning, PAAR@IJCAR 2014, Vienna, Austria, 2014: 50-59 (2014).</t>
         </is>
       </c>
     </row>
@@ -31686,7 +31686,7 @@
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
+          <t xml:space="preserve"> Matching Concepts across HOL Libraries. </t>
         </is>
       </c>
       <c r="C1043" t="n">
@@ -31699,28 +31699,28 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q108482167 </t>
         </is>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - International Conference, CICM 2014, Coimbra, Portugal, July 7-11, 2014. Proceedings: 267-281 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Blaauwbroek </t>
+          <t xml:space="preserve">Thibault Gauthier, Cezary Kaliszyk </t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
+          <t xml:space="preserve"> Matching concepts across HOL libraries. </t>
         </is>
       </c>
       <c r="C1044" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -31729,28 +31729,28 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1405.3906 </t>
         </is>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1405.3906 (2014).</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Lasse Blaauwbroek </t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> The Tactician's Web of Large-Scale Formal Knowledge. </t>
         </is>
       </c>
       <c r="C1045" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -31759,12 +31759,12 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.02950 </t>
         </is>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.02950 (2024).</t>
         </is>
       </c>
     </row>
@@ -31776,11 +31776,11 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
+          <t xml:space="preserve"> Faster Smarter Proof by Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1046" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -31789,12 +31789,12 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
+          <t xml:space="preserve"> https://doi.org/10.24963/ijcai.2021/273 </t>
         </is>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
+          <t xml:space="preserve"> Proceedings of the Thirtieth International Joint Conference on Artificial Intelligence, IJCAI 2021, Virtual Event / Montreal, Canada, 19-27 August 2021.: 1981-1988 (2021).</t>
         </is>
       </c>
     </row>
@@ -31806,7 +31806,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (Tool Paper). </t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -31819,12 +31819,12 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2020/isbn.978-3-85448-042-6_32 </t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
+          <t xml:space="preserve"> 2020 Formal Methods in Computer Aided Design, FMCAD 2020, Haifa, Israel, September 21-24, 2020: 245-254 (2020).</t>
         </is>
       </c>
     </row>
@@ -31836,7 +31836,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -31849,12 +31849,12 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-53518-6_21 </t>
         </is>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 13th International Conference, CICM 2020, Bertinoro, Italy, July 26-31, 2020, Proceedings: 297-302 (2020).</t>
         </is>
       </c>
     </row>
@@ -31866,7 +31866,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
+          <t xml:space="preserve"> Smart Induction for Isabelle/HOL (System Description). </t>
         </is>
       </c>
       <c r="C1049" t="n">
@@ -31879,12 +31879,12 @@
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2001.10834 </t>
         </is>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2001.10834 (2020).</t>
         </is>
       </c>
     </row>
@@ -31896,7 +31896,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Simple Dataset for Proof Method Recommendation in Isabelle/HOL (Dataset Description). </t>
         </is>
       </c>
       <c r="C1050" t="n">
@@ -31909,12 +31909,12 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2004.10667 </t>
         </is>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2004.10667 (2020).</t>
         </is>
       </c>
     </row>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
+          <t xml:space="preserve"> Towards United Reasoning for Automatic Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1051" t="n">
@@ -31939,12 +31939,12 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2005.12737 </t>
         </is>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2005.12737 (2020).</t>
         </is>
       </c>
     </row>
@@ -31956,7 +31956,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Faster Smarter Induction in Isabelle/HOL with SeLFiE. </t>
         </is>
       </c>
       <c r="C1052" t="n">
@@ -31969,12 +31969,12 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2009.09215 </t>
         </is>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2009.09215 (2020).</t>
         </is>
       </c>
     </row>
@@ -31986,11 +31986,11 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> SeLFiE: Modular Semantic Reasoning for Induction in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1053" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -31999,12 +31999,12 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
+          <t xml:space="preserve"> https://arxiv.org/abs/2010.10296 </t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2010.10296 (2020).</t>
         </is>
       </c>
     </row>
@@ -32016,7 +32016,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1054" t="n">
@@ -32029,12 +32029,12 @@
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-030-34175-6_14 </t>
         </is>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
+          <t xml:space="preserve"> Programming Languages and Systems - 17th Asian Symposium, APLAS 2019, Nusa Dua, Bali, Indonesia, December 1-4, 2019, Proceedings: 266-287 (2019).</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards evolutionary theorem proving for isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -32059,12 +32059,12 @@
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3319619.3321921 </t>
         </is>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
+          <t xml:space="preserve"> Proceedings of the Genetic and Evolutionary Computation Conference Companion, GECCO 2019, Prague, Czech Republic, July 13-17, 2019.: 419-420 (2019).</t>
         </is>
       </c>
     </row>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Evolutionary Theorem Proving for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1056" t="n">
@@ -32089,12 +32089,12 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1904.08468 </t>
         </is>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1904.08468 (2019).</t>
         </is>
       </c>
     </row>
@@ -32106,7 +32106,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Designing Game of Theorems. </t>
+          <t xml:space="preserve"> LiFtEr: Language to Encode Induction Heuristics for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08084 </t>
         </is>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08084 (2019).</t>
         </is>
       </c>
     </row>
@@ -32136,7 +32136,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
+          <t xml:space="preserve"> Designing Game of Theorems. </t>
         </is>
       </c>
       <c r="C1058" t="n">
@@ -32149,28 +32149,28 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1906.08549 </t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1906.08549 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Domain-Specific Language to Encode Induction Heuristics. </t>
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -32179,24 +32179,24 @@
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1907.02594 </t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1907.02594 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
+          <t xml:space="preserve"> PaMpeR: proof method recommendation system for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1060" t="n">
@@ -32209,12 +32209,12 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/3238147.3238210 </t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
+          <t xml:space="preserve"> Proceedings of the 33rd ACM/IEEE International Conference on Automated Software Engineering, ASE 2018, Montpellier, France, September 3-7, 2018: 362-372 (2018).</t>
         </is>
       </c>
     </row>
@@ -32239,24 +32239,24 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-96812-4_19 </t>
         </is>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 11th International Conference, CICM 2018, Hagenberg, Austria, August 13-17, 2018, Proceedings: 225-231 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
+          <t xml:space="preserve">Yutaka Nagashima, Julian Parsert </t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Goal-Oriented Conjecturing for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -32269,24 +32269,24 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.04774 </t>
         </is>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.04774 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Yilun He </t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
+          <t xml:space="preserve"> PaMpeR: Proof Method Recommendation System for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -32299,28 +32299,28 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1806.07239 </t>
         </is>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1806.07239 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
+          <t xml:space="preserve"> Towards Machine Learning Mathematical Induction. </t>
         </is>
       </c>
       <c r="C1064" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -32329,24 +32329,24 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1812.04088 </t>
         </is>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1812.04088 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -32359,12 +32359,12 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-63046-5_32 </t>
         </is>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
+          <t xml:space="preserve"> Automated Deduction - CADE 26 - 26th International Conference on Automated Deduction, Gothenburg, Sweden, August 6-11, 2017, Proceedings: 528-545 (2017).</t>
         </is>
       </c>
     </row>
@@ -32376,11 +32376,11 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proof Strategy Language. </t>
+          <t xml:space="preserve"> Towards Smart Proof Search for Isabelle. </t>
         </is>
       </c>
       <c r="C1066" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -32389,24 +32389,24 @@
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1701.03037 </t>
         </is>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1701.03037 (2017).</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
+          <t xml:space="preserve">Yutaka Nagashima </t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
+          <t xml:space="preserve"> Proof Strategy Language. </t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -32419,24 +32419,24 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/Proof_Strategy_Language.shtml </t>
         </is>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2016: (2016).</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
+          <t xml:space="preserve">Sidney Amani, Alex Hixon, Zilin Chen, Christine Rizkallah, Peter Chubb, Liam O'Connor, Joel Beeren, Yutaka Nagashima, Japheth Lim, Thomas Sewell, Joseph Tuong, Gabriele Keller, Toby C. Murray, Gerwin Klein, Gernot Heiser </t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
+          <t xml:space="preserve"> CoGENT: Verifying High-Assurance File System Implementations. </t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -32449,24 +32449,24 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
+          <t xml:space="preserve"> https://doi.org/10.1145/2980024.2872404 </t>
         </is>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the Twenty-First International Conference on Architectural Support for Programming Languages and Operating Systems, ASPLOS 2016, Atlanta, GA, USA, April 2-6, 2016: 175-188 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
+          <t xml:space="preserve">Liam O'Connor, Zilin Chen, Christine Rizkallah, Sidney Amani, Japheth Lim, Toby C. Murray, Yutaka Nagashima, Thomas Sewell, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
+          <t xml:space="preserve"> Refinement through restraint: bringing down the cost of verification. </t>
         </is>
       </c>
       <c r="C1069" t="n">
@@ -32479,24 +32479,24 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q130970044 </t>
         </is>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
+          <t xml:space="preserve"> Proceedings of the 21st ACM SIGPLAN International Conference on Functional Programming, ICFP 2016, Nara, Japan, September 18-22, 2016: 89-102 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
+          <t xml:space="preserve">Christine Rizkallah, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Zilin Chen, Liam O'Connor, Toby C. Murray, Gabriele Keller, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
+          <t xml:space="preserve"> A Framework for the Automatic Formal Verification of Refinement from Cogent to C. </t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -32509,24 +32509,24 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-319-43144-4_20 </t>
         </is>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
+          <t xml:space="preserve"> Interactive Theorem Proving - 7th International Conference, ITP 2016, Nancy, France, August 22-25, 2016, Proceedings: 323-340 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
+          <t xml:space="preserve">Liam O'Connor, Christine Rizkallah, Zilin Chen, Sidney Amani, Japheth Lim, Yutaka Nagashima, Thomas Sewell, Alex Hixon, Gabriele Keller, Toby C. Murray, Gerwin Klein </t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
+          <t xml:space="preserve"> COGENT: Certified Compilation for a Functional Systems Language. </t>
         </is>
       </c>
       <c r="C1071" t="n">
@@ -32539,24 +32539,24 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1601.05520 </t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1601.05520 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
+          <t xml:space="preserve">Yutaka Nagashima, Ramana Kumar </t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
+          <t xml:space="preserve"> A Proof Strategy Language and Proof Script Generation for Isabelle. </t>
         </is>
       </c>
       <c r="C1072" t="n">
@@ -32569,54 +32569,54 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1606.02941 </t>
         </is>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1606.02941 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
+          <t xml:space="preserve">Yutaka Nagashima, Liam O'Connor </t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
+          <t xml:space="preserve"> Close Encounters of the Higher Kind Emulating Constructor Classes in Standard ML. </t>
         </is>
       </c>
       <c r="C1073" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FM </t>
+          <t xml:space="preserve"> AR </t>
         </is>
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
+          <t xml:space="preserve"> http://arxiv.org/abs/1608.03350 </t>
         </is>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/1608.03350 (2016).</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Maciej Mikula, Szymon Tworkowski, Szymon Antoniak, Bartosz Piotrowski, Albert Q. Jiang, Jin Peng Zhou, Christian Szegedy, Lukasz Kucinski, Piotr Milos, Yuhuai Wu </t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
+          <t xml:space="preserve"> Magnushammer: A Transformer-Based Approach to Premise Selection. </t>
         </is>
       </c>
       <c r="C1074" t="n">
@@ -32629,19 +32629,19 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
+          <t xml:space="preserve"> https://openreview.net/forum?id=oYjPk8mqAV </t>
         </is>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
+          <t xml:space="preserve"> The Twelfth International Conference on Learning Representations, ICLR 2024, Vienna, Austria, May 7-11, 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
+          <t xml:space="preserve">Albert Q. Jiang, Alicja Ziarko, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
@@ -32659,28 +32659,28 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
+          <t xml:space="preserve"> http://papers.nips.cc/paper_files/paper/2024/hash/707a2d58641b2192203b4bf4c532cfe1-Abstract-Conference.html </t>
         </is>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
+          <t xml:space="preserve"> Advances in Neural Information Processing Systems 37: Annual Conference on Neural Information Processing Systems 2024, NeurIPS 2024, Vancouver, BC, Canada, December 10 - 15, 2024.: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Alicja Ziarko, Albert Q. Jiang, Bartosz Piotrowski, Wenda Li, Mateja Jamnik, Piotr Milos </t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> Repurposing Language Models into Embedding Models: Finding the Compute-Optimal Recipe. </t>
         </is>
       </c>
       <c r="C1076" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -32689,24 +32689,24 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.04165 </t>
         </is>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.04165 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -32719,24 +32719,24 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-43513-3_10 </t>
         </is>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
+          <t xml:space="preserve"> Automated Reasoning with Analytic Tableaux and Related Methods - 32nd International Conference, TABLEAUX 2023, Prague, Czech Republic, September 18-21, 2023, Proceedings: 175-186 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
+          <t xml:space="preserve">Zhangir Azerbayev, Bartosz Piotrowski, Hailey Schoelkopf, Edward W. Ayers, Dragomir Radev, Jeremy Avigad </t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
+          <t xml:space="preserve"> ProofNet: Autoformalizing and Formally Proving Undergraduate-Level Mathematics. </t>
         </is>
       </c>
       <c r="C1078" t="n">
@@ -32749,28 +32749,28 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2302.12433 </t>
         </is>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2302.12433 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
+          <t xml:space="preserve">Bartosz Piotrowski, Ramon Fernández Mir, Edward W. Ayers </t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
+          <t xml:space="preserve"> Machine-Learned Premise Selection for Lean. </t>
         </is>
       </c>
       <c r="C1079" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -32779,28 +32779,28 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2304.00994 </t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2304.00994 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
+          <t xml:space="preserve">Bartosz Pawel Piotrowski, Miron Bartosz Kursa </t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
+          <t xml:space="preserve"> Fully Automatic Classification of Flow Cytometry Data. </t>
         </is>
       </c>
       <c r="C1080" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -32809,24 +32809,24 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
+          <t xml:space="preserve"> https://www.wikidata.org/entity/Q112319718 </t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
+          <t xml:space="preserve"> Foundations of Intelligent Systems - 24th International Symposium, ISMIS 2018, Limassol, Cyprus, October 29-31, 2018, Proceedings: 3-12 (2018).</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
+          <t xml:space="preserve">Chengsong Tan, Alastair F. Donaldson, Jonathan Julián Huerta y Munive, John Wickerson </t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
+          <t xml:space="preserve"> The Burden of Proof: Automated Tooling for Rapid Iteration on Large Mechanised Proofs. </t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -32839,28 +32839,28 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/FormaliSE66629.2025.00010 </t>
         </is>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
+          <t xml:space="preserve"> 13th IEEE/ACM International Conference on Formal Methods in Software Engineering, FormaliSE@ICSE 2025, Ottawa, ON, Canada, April 27-28, 2025: 34-45 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
+          <t xml:space="preserve">Dustin Bryant, Jonathan Julián Huerta y Munive, Simon Foster </t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> Verifying Numerical Methods with Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1082" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -32869,24 +32869,24 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2511.20550 </t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2511.20550 (2025/11).</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Andrei Herasimau, Jonathan Julián Huerta y Munive, Leonardo Lima, Martin Raszyk, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
+          <t xml:space="preserve"> A Verified Proof Checker for Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C1083" t="n">
@@ -32899,24 +32899,24 @@
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
+          <t xml:space="preserve"> https://www.isa-afp.org/entries/MFOTL_Checker.html </t>
         </is>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
+          <t xml:space="preserve"> Arch. Formal Proofs 2024: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
+          <t xml:space="preserve"> IsaVODEs: Interactive Verification of Cyber-Physical Systems at Scale. </t>
         </is>
       </c>
       <c r="C1084" t="n">
@@ -32929,12 +32929,12 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/s10817-024-09709-2 </t>
         </is>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
+          <t xml:space="preserve"> J. Autom. Reason. 68: (2024/12).</t>
         </is>
       </c>
     </row>
@@ -32946,7 +32946,7 @@
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
+          <t xml:space="preserve"> WhyMon: A Runtime Monitoring Tool with Explanations as Verdicts. </t>
         </is>
       </c>
       <c r="C1085" t="n">
@@ -32959,24 +32959,24 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-78750-8_4 </t>
         </is>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
+          <t xml:space="preserve"> Automated Technology for Verification and Analysis - 22nd International Symposium, ATVA 2024, Kyoto, Japan, October 21-25, 2024, Proceedings, Part II: 76-90 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
+          <t xml:space="preserve">Leonardo Lima, Jonathan Julián Huerta y Munive, Dmitriy Traytel </t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
+          <t xml:space="preserve"> Explainable Online Monitoring of Metric First-Order Temporal Logic. </t>
         </is>
       </c>
       <c r="C1086" t="n">
@@ -32989,28 +32989,28 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-031-57246-3_16 </t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
+          <t xml:space="preserve"> Tools and Algorithms for the Construction and Analysis of Systems - 30th International Conference, TACAS 2024, Held as Part of the European Joint Conferences on Theory and Practice of Software, ETAPS 2024, Luxembourg City, Luxembourg, April 6-11, 2024, Proceedings, Part I: 288-307 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Jonathan Julián Huerta y Munive, Simon Foster, Mario Gleirscher, Georg Struth, Christian Pardillo Laursen, Thomas Hickman </t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Scalable Automated Verification for Cyber-Physical Systems in Isabelle/HOL. </t>
         </is>
       </c>
       <c r="C1087" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -33019,24 +33019,24 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2401.12061 </t>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2401.12061 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C1088" t="n">
@@ -33049,19 +33049,19 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
+          <t xml:space="preserve"> https://doi.org/10.34727/2025/isbn.978-3-85448-084-6_28 </t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
+          <t xml:space="preserve"> Proceedings of the 25th Conference on Formal Methods in Computer-Aided Design, FMCAD 2025, Menlo Park, CA, USA, October 6-10, 2025: (2025).</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -33079,24 +33079,24 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
+          <t xml:space="preserve"> https://doi.org/10.1007/978-3-032-07021-0_2 </t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zenodo (2025/08)</t>
+          <t xml:space="preserve"> Intelligent Computer Mathematics - 18th International Conference, CICM 2025, Brasilia, Brazil, October 6-10, 2025, Proceedings: 21-28 (2025).</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
+          <t xml:space="preserve">Petra Hozzová, Márton Hajdú, Laura Kovács, Eva Maria Wagner, Richard Steven Zilincík, Andrei Voronkov </t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -33109,24 +33109,24 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
+          <t xml:space="preserve"> https://doi.org/10.5281/zenodo.16967257 </t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
+          <t xml:space="preserve"> Zenodo (2025/08)</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
+          <t xml:space="preserve">Petra Hozzová, Nikolaj Bjørner </t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
+          <t xml:space="preserve"> Synthesiz3 This: an SMT-Based Approach for Synthesis with Uncomputable Symbols. </t>
         </is>
       </c>
       <c r="C1091" t="n">
@@ -33139,58 +33139,58 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2504.16536 </t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2504.16536 (2025/04).</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Frantisek Dusek, Marco Tuccio, Clément Hongler </t>
+          <t xml:space="preserve">Márton Hajdú, Petra Hozzová, Laura Kovács, Andrei Voronkov, Eva Maria Wagner, Richard Steven Zilincík </t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Visualizing the Structure of Lenia Parameter Space. </t>
+          <t xml:space="preserve"> Synthesis Benchmarks for Automated Reasoning. </t>
         </is>
       </c>
       <c r="C1092" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FAI </t>
+          <t xml:space="preserve"> FM </t>
         </is>
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2601.01932 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2507.19827 </t>
         </is>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2601.01932 (2026/01).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2507.19827 (2025/07).</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
+          <t xml:space="preserve">Barbora Hudcová, Frantisek Dusek, Marco Tuccio, Clément Hongler </t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
+          <t xml:space="preserve"> Visualizing the Structure of Lenia Parameter Space. </t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -33199,24 +33199,24 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2601.01932 </t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2601.01932 (2026/01).</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
+          <t xml:space="preserve">Cédric Koller, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
+          <t xml:space="preserve"> Counting Short Trajectories in Elementary Cellular Automata using the Transfer Matrix Method. </t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -33229,28 +33229,28 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.09768 </t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.09768 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
+          <t xml:space="preserve">Jordan Cotler, Clément Hongler, Barbora Hudcová </t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
+          <t xml:space="preserve"> Self-replication and Computational Universality. </t>
         </is>
       </c>
       <c r="C1095" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -33259,24 +33259,24 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2510.08342 </t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2510.08342 (2025/10).</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
+          <t xml:space="preserve">Silvia Holler, Barbora Hudcová, Richard Löffler, Stuart Bartlett </t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
+          <t xml:space="preserve"> Editorial Introduction to the 2022 Conference on Artificial Life Special Issue. </t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -33289,12 +33289,12 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
+          <t xml:space="preserve"> https://doi.org/10.1162/artl_e_00439 </t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
+          <t xml:space="preserve"> Artif. Life 30: 144-146 (2024).</t>
         </is>
       </c>
     </row>
@@ -33306,11 +33306,11 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
+          <t xml:space="preserve"> Simulation limitations of affine cellular automata. </t>
         </is>
       </c>
       <c r="C1097" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -33319,58 +33319,58 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.tcs.2024.114606 </t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
+          <t xml:space="preserve"> Theor. Comput. Sci. 1003: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Aditya Gulati, Ayoub Bagheri, Nuria Oliver </t>
+          <t xml:space="preserve">Barbora Hudcová, Jakub Krásenský </t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mind the Style: Impact of Communication Style on Human-Chatbot Interaction. </t>
+          <t xml:space="preserve"> Simulation Limitations of Affine Cellular Automata. </t>
         </is>
       </c>
       <c r="C1098" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ML </t>
+          <t xml:space="preserve"> FAI </t>
         </is>
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2602.17850 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2311.14477 </t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2602.17850 (2026/02).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2311.14477 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Aditya Gulati, Ayoub Bagheri, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
+          <t xml:space="preserve"> Mind the Style: Impact of Communication Style on Human-Chatbot Interaction. </t>
         </is>
       </c>
       <c r="C1099" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -33379,24 +33379,24 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2602.17850 </t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2602.17850 (2026/02).</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
+          <t xml:space="preserve">Thilo Hagendorff, Erik Derner, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
+          <t xml:space="preserve"> Large Reasoning Models Are Autonomous Jailbreak Agents. </t>
         </is>
       </c>
       <c r="C1100" t="n">
@@ -33409,28 +33409,28 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2508.04039 </t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2508.04039 (2025/08).</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Adrián Arnaiz-Rodríguez, Miguel Baidal, Erik Derner, Jenn Layton Annable, Mark Ball, Mark Ince, Elvira Perez Vallejos, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT read who you are? </t>
+          <t xml:space="preserve"> Between Help and Harm: An Evaluation of Mental Health Crisis Handling by LLMs. </t>
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -33439,24 +33439,24 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1016/j.chbah.2024.100088 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2509.24857 </t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Comput. Hum. Behav. Artif. Humans 2: (2024).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2509.24857 (2025/09).</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
+          <t xml:space="preserve"> Can ChatGPT read who you are? </t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -33469,28 +33469,28 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
+          <t xml:space="preserve"> https://doi.org/10.1016/j.chbah.2024.100088 </t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
+          <t xml:space="preserve"> Comput. Hum. Behav. Artif. Humans 2: (2024).</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
+          <t xml:space="preserve">Erik Derner, Sara Sansalvador de la Fuente, Yoan Gutiérrez, Paloma Moreda, Nuria Oliver </t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
+          <t xml:space="preserve"> Leveraging Large Language Models to Measure Gender Bias in Gendered Languages. </t>
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -33499,24 +33499,24 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2406.13677 </t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2406.13677 (2024).</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
+          <t xml:space="preserve">Erik Derner, Kristina Batistic </t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
+          <t xml:space="preserve"> Beyond the Safeguards: Exploring the Security Risks of ChatGPT. </t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -33529,28 +33529,28 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2305.08005 </t>
         </is>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2305.08005 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Derner </t>
+          <t xml:space="preserve">Erik Derner, Dalibor Kucera, Nuria Oliver, Jan Zahálka </t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Efektivní metody pro učení modelů a řízení v robotice ; Data-efficient methods for model learning and control in robotics. </t>
+          <t xml:space="preserve"> Can ChatGPT Read Who You Are? </t>
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -33559,28 +33559,28 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://www.base-search.net/Record/3b90c2a04826d994a37adc80910808ac880f4b67e04d4782e78b8061204064db </t>
+          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2312.16070 </t>
         </is>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thesis (2022).</t>
+          <t xml:space="preserve"> arXiv CoRR abs/2312.16070 (2023).</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Erik Derner </t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
+          <t xml:space="preserve"> Efektivní metody pro učení modelů a řízení v robotice ; Data-efficient methods for model learning and control in robotics. </t>
         </is>
       </c>
       <c r="C1106" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -33589,24 +33589,24 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
+          <t xml:space="preserve"> https://www.base-search.net/Record/3b90c2a04826d994a37adc80910808ac880f4b67e04d4782e78b8061204064db </t>
         </is>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
+          <t xml:space="preserve"> Thesis (2022).</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
+          <t xml:space="preserve">Clara Gómez, Alejandra C. Hernández, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
+          <t xml:space="preserve"> Semantic Localization through Propagation of Scene Information in a Hierarchical Model. </t>
         </is>
       </c>
       <c r="C1107" t="n">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870972 </t>
         </is>
       </c>
       <c r="F1107" t="inlineStr">
@@ -33631,16 +33631,16 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas Mitschke, Andreas Zindel </t>
+          <t xml:space="preserve">Alejandra C. Hernández, Clara Gómez, Erik Derner, Ramón Barber </t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Towards Resilient and Sustainable Global Industrial Systems: An Evolutionary-Based Approach. </t>
+          <t xml:space="preserve"> Indoor Scene Recognition based on Weighted Voting Schemes. </t>
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
@@ -33649,28 +33649,28 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> https://doi.org/10.48550/arXiv.2503.11688 </t>
+          <t xml:space="preserve"> https://doi.org/10.1109/ECMR.2019.8870931 </t>
         </is>
       </c>
       <c r="F1108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> arXiv CoRR abs/2503.11688 (2025/03).</t>
+          <t xml:space="preserve"> 2019 European Conference on Mobile Robots, ECMR 2019, Prague, Czech Republic, September 4-6, 2019: 1-6 (2019).</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miroslav Kulich, Jirí Kubalík, Libor Preucil </t>
+          <t xml:space="preserve">Václav Jirkovský, Jirí Kubalík, Petr Kadera, Arnd Schirrmann, Andreas 